--- a/2026_자산시장_업데이트.xlsx
+++ b/2026_자산시장_업데이트.xlsx
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4702.7001953125</v>
+        <v>4879.60009765625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -577,19 +577,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>13.1%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>9.0%</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>9.0%</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>11.0%</t>
@@ -602,27 +602,27 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4786.960009765625</v>
+        <v>4652.464990234375</v>
       </c>
       <c r="Q2" t="n">
-        <v>4881.998315429688</v>
+        <v>4908.556656901042</v>
       </c>
       <c r="R2" t="n">
-        <v>4533.956652832031</v>
+        <v>4585.077484130859</v>
       </c>
       <c r="S2" t="n">
-        <v>3753.991552575842</v>
+        <v>3819.718823717786</v>
       </c>
       <c r="T2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -656,12 +656,12 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02'], 'prices': [1524.5, 1549.199951171875, 1566.199951171875, 1571.800048828125, 1557.4000244140625, 1551.699951171875, 1557.5, 1548.4000244140625, 1542.4000244140625, 1552.0999755859375, 1549.0, 1558.800048828125, 1556.4000244140625, 1555.300048828125, 1564.5999755859375, 1571.0999755859375, 1576.800048828125, 1569.199951171875, 1569.800048828125, 1583.5, 1582.9000244140625, 1577.199951171875, 1550.4000244140625, 1557.800048828125, 1565.0999755859375, 1568.5999755859375, 1574.699951171875, 1565.5999755859375, 1567.4000244140625, 1575.0999755859375, 1582.699951171875, 1600.0, 1607.5, 1616.5999755859375, 1644.5999755859375, 1672.4000244140625, 1646.9000244140625, 1640.0, 1640.0, 1564.0999755859375, 1592.300048828125, 1642.0999755859375, 1641.0999755859375, 1666.4000244140625, 1670.800048828125, 1674.5, 1659.0999755859375, 1641.4000244140625, 1589.300048828125, 1515.699951171875, 1485.9000244140625, 1524.9000244140625, 1477.300048828125, 1478.5999755859375, 1484.0, 1567.0, 1660.199951171875, 1632.300048828125, 1650.0999755859375, 1623.9000244140625, 1622.0, 1583.4000244140625, 1578.199951171875, 1625.699951171875, 1633.699951171875, 1677.0, 1664.800048828125, 1665.4000244140625, 1736.199951171875, 1744.800048828125, 1756.699951171875, 1727.199951171875, 1720.4000244140625, 1689.199951171875, 1701.5999755859375, 1678.199951171875, 1728.699951171875, 1733.300048828125, 1723.5, 1711.9000244140625, 1710.5, 1703.4000244140625, 1684.199951171875, 1694.5, 1706.9000244140625, 1704.4000244140625, 1684.199951171875, 1721.800048828125, 1709.9000244140625, 1695.300048828125, 1704.4000244140625, 1713.9000244140625, 1738.0999755859375, 1753.4000244140625, 1731.800048828125, 1744.199951171875, 1750.5999755859375, 1720.5, 1734.5999755859375, 1704.800048828125, 1710.300048828125, 1713.300048828125, 1736.9000244140625, 1737.800048828125, 1725.199951171875, 1697.800048828125, 1718.9000244140625, 1676.199951171875, 1698.300048828125, 1714.699951171875, 1713.300048828125, 1732.0, 1729.300048828125, 1720.300048828125, 1729.5999755859375, 1729.199951171875, 1724.800048828125, 1745.9000244140625, 1756.699951171875, 1772.0999755859375, 1765.800048828125, 1762.0999755859375, 1772.5, 1774.800048828125, 1793.0, 1773.199951171875, 1784.0, 1788.5, 1804.199951171875, 1815.5, 1799.199951171875, 1798.199951171875, 1811.0, 1810.5999755859375, 1811.4000244140625, 1798.699951171875, 1808.300048828125, 1815.9000244140625, 1842.4000244140625, 1864.0999755859375, 1889.0999755859375, 1897.300048828125, 1931.0, 1944.699951171875, 1953.5, 1942.300048828125, 1962.800048828125, 1966.0, 2001.199951171875, 2031.0999755859375, 2051.5, 2010.0999755859375, 2024.4000244140625, 1932.5999755859375, 1934.9000244140625, 1956.699951171875, 1937.0, 1985.0, 1999.4000244140625, 1958.699951171875, 1933.800048828125, 1934.5999755859375, 1927.699951171875, 1911.800048828125, 1940.699951171875, 1921.5999755859375, 1964.5999755859375, 1967.5999755859375, 1968.199951171875, 1934.4000244140625, 1927.5999755859375, 1923.9000244140625, 1933.0, 1944.699951171875, 1954.199951171875, 1937.800048828125, 1953.0999755859375, 1956.300048828125, 1960.199951171875, 1940.0, 1952.0999755859375, 1901.199951171875, 1898.5999755859375, 1859.9000244140625, 1868.300048828125, 1857.699951171875, 1872.800048828125, 1894.300048828125, 1887.5, 1908.4000244140625, 1900.199951171875, 1912.5, 1901.0999755859375, 1883.5999755859375, 1888.5999755859375, 1919.5, 1922.5, 1888.5, 1901.300048828125, 1903.199951171875, 1900.800048828125, 1906.4000244140625, 1910.4000244140625, 1924.5999755859375, 1901.0999755859375, 1902.0, 1902.699951171875, 1908.800048828125, 1876.199951171875, 1865.5999755859375, 1877.4000244140625, 1890.4000244140625, 1908.5, 1894.5999755859375, 1945.300048828125, 1950.300048828125, 1853.199951171875, 1875.4000244140625, 1860.699951171875, 1872.5999755859375, 1885.699951171875, 1887.300048828125, 1884.5, 1873.5, 1861.0999755859375, 1872.5999755859375, 1837.800048828125, 1804.800048828125, 1805.699951171875, 1781.9000244140625, 1775.699951171875, 1814.0999755859375, 1825.699951171875, 1836.800048828125, 1835.9000244140625, 1861.800048828125, 1870.800048828125, 1834.5999755859375, 1833.5999755859375, 1839.800048828125, 1828.699951171875, 1852.300048828125, 1856.0999755859375, 1887.199951171875, 1885.699951171875, 1879.199951171875, 1866.5999755859375, 1874.699951171875, 1879.9000244140625, 1877.199951171875, 1879.699951171875, 1891.0, 1893.0999755859375, 1944.699951171875, 1952.699951171875, 1906.9000244140625, 1912.300048828125, 1834.0999755859375, 1849.5999755859375, 1842.9000244140625, 1853.5999755859375, 1850.300048828125, 1829.300048828125, 1839.5, 1865.9000244140625, 1865.300048828125, 1855.699951171875, 1854.9000244140625, 1850.699951171875, 1844.9000244140625, 1837.9000244140625, 1847.300048828125, 1860.800048828125, 1830.5, 1832.199951171875, 1788.9000244140625, 1810.9000244140625, 1831.9000244140625, 1835.300048828125, 1840.5999755859375, 1824.9000244140625, 1821.5999755859375, 1797.199951171875, 1771.0999755859375, 1773.4000244140625, 1775.800048828125, 1806.699951171875, 1804.4000244140625, 1796.4000244140625, 1774.4000244140625, 1728.0999755859375, 1722.5, 1733.0999755859375, 1715.300048828125, 1700.199951171875, 1698.0, 1677.699951171875, 1716.5999755859375, 1721.5, 1722.300048828125, 1719.5, 1728.9000244140625, 1730.5999755859375, 1726.800048828125, 1732.199951171875, 1741.4000244140625, 1737.800048828125, 1724.699951171875, 1732.9000244140625, 1724.9000244140625, 1732.199951171875, 1712.0999755859375, 1683.9000244140625, 1713.800048828125, 1726.5, 1727.0, 1741.5, 1740.0999755859375, 1756.800048828125, 1743.300048828125, 1731.199951171875, 1746.199951171875, 1734.9000244140625, 1765.4000244140625, 1779.0, 1769.4000244140625, 1777.300048828125, 1792.300048828125, 1781.199951171875, 1777.0, 1779.199951171875, 1778.0, 1773.199951171875, 1768.0999755859375, 1767.300048828125, 1791.4000244140625, 1775.800048828125, 1784.0999755859375, 1815.5, 1831.0999755859375, 1837.5, 1835.9000244140625, 1822.5999755859375, 1823.800048828125, 1837.9000244140625, 1867.5, 1867.800048828125, 1881.300048828125, 1881.800048828125, 1876.699951171875, 1884.5999755859375, 1898.0999755859375, 1901.300048828125, 1895.699951171875, 1902.5, 1902.9000244140625, 1907.5, 1871.199951171875, 1889.800048828125, 1896.800048828125, 1892.199951171875, 1893.199951171875, 1894.199951171875, 1877.4000244140625, 1864.0, 1854.5, 1859.5, 1773.800048828125, 1767.9000244140625, 1781.800048828125, 1776.300048828125, 1782.300048828125, 1775.5999755859375, 1776.5999755859375, 1779.5999755859375, 1762.800048828125, 1770.800048828125, 1775.9000244140625, 1782.5999755859375, 1793.5, 1801.5, 1799.5999755859375, 1810.0, 1805.5, 1809.4000244140625, 1824.300048828125, 1828.4000244140625, 1814.5, 1808.699951171875, 1810.9000244140625, 1802.9000244140625, 1805.0, 1801.4000244140625, 1798.699951171875, 1799.5, 1799.5, 1831.199951171875, 1812.5999755859375, 1818.0999755859375, 1810.0999755859375, 1810.5, 1805.0999755859375, 1760.0, 1723.4000244140625, 1728.800048828125, 1750.4000244140625, 1749.0, 1775.199951171875, 1786.9000244140625, 1785.0, 1781.5999755859375, 1780.199951171875, 1781.0, 1803.199951171875, 1805.5999755859375, 1788.199951171875, 1792.199951171875, 1816.5999755859375, 1809.0, 1815.0, 1813.0999755859375, 1808.699951171875, 1830.9000244140625, 1795.9000244140625, 1790.699951171875, 1797.4000244140625, 1789.5999755859375, 1792.0, 1804.699951171875, 1792.4000244140625, 1754.5999755859375, 1749.4000244140625, 1761.800048828125, 1776.0, 1776.699951171875, 1747.699951171875, 1749.699951171875, 1750.0, 1735.800048828125, 1721.5, 1755.300048828125, 1757.0, 1766.199951171875, 1759.5999755859375, 1760.5, 1757.9000244140625, 1756.300048828125, 1754.5999755859375, 1758.300048828125, 1793.699951171875, 1796.699951171875, 1767.199951171875, 1764.800048828125, 1769.699951171875, 1784.0999755859375, 1781.199951171875, 1795.5, 1806.0, 1792.699951171875, 1797.9000244140625, 1801.5999755859375, 1783.0, 1795.0999755859375, 1788.699951171875, 1763.5999755859375, 1793.0, 1816.4000244140625, 1827.4000244140625, 1830.199951171875, 1847.5999755859375, 1863.199951171875, 1867.9000244140625, 1866.0999755859375, 1853.5999755859375, 1869.699951171875, 1861.0, 1851.199951171875, 1806.0, 1783.5, 1784.0999755859375, 1785.300048828125, 1782.300048828125, 1773.5999755859375, 1781.5999755859375, 1760.699951171875, 1782.0, 1777.5, 1782.5999755859375, 1783.4000244140625, 1774.5999755859375, 1782.9000244140625, 1786.300048828125, 1770.4000244140625, 1762.5999755859375, 1796.5999755859375, 1803.800048828125, 1793.699951171875, 1787.9000244140625, 1801.5999755859375, 1811.199951171875, 1808.0999755859375, 1810.199951171875, 1805.0999755859375, 1812.699951171875, 1827.5, 1799.4000244140625, 1814.0, 1824.5999755859375, 1788.699951171875, 1797.0, 1798.4000244140625, 1818.5999755859375, 1827.199951171875, 1821.199951171875, 1816.5, 1812.300048828125, 1843.0999755859375, 1842.5, 1831.800048828125, 1841.699951171875, 1852.699951171875, 1829.9000244140625, 1793.300048828125, 1784.9000244140625, 1795.0, 1800.300048828125, 1809.199951171875, 1803.0, 1806.5999755859375, 1820.5999755859375, 1826.5999755859375, 1835.199951171875, 1836.199951171875, 1840.800048828125, 1868.0, 1854.800048828125, 1870.199951171875, 1900.699951171875, 1898.5999755859375, 1906.0999755859375, 1909.199951171875, 1925.0999755859375, 1886.5, 1899.4000244140625, 1942.4000244140625, 1920.9000244140625, 1934.4000244140625, 1965.0999755859375, 1993.9000244140625, 2040.0999755859375, 1985.9000244140625, 1998.0999755859375, 1982.699951171875, 1959.5999755859375, 1928.5, 1908.0, 1942.0999755859375, 1928.199951171875, 1928.5999755859375, 1920.699951171875, 1936.5999755859375, 1961.5999755859375, 1953.800048828125, 1939.5999755859375, 1912.0, 1933.5, 1949.199951171875, 1919.0999755859375, 1929.199951171875, 1922.9000244140625, 1918.4000244140625, 1933.800048828125, 1941.5999755859375, 1944.300048828125, 1972.0999755859375, 1981.0, 1970.9000244140625, 1982.9000244140625, 1955.699951171875, 1952.300048828125, 1944.9000244140625, 1931.0, 1893.199951171875, 1901.4000244140625, 1885.9000244140625, 1888.699951171875, 1909.300048828125, 1861.800048828125, 1868.800048828125, 1867.0, 1874.0, 1881.199951171875, 1857.0999755859375, 1839.9000244140625, 1852.5999755859375, 1823.800048828125, 1807.4000244140625, 1813.5, 1818.199951171875, 1815.9000244140625, 1841.199951171875, 1841.800048828125, 1847.800048828125, 1865.0999755859375, 1846.199951171875, 1847.4000244140625, 1851.300048828125, 1842.699951171875, 1843.300048828125, 1866.5, 1845.4000244140625, 1839.199951171875, 1847.5, 1851.9000244140625, 1848.800048828125, 1871.5, 1828.0, 1809.</t>
+          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [1524.5, 1549.199951171875, 1566.199951171875, 1571.800048828125, 1557.4000244140625, 1551.699951171875, 1557.5, 1548.4000244140625, 1542.4000244140625, 1552.0999755859375, 1549.0, 1558.800048828125, 1556.4000244140625, 1555.300048828125, 1564.5999755859375, 1571.0999755859375, 1576.800048828125, 1569.199951171875, 1569.800048828125, 1583.5, 1582.9000244140625, 1577.199951171875, 1550.4000244140625, 1557.800048828125, 1565.0999755859375, 1568.5999755859375, 1574.699951171875, 1565.5999755859375, 1567.4000244140625, 1575.0999755859375, 1582.699951171875, 1600.0, 1607.5, 1616.5999755859375, 1644.5999755859375, 1672.4000244140625, 1646.9000244140625, 1640.0, 1640.0, 1564.0999755859375, 1592.300048828125, 1642.0999755859375, 1641.0999755859375, 1666.4000244140625, 1670.800048828125, 1674.5, 1659.0999755859375, 1641.4000244140625, 1589.300048828125, 1515.699951171875, 1485.9000244140625, 1524.9000244140625, 1477.300048828125, 1478.5999755859375, 1484.0, 1567.0, 1660.199951171875, 1632.300048828125, 1650.0999755859375, 1623.9000244140625, 1622.0, 1583.4000244140625, 1578.199951171875, 1625.699951171875, 1633.699951171875, 1677.0, 1664.800048828125, 1665.4000244140625, 1736.199951171875, 1744.800048828125, 1756.699951171875, 1727.199951171875, 1720.4000244140625, 1689.199951171875, 1701.5999755859375, 1678.199951171875, 1728.699951171875, 1733.300048828125, 1723.5, 1711.9000244140625, 1710.5, 1703.4000244140625, 1684.199951171875, 1694.5, 1706.9000244140625, 1704.4000244140625, 1684.199951171875, 1721.800048828125, 1709.9000244140625, 1695.300048828125, 1704.4000244140625, 1713.9000244140625, 1738.0999755859375, 1753.4000244140625, 1731.800048828125, 1744.199951171875, 1750.5999755859375, 1720.5, 1734.5999755859375, 1704.800048828125, 1710.300048828125, 1713.300048828125, 1736.9000244140625, 1737.800048828125, 1725.199951171875, 1697.800048828125, 1718.9000244140625, 1676.199951171875, 1698.300048828125, 1714.699951171875, 1713.300048828125, 1732.0, 1729.300048828125, 1720.300048828125, 1729.5999755859375, 1729.199951171875, 1724.800048828125, 1745.9000244140625, 1756.699951171875, 1772.0999755859375, 1765.800048828125, 1762.0999755859375, 1772.5, 1774.800048828125, 1793.0, 1773.199951171875, 1784.0, 1788.5, 1804.199951171875, 1815.5, 1799.199951171875, 1798.199951171875, 1811.0, 1810.5999755859375, 1811.4000244140625, 1798.699951171875, 1808.300048828125, 1815.9000244140625, 1842.4000244140625, 1864.0999755859375, 1889.0999755859375, 1897.300048828125, 1931.0, 1944.699951171875, 1953.5, 1942.300048828125, 1962.800048828125, 1966.0, 2001.199951171875, 2031.0999755859375, 2051.5, 2010.0999755859375, 2024.4000244140625, 1932.5999755859375, 1934.9000244140625, 1956.699951171875, 1937.0, 1985.0, 1999.4000244140625, 1958.699951171875, 1933.800048828125, 1934.5999755859375, 1927.699951171875, 1911.800048828125, 1940.699951171875, 1921.5999755859375, 1964.5999755859375, 1967.5999755859375, 1968.199951171875, 1934.4000244140625, 1927.5999755859375, 1923.9000244140625, 1933.0, 1944.699951171875, 1954.199951171875, 1937.800048828125, 1953.0999755859375, 1956.300048828125, 1960.199951171875, 1940.0, 1952.0999755859375, 1901.199951171875, 1898.5999755859375, 1859.9000244140625, 1868.300048828125, 1857.699951171875, 1872.800048828125, 1894.300048828125, 1887.5, 1908.4000244140625, 1900.199951171875, 1912.5, 1901.0999755859375, 1883.5999755859375, 1888.5999755859375, 1919.5, 1922.5, 1888.5, 1901.300048828125, 1903.199951171875, 1900.800048828125, 1906.4000244140625, 1910.4000244140625, 1924.5999755859375, 1901.0999755859375, 1902.0, 1902.699951171875, 1908.800048828125, 1876.199951171875, 1865.5999755859375, 1877.4000244140625, 1890.4000244140625, 1908.5, 1894.5999755859375, 1945.300048828125, 1950.300048828125, 1853.199951171875, 1875.4000244140625, 1860.699951171875, 1872.5999755859375, 1885.699951171875, 1887.300048828125, 1884.5, 1873.5, 1861.0999755859375, 1872.5999755859375, 1837.800048828125, 1804.800048828125, 1805.699951171875, 1781.9000244140625, 1775.699951171875, 1814.0999755859375, 1825.699951171875, 1836.800048828125, 1835.9000244140625, 1861.800048828125, 1870.800048828125, 1834.5999755859375, 1833.5999755859375, 1839.800048828125, 1828.699951171875, 1852.300048828125, 1856.0999755859375, 1887.199951171875, 1885.699951171875, 1879.199951171875, 1866.5999755859375, 1874.699951171875, 1879.9000244140625, 1877.199951171875, 1879.699951171875, 1891.0, 1893.0999755859375, 1944.699951171875, 1952.699951171875, 1906.9000244140625, 1912.300048828125, 1834.0999755859375, 1849.5999755859375, 1842.9000244140625, 1853.5999755859375, 1850.300048828125, 1829.300048828125, 1839.5, 1865.9000244140625, 1865.300048828125, 1855.699951171875, 1854.9000244140625, 1850.699951171875, 1844.9000244140625, 1837.9000244140625, 1847.300048828125, 1860.800048828125, 1830.5, 1832.199951171875, 1788.9000244140625, 1810.9000244140625, 1831.9000244140625, 1835.300048828125, 1840.5999755859375, 1824.9000244140625, 1821.5999755859375, 1797.199951171875, 1771.0999755859375, 1773.4000244140625, 1775.800048828125, 1806.699951171875, 1804.4000244140625, 1796.4000244140625, 1774.4000244140625, 1728.0999755859375, 1722.5, 1733.0999755859375, 1715.300048828125, 1700.199951171875, 1698.0, 1677.699951171875, 1716.5999755859375, 1721.5, 1722.300048828125, 1719.5, 1728.9000244140625, 1730.5999755859375, 1726.800048828125, 1732.199951171875, 1741.4000244140625, 1737.800048828125, 1724.699951171875, 1732.9000244140625, 1724.9000244140625, 1732.199951171875, 1712.0999755859375, 1683.9000244140625, 1713.800048828125, 1726.5, 1727.0, 1741.5, 1740.0999755859375, 1756.800048828125, 1743.300048828125, 1731.199951171875, 1746.199951171875, 1734.9000244140625, 1765.4000244140625, 1779.0, 1769.4000244140625, 1777.300048828125, 1792.300048828125, 1781.199951171875, 1777.0, 1779.199951171875, 1778.0, 1773.199951171875, 1768.0999755859375, 1767.300048828125, 1791.4000244140625, 1775.800048828125, 1784.0999755859375, 1815.5, 1831.0999755859375, 1837.5, 1835.9000244140625, 1822.5999755859375, 1823.800048828125, 1837.9000244140625, 1867.5, 1867.800048828125, 1881.300048828125, 1881.800048828125, 1876.699951171875, 1884.5999755859375, 1898.0999755859375, 1901.300048828125, 1895.699951171875, 1902.5, 1902.9000244140625, 1907.5, 1871.199951171875, 1889.800048828125, 1896.800048828125, 1892.199951171875, 1893.199951171875, 1894.199951171875, 1877.4000244140625, 1864.0, 1854.5, 1859.5, 1773.800048828125, 1767.9000244140625, 1781.800048828125, 1776.300048828125, 1782.300048828125, 1775.5999755859375, 1776.5999755859375, 1779.5999755859375, 1762.800048828125, 1770.800048828125, 1775.9000244140625, 1782.5999755859375, 1793.5, 1801.5, 1799.5999755859375, 1810.0, 1805.5, 1809.4000244140625, 1824.300048828125, 1828.4000244140625, 1814.5, 1808.699951171875, 1810.9000244140625, 1802.9000244140625, 1805.0, 1801.4000244140625, 1798.699951171875, 1799.5, 1799.5, 1831.199951171875, 1812.5999755859375, 1818.0999755859375, 1810.0999755859375, 1810.5, 1805.0999755859375, 1760.0, 1723.4000244140625, 1728.800048828125, 1750.4000244140625, 1749.0, 1775.199951171875, 1786.9000244140625, 1785.0, 1781.5999755859375, 1780.199951171875, 1781.0, 1803.199951171875, 1805.5999755859375, 1788.199951171875, 1792.199951171875, 1816.5999755859375, 1809.0, 1815.0, 1813.0999755859375, 1808.699951171875, 1830.9000244140625, 1795.9000244140625, 1790.699951171875, 1797.4000244140625, 1789.5999755859375, 1792.0, 1804.699951171875, 1792.4000244140625, 1754.5999755859375, 1749.4000244140625, 1761.800048828125, 1776.0, 1776.699951171875, 1747.699951171875, 1749.699951171875, 1750.0, 1735.800048828125, 1721.5, 1755.300048828125, 1757.0, 1766.199951171875, 1759.5999755859375, 1760.5, 1757.9000244140625, 1756.300048828125, 1754.5999755859375, 1758.300048828125, 1793.699951171875, 1796.699951171875, 1767.199951171875, 1764.800048828125, 1769.699951171875, 1784.0999755859375, 1781.199951171875, 1795.5, 1806.0, 1792.699951171875, 1797.9000244140625, 1801.5999755859375, 1783.0, 1795.0999755859375, 1788.699951171875, 1763.5999755859375, 1793.0, 1816.4000244140625, 1827.4000244140625, 1830.199951171875, 1847.5999755859375, 1863.199951171875, 1867.9000244140625, 1866.0999755859375, 1853.5999755859375, 1869.699951171875, 1861.0, 1851.199951171875, 1806.0, 1783.5, 1784.0999755859375, 1785.300048828125, 1782.300048828125, 1773.5999755859375, 1781.5999755859375, 1760.699951171875, 1782.0, 1777.5, 1782.5999755859375, 1783.4000244140625, 1774.5999755859375, 1782.9000244140625, 1786.300048828125, 1770.4000244140625, 1762.5999755859375, 1796.5999755859375, 1803.800048828125, 1793.699951171875, 1787.9000244140625, 1801.5999755859375, 1811.199951171875, 1808.0999755859375, 1810.199951171875, 1805.0999755859375, 1812.699951171875, 1827.5, 1799.4000244140625, 1814.0, 1824.5999755859375, 1788.699951171875, 1797.0, 1798.4000244140625, 1818.5999755859375, 1827.199951171875, 1821.199951171875, 1816.5, 1812.300048828125, 1843.0999755859375, 1842.5, 1831.800048828125, 1841.699951171875, 1852.699951171875, 1829.9000244140625, 1793.300048828125, 1784.9000244140625, 1795.0, 1800.300048828125, 1809.199951171875, 1803.0, 1806.5999755859375, 1820.5999755859375, 1826.5999755859375, 1835.199951171875, 1836.199951171875, 1840.800048828125, 1868.0, 1854.800048828125, 1870.199951171875, 1900.699951171875, 1898.5999755859375, 1906.0999755859375, 1909.199951171875, 1925.0999755859375, 1886.5, 1899.4000244140625, 1942.4000244140625, 1920.9000244140625, 1934.4000244140625, 1965.0999755859375, 1993.9000244140625, 2040.0999755859375, 1985.9000244140625, 1998.0999755859375, 1982.699951171875, 1959.5999755859375, 1928.5, 1908.0, 1942.0999755859375, 1928.199951171875, 1928.5999755859375, 1920.699951171875, 1936.5999755859375, 1961.5999755859375, 1953.800048828125, 1939.5999755859375, 1912.0, 1933.5, 1949.199951171875, 1919.0999755859375, 1929.199951171875, 1922.9000244140625, 1918.4000244140625, 1933.800048828125, 1941.5999755859375, 1944.300048828125, 1972.0999755859375, 1981.0, 1970.9000244140625, 1982.9000244140625, 1955.699951171875, 1952.300048828125, 1944.9000244140625, 1931.0, 1893.199951171875, 1901.4000244140625, 1885.9000244140625, 1888.699951171875, 1909.300048828125, 1861.800048828125, 1868.800048828125, 1867.0, 1874.0, 1881.199951171875, 1857.0999755859375, 1839.9000244140625, 1852.5999755859375, 1823.800048828125, 1807.4000244140625, 1813.5, 1818.199951171875, 1815.9000244140625, 1841.199951171875, 1841.800048828125, 1847.800048828125, 1865.0999755859375, 1846.199951171875, 1847.4000244140625, 1851.300048828125, 1842.69995117</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -672,11 +672,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.16999816894531</v>
+        <v>81.84200286865234</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-36.4%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -711,27 +711,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -740,22 +740,22 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>76.34119987487793</v>
+        <v>73.90205001831055</v>
       </c>
       <c r="Q3" t="n">
-        <v>83.26421699523925</v>
+        <v>81.73515014648437</v>
       </c>
       <c r="R3" t="n">
-        <v>69.86681687037149</v>
+        <v>72.12411692937215</v>
       </c>
       <c r="S3" t="n">
-        <v>49.09719811476671</v>
+        <v>50.58490590925341</v>
       </c>
       <c r="T3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
@@ -765,12 +765,12 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02'], 'prices': [17.965999603271484, 18.06800079345703, 18.097000122070312, 18.31599998474121, 18.08799934387207, 17.860000610351562, 18.033000946044922, 17.926000595092773, 17.673999786376953, 17.92300033569336, 17.875, 18.01300048828125, 17.750999450683594, 17.770999908447266, 17.773000717163086, 18.05699920654297, 18.0, 17.402000427246094, 17.430999755859375, 17.95199966430664, 17.972000122070312, 17.639999389648438, 17.527999877929688, 17.569000244140625, 17.788999557495117, 17.665000915527344, 17.757999420166016, 17.572999954223633, 17.47800064086914, 17.600000381469727, 17.71500015258789, 18.131000518798828, 18.29199981689453, 18.30900001525879, 18.520999908447266, 18.868000030517578, 18.183000564575195, 17.826000213623047, 17.658000946044922, 16.386999130249023, 16.679000854492188, 17.128999710083008, 17.187000274658203, 17.341999053955078, 17.214000701904297, 17.000999450683594, 16.9060001373291, 16.729000091552734, 15.961000442504883, 14.456000328063965, 12.772000312805176, 12.468999862670898, 11.734999656677246, 12.097000122070312, 12.348999977111816, 13.225000381469727, 14.229000091552734, 14.836999893188477, 14.640000343322754, 14.498000144958496, 14.074000358581543, 14.097999572753906, 13.925999641418457, 14.595999717712402, 14.435999870300293, 15.111000061035156, 15.42199993133545, 15.147000312805176, 15.994999885559082, 15.479000091552734, 16.07200050354004, 15.446999549865723, 15.564000129699707, 15.237000465393066, 15.555999755859375, 14.817999839782715, 15.277000427246094, 15.347999572753906, 15.253999710083008, 15.201000213623047, 15.161999702453613, 15.15999984741211, 14.89799976348877, 14.86299991607666, 14.722000122070312, 15.057000160217285, 14.987000465393066, 15.562000274658203, 15.739999771118164, 15.63599967956543, 15.687000274658203, 15.663000106811523, 16.13599967956543, 17.04599952697754, 17.464000701904297, 17.892000198364258, 18.00200080871582, 17.334999084472656, 17.663999557495117, 17.565000534057617, 17.68600082397461, 17.895000457763672, 18.440000534057617, 18.76799964904785, 18.207000732421875, 17.92099952697754, 18.02400016784668, 17.44300079345703, 17.868000030517578, 17.77400016784668, 17.775999069213867, 17.868999481201172, 17.461999893188477, 17.378999710083008, 17.631999969482422, 17.756999969482422, 17.493000030517578, 17.832000732421875, 17.886999130249023, 18.051000595092773, 17.658000946044922, 17.882999420166016, 18.023000717163086, 17.979999542236328, 18.541000366210938, 18.132999420166016, 18.243999481201172, 18.503999710083008, 18.628000259399414, 19.08099937438965, 18.881999969482422, 18.982999801635742, 19.708999633789062, 19.451000213623047, 19.684999465942383, 19.496999740600586, 19.684999465942383, 20.124000549316406, 21.496999740600586, 23.08300018310547, 22.94499969482422, 22.808000564575195, 24.47599983215332, 24.266000747680664, 24.292999267578125, 23.34000015258789, 24.18899917602539, 24.389999389648438, 26.011999130249023, 26.87700080871582, 28.386999130249023, 27.533000946044922, 29.249000549316406, 26.03700065612793, 25.954999923706055, 27.694000244140625, 26.065000534057617, 27.64299964904785, 28.048999786376953, 27.315000534057617, 27.121999740600586, 26.707000732421875, 26.58799934387207, 26.253999710083008, 27.43000030517578, 27.010000228881836, 27.610000610351562, 28.437000274658203, 28.486000061035156, 27.249000549316406, 26.735000610351562, 26.576000213623047, 26.86400032043457, 26.954999923706055, 27.163000106811523, 26.73900032043457, 27.229000091552734, 27.34600067138672, 27.354999542236328, 26.985000610351562, 27.027999877929688, 24.298999786376953, 24.441999435424805, 23.013999938964844, 23.118000030517578, 23.017000198364258, 23.527999877929688, 24.3799991607666, 23.433000564575195, 24.19300079345703, 23.97100067138672, 24.50200080871582, 23.8700008392334, 23.847999572753906, 23.836999893188477, 25.069000244140625, 25.22599983215332, 24.086000442504883, 24.36400032043457, 24.19300079345703, 24.368999481201172, 24.656999588012695, 24.937000274658203, 25.19700050354004, 24.665000915527344, 24.62700080871582, 24.375999450683594, 24.525999069213867, 23.323999404907227, 23.339000701904297, 23.617000579833984, 24.006000518798828, 24.30500030517578, 23.86400032043457, 25.17099952697754, 25.645999908447266, 23.684999465942383, 24.445999145507812, 24.250999450683594, 24.290000915527344, 24.759000778198242, 24.785999298095703, 24.635000228881836, 24.433000564575195, 24.033000946044922, 24.347999572753906, 23.624000549316406, 23.29199981689453, 23.356000900268555, 22.55299949645996, 22.534000396728516, 24.033000946044922, 24.024999618530273, 24.086999893188477, 24.202999114990234, 24.740999221801758, 24.68400001525879, 23.93000030517578, 24.0310001373291, 24.031999588012695, 23.985000610351562, 24.58099937438965, 24.985000610351562, 26.100000381469727, 25.948999404907227, 26.277999877929688, 25.43400001525879, 25.823999404907227, 25.81100082397461, 26.459999084472656, 26.13800048828125, 26.488000869750977, 26.332000732421875, 27.284000396728516, 27.570999145507812, 26.972999572753906, 27.200000762939453, 24.582000732421875, 25.23900032043457, 25.384000778198242, 25.520000457763672, 25.746000289916992, 24.825000762939453, 25.27899932861328, 25.733999252319336, 25.82200050354004, 25.52400016784668, 25.454999923706055, 25.52899932861328, 25.375999450683594, 25.909000396728516, 26.899999618530273, 29.398000717163086, 26.384000778198242, 26.878000259399414, 26.222999572753906, 27.013999938964844, 27.56999969482422, 27.395999908447266, 27.073999404907227, 27.04199981689453, 27.322999954223633, 27.319000244140625, 27.31399917602539, 27.07699966430664, 27.25200080871582, 28.08300018310547, 27.68600082397461, 27.85700035095215, 27.636999130249023, 26.402000427246094, 26.64699935913086, 26.850000381469727, 26.35700035095215, 25.43400001525879, 25.256999969482422, 25.239999771118164, 26.148000717163086, 26.101999282836914, 26.16200065612793, 25.8799991607666, 26.253000259399414, 25.974000930786133, 26.030000686645508, 26.320999145507812, 26.29199981689453, 25.740999221801758, 25.200000762939453, 25.201000213623047, 25.02199935913086, 25.091999053955078, 24.746999740600586, 24.121000289916992, 24.517000198364258, 24.934999465942383, 24.76300048828125, 25.211999893188477, 25.232999801635742, 25.569000244140625, 25.31100082397461, 24.85300064086914, 25.41699981689453, 25.514999389648438, 25.95599937438965, 26.099000930786133, 25.83099937438965, 25.834999084472656, 26.565000534057617, 26.173999786376953, 26.07699966430664, 26.211000442504883, 26.41200065612793, 26.08099937438965, 26.05299949645996, 25.85300064086914, 26.94300079345703, 26.538999557495117, 26.50200080871582, 27.461999893188477, 27.461999893188477, 27.479000091552734, 27.656999588012695, 27.231000900268555, 27.04400062561035, 27.35300064086914, 28.260000228881836, 28.31399917602539, 28.007999420166016, 28.052000045776367, 27.472999572753906, 27.886999130249023, 28.03700065612793, 27.85300064086914, 27.91900062561035, 27.993000030517578, 28.08300018310547, 28.18600082397461, 27.459999084472656, 27.878999710083008, 28.000999450683594, 27.71500015258789, 27.985000610351562, 28.014999389648438, 28.131000518798828, 28.02400016784668, 27.679000854492188, 27.799999237060547, 25.8439998626709, 25.95800018310547, 26.014999389648438, 25.847999572753906, 26.107999801635742, 26.047000885009766, 26.082000732421875, 26.218000411987305, 25.871999740600586, 26.165000915527344, 26.075000762939453, 26.481000900268555, 26.15399932861328, 26.110000610351562, 25.966999053955078, 26.211000442504883, 26.216999053955078, 26.114999771118164, 26.246000289916992, 26.375, 25.777000427246094, 25.125999450683594, 24.976999282836914, 25.238000869750977, 25.364999771118164, 25.218000411987305, 25.295000076293945, 24.631999969482422, 24.856000900268555, 25.763999938964844, 25.527999877929688, 25.55699920654297, 25.56599998474121, 25.445999145507812, 25.277000427246094, 24.312000274658203, 23.2549991607666, 23.37700080871582, 23.474000930786133, 23.104999542236328, 23.76799964904785, 23.780000686645508, 23.648000717163086, 23.41200065612793, 23.219999313354492, 23.104999542236328, 23.64900016784668, 23.889999389648438, 23.770999908447266, 23.54599952697754, 24.059999465942383, 23.959999084472656, 23.959999084472656, 24.177000045776367, 23.875, 24.761999130249023, 24.333999633789062, 24.011999130249023, 24.132999420166016, 23.854999542236328, 23.753000259399414, 23.841999053955078, 23.759000778198242, 22.75200080871582, 22.295000076293945, 22.163000106811523, 22.572999954223633, 22.868999481201172, 22.642000198364258, 22.38800048828125, 22.656999588012695, 22.43000030517578, 21.458999633789062, 22.020999908447266, 22.510000228881836, 22.618000030517578, 22.582000732421875, 22.506000518798828, 22.631999969482422, 22.679000854492188, 22.639999389648438, 22.490999221801758, 23.14900016784668, 23.45599937438965, 23.327999114990234, 23.243000030517578, 23.86199951171875, 24.423999786376953, 24.149999618530273, 24.429000854492188, 24.57200050354004, 24.086000442504883, 24.18899917602539, 24.117000579833984, 23.94499969482422, 24.06399917602539, 23.5, 23.22599983215332, 23.9060001373291, 24.152000427246094, 24.53700065612793, 24.312999725341797, 24.767000198364258, 25.301000595092773, 25.3439998626709, 25.10700035095215, 24.944000244140625, 25.16699981689453, 24.900999069213867, 24.780000686645508, 24.297000885009766, 23.434999465942383, 23.496000289916992, 23.10700035095215, 22.798999786376953, 22.764999389648438, 22.298999786376953, 22.280000686645508, 22.44499969482422, 22.22800064086914, 22.48699951171875, 22.389999389648438, 21.974000930786133, 22.15999984741211, 22.290000915527344, 21.886999130249023, 21.507999420166016, 22.454999923706055, 22.506999969482422, 22.274999618530273, 22.50200080871582, 22.79199981689453, 22.930999755859375, 22.979000091552734, 23.111000061035156, 22.847999572753906, 23.027999877929688, 23.327999114990234, 22.790000915527344, 23.038000106811523, 23.149999618530273, 22.173999786376953, 22.393999099731445, 22.445999145507812, 22.805999755859375, 23.200000762939453, 23.155000686645508, 22.910999298095703, 23.48699951171875, 24.22599983215332, 24.711000442504883, 24.31399917602539, 23.795000076293945, 23.895999908447266, 23.80699920654297, 22.67300033569336, 22.302000045776367, 22.395000457763672, 22.59600067138672, 22.711000442504883, 22.375, 22.475000381469727, 23.076000213623047, 23.19499969482422, 23.336000442504883, 23.518999099731445, 23.365999221801758, 23.844999313354492, 23.33799934387207, 23.60099983215332, 23.874000549316406, 23.990999221801758, 24.31100082397461, 24.55500030517578, 24.68600082397461, 23.996999740600586, 24.361000061035156, 25.534000396728516, 25.183000564575195, 25.204999923706055, 25.781999588012695,</t>
+          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [17.965999603271484, 18.06800079345703, 18.097000122070312, 18.31599998474121, 18.08799934387207, 17.860000610351562, 18.033000946044922, 17.926000595092773, 17.673999786376953, 17.92300033569336, 17.875, 18.01300048828125, 17.750999450683594, 17.770999908447266, 17.773000717163086, 18.05699920654297, 18.0, 17.402000427246094, 17.430999755859375, 17.95199966430664, 17.972000122070312, 17.639999389648438, 17.527999877929688, 17.569000244140625, 17.788999557495117, 17.665000915527344, 17.757999420166016, 17.572999954223633, 17.47800064086914, 17.600000381469727, 17.71500015258789, 18.131000518798828, 18.29199981689453, 18.30900001525879, 18.520999908447266, 18.868000030517578, 18.183000564575195, 17.826000213623047, 17.658000946044922, 16.386999130249023, 16.679000854492188, 17.128999710083008, 17.187000274658203, 17.341999053955078, 17.214000701904297, 17.000999450683594, 16.9060001373291, 16.729000091552734, 15.961000442504883, 14.456000328063965, 12.772000312805176, 12.468999862670898, 11.734999656677246, 12.097000122070312, 12.348999977111816, 13.225000381469727, 14.229000091552734, 14.836999893188477, 14.640000343322754, 14.498000144958496, 14.074000358581543, 14.097999572753906, 13.925999641418457, 14.595999717712402, 14.435999870300293, 15.111000061035156, 15.42199993133545, 15.147000312805176, 15.994999885559082, 15.479000091552734, 16.07200050354004, 15.446999549865723, 15.564000129699707, 15.237000465393066, 15.555999755859375, 14.817999839782715, 15.277000427246094, 15.347999572753906, 15.253999710083008, 15.201000213623047, 15.161999702453613, 15.15999984741211, 14.89799976348877, 14.86299991607666, 14.722000122070312, 15.057000160217285, 14.987000465393066, 15.562000274658203, 15.739999771118164, 15.63599967956543, 15.687000274658203, 15.663000106811523, 16.13599967956543, 17.04599952697754, 17.464000701904297, 17.892000198364258, 18.00200080871582, 17.334999084472656, 17.663999557495117, 17.565000534057617, 17.68600082397461, 17.895000457763672, 18.440000534057617, 18.76799964904785, 18.207000732421875, 17.92099952697754, 18.02400016784668, 17.44300079345703, 17.868000030517578, 17.77400016784668, 17.775999069213867, 17.868999481201172, 17.461999893188477, 17.378999710083008, 17.631999969482422, 17.756999969482422, 17.493000030517578, 17.832000732421875, 17.886999130249023, 18.051000595092773, 17.658000946044922, 17.882999420166016, 18.023000717163086, 17.979999542236328, 18.541000366210938, 18.132999420166016, 18.243999481201172, 18.503999710083008, 18.628000259399414, 19.08099937438965, 18.881999969482422, 18.982999801635742, 19.708999633789062, 19.451000213623047, 19.684999465942383, 19.496999740600586, 19.684999465942383, 20.124000549316406, 21.496999740600586, 23.08300018310547, 22.94499969482422, 22.808000564575195, 24.47599983215332, 24.266000747680664, 24.292999267578125, 23.34000015258789, 24.18899917602539, 24.389999389648438, 26.011999130249023, 26.87700080871582, 28.386999130249023, 27.533000946044922, 29.249000549316406, 26.03700065612793, 25.954999923706055, 27.694000244140625, 26.065000534057617, 27.64299964904785, 28.048999786376953, 27.315000534057617, 27.121999740600586, 26.707000732421875, 26.58799934387207, 26.253999710083008, 27.43000030517578, 27.010000228881836, 27.610000610351562, 28.437000274658203, 28.486000061035156, 27.249000549316406, 26.735000610351562, 26.576000213623047, 26.86400032043457, 26.954999923706055, 27.163000106811523, 26.73900032043457, 27.229000091552734, 27.34600067138672, 27.354999542236328, 26.985000610351562, 27.027999877929688, 24.298999786376953, 24.441999435424805, 23.013999938964844, 23.118000030517578, 23.017000198364258, 23.527999877929688, 24.3799991607666, 23.433000564575195, 24.19300079345703, 23.97100067138672, 24.50200080871582, 23.8700008392334, 23.847999572753906, 23.836999893188477, 25.069000244140625, 25.22599983215332, 24.086000442504883, 24.36400032043457, 24.19300079345703, 24.368999481201172, 24.656999588012695, 24.937000274658203, 25.19700050354004, 24.665000915527344, 24.62700080871582, 24.375999450683594, 24.525999069213867, 23.323999404907227, 23.339000701904297, 23.617000579833984, 24.006000518798828, 24.30500030517578, 23.86400032043457, 25.17099952697754, 25.645999908447266, 23.684999465942383, 24.445999145507812, 24.250999450683594, 24.290000915527344, 24.759000778198242, 24.785999298095703, 24.635000228881836, 24.433000564575195, 24.033000946044922, 24.347999572753906, 23.624000549316406, 23.29199981689453, 23.356000900268555, 22.55299949645996, 22.534000396728516, 24.033000946044922, 24.024999618530273, 24.086999893188477, 24.202999114990234, 24.740999221801758, 24.68400001525879, 23.93000030517578, 24.0310001373291, 24.031999588012695, 23.985000610351562, 24.58099937438965, 24.985000610351562, 26.100000381469727, 25.948999404907227, 26.277999877929688, 25.43400001525879, 25.823999404907227, 25.81100082397461, 26.459999084472656, 26.13800048828125, 26.488000869750977, 26.332000732421875, 27.284000396728516, 27.570999145507812, 26.972999572753906, 27.200000762939453, 24.582000732421875, 25.23900032043457, 25.384000778198242, 25.520000457763672, 25.746000289916992, 24.825000762939453, 25.27899932861328, 25.733999252319336, 25.82200050354004, 25.52400016784668, 25.454999923706055, 25.52899932861328, 25.375999450683594, 25.909000396728516, 26.899999618530273, 29.398000717163086, 26.384000778198242, 26.878000259399414, 26.222999572753906, 27.013999938964844, 27.56999969482422, 27.395999908447266, 27.073999404907227, 27.04199981689453, 27.322999954223633, 27.319000244140625, 27.31399917602539, 27.07699966430664, 27.25200080871582, 28.08300018310547, 27.68600082397461, 27.85700035095215, 27.636999130249023, 26.402000427246094, 26.64699935913086, 26.850000381469727, 26.35700035095215, 25.43400001525879, 25.256999969482422, 25.239999771118164, 26.148000717163086, 26.101999282836914, 26.16200065612793, 25.8799991607666, 26.253000259399414, 25.974000930786133, 26.030000686645508, 26.320999145507812, 26.29199981689453, 25.740999221801758, 25.200000762939453, 25.201000213623047, 25.02199935913086, 25.091999053955078, 24.746999740600586, 24.121000289916992, 24.517000198364258, 24.934999465942383, 24.76300048828125, 25.211999893188477, 25.232999801635742, 25.569000244140625, 25.31100082397461, 24.85300064086914, 25.41699981689453, 25.514999389648438, 25.95599937438965, 26.099000930786133, 25.83099937438965, 25.834999084472656, 26.565000534057617, 26.173999786376953, 26.07699966430664, 26.211000442504883, 26.41200065612793, 26.08099937438965, 26.05299949645996, 25.85300064086914, 26.94300079345703, 26.538999557495117, 26.50200080871582, 27.461999893188477, 27.461999893188477, 27.479000091552734, 27.656999588012695, 27.231000900268555, 27.04400062561035, 27.35300064086914, 28.260000228881836, 28.31399917602539, 28.007999420166016, 28.052000045776367, 27.472999572753906, 27.886999130249023, 28.03700065612793, 27.85300064086914, 27.91900062561035, 27.993000030517578, 28.08300018310547, 28.18600082397461, 27.459999084472656, 27.878999710083008, 28.000999450683594, 27.71500015258789, 27.985000610351562, 28.014999389648438, 28.131000518798828, 28.02400016784668, 27.679000854492188, 27.799999237060547, 25.8439998626709, 25.95800018310547, 26.014999389648438, 25.847999572753906, 26.107999801635742, 26.047000885009766, 26.082000732421875, 26.218000411987305, 25.871999740600586, 26.165000915527344, 26.075000762939453, 26.481000900268555, 26.15399932861328, 26.110000610351562, 25.966999053955078, 26.211000442504883, 26.216999053955078, 26.114999771118164, 26.246000289916992, 26.375, 25.777000427246094, 25.125999450683594, 24.976999282836914, 25.238000869750977, 25.364999771118164, 25.218000411987305, 25.295000076293945, 24.631999969482422, 24.856000900268555, 25.763999938964844, 25.527999877929688, 25.55699920654297, 25.56599998474121, 25.445999145507812, 25.277000427246094, 24.312000274658203, 23.2549991607666, 23.37700080871582, 23.474000930786133, 23.104999542236328, 23.76799964904785, 23.780000686645508, 23.648000717163086, 23.41200065612793, 23.219999313354492, 23.104999542236328, 23.64900016784668, 23.889999389648438, 23.770999908447266, 23.54599952697754, 24.059999465942383, 23.959999084472656, 23.959999084472656, 24.177000045776367, 23.875, 24.761999130249023, 24.333999633789062, 24.011999130249023, 24.132999420166016, 23.854999542236328, 23.753000259399414, 23.841999053955078, 23.759000778198242, 22.75200080871582, 22.295000076293945, 22.163000106811523, 22.572999954223633, 22.868999481201172, 22.642000198364258, 22.38800048828125, 22.656999588012695, 22.43000030517578, 21.458999633789062, 22.020999908447266, 22.510000228881836, 22.618000030517578, 22.582000732421875, 22.506000518798828, 22.631999969482422, 22.679000854492188, 22.639999389648438, 22.490999221801758, 23.14900016784668, 23.45599937438965, 23.327999114990234, 23.243000030517578, 23.86199951171875, 24.423999786376953, 24.149999618530273, 24.429000854492188, 24.57200050354004, 24.086000442504883, 24.18899917602539, 24.117000579833984, 23.94499969482422, 24.06399917602539, 23.5, 23.22599983215332, 23.9060001373291, 24.152000427246094, 24.53700065612793, 24.312999725341797, 24.767000198364258, 25.301000595092773, 25.3439998626709, 25.10700035095215, 24.944000244140625, 25.16699981689453, 24.900999069213867, 24.780000686645508, 24.297000885009766, 23.434999465942383, 23.496000289916992, 23.10700035095215, 22.798999786376953, 22.764999389648438, 22.298999786376953, 22.280000686645508, 22.44499969482422, 22.22800064086914, 22.48699951171875, 22.389999389648438, 21.974000930786133, 22.15999984741211, 22.290000915527344, 21.886999130249023, 21.507999420166016, 22.454999923706055, 22.506999969482422, 22.274999618530273, 22.50200080871582, 22.79199981689453, 22.930999755859375, 22.979000091552734, 23.111000061035156, 22.847999572753906, 23.027999877929688, 23.327999114990234, 22.790000915527344, 23.038000106811523, 23.149999618530273, 22.173999786376953, 22.393999099731445, 22.445999145507812, 22.805999755859375, 23.200000762939453, 23.155000686645508, 22.910999298095703, 23.48699951171875, 24.22599983215332, 24.711000442504883, 24.31399917602539, 23.795000076293945, 23.895999908447266, 23.80699920654297, 22.67300033569336, 22.302000045776367, 22.395000457763672, 22.59600067138672, 22.711000442504883, 22.375, 22.475000381469727, 23.076000213623047, 23.19499969482422, 23.336000442504883, 23.518999099731445, 23.365999221801758, 23.844999313354492, 23.33799934387207, 23.60099983215332, 23.874000549316406, 23.990999221801758, 24.31100082397461, 24.55500030517578</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -781,11 +781,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.0599975585938</v>
+        <v>82.58999633789062</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -795,73 +795,73 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>-26.9%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>47.5%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>49.4%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-17.5%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-13.4%</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-14.5%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>100.1%</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>13.6%</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>49.4%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>11.9%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-5.7%</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>8.9%</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>{'supply': ['1. 호르무즈 해협 리스크: 물리적 봉쇄 시 배럴당 $150 돌파 경고', '2. SPR 방출 한계: 미 전략비축유 보충 수요가 하방 가격 지지', '3. 러시아 생산 차질: 제재 강화로 인한 정유 시설 가동률 하락'], 'quant': ['1. $95 박스권 상단: 강력한 저항 구간으로 확인', '2. Open Interest 급증: 선물 시장내 대규모 투기 자금 유입 포착', '3. 유가-달러 상관관계: 달러 약세 전환 시 추가 상승 모멘텀'], 'qual': ['1. 중동 전면전 우려: 지정학적 프리미엄의 공격적 반영 구간', '2. 신재생 에너지 전환: 장기적 수요 감소 대비 단기 공급 부족 상충', '3. 사우디의 의지: 배럴당 $90 이상 사수하려는 OPEC의 단결력'], 'links': [{'t': 'Global Macro Report 2026', 'u': 'https://www.bloomberg.com/markets'}, {'t': 'Capital Flow Analytics', 'u': 'https://www.reuters.com/business'}]}</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>95.63299942016602</v>
+        <v>97.6150001525879</v>
       </c>
       <c r="Q4" t="n">
-        <v>74.54133294423421</v>
+        <v>80.83283316294352</v>
       </c>
       <c r="R4" t="n">
-        <v>66.66166655222575</v>
+        <v>69.88358325958252</v>
       </c>
       <c r="S4" t="n">
-        <v>66.36655839697107</v>
+        <v>67.03512984436829</v>
       </c>
       <c r="T4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="b">
         <v>1</v>
@@ -874,12 +874,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02'], 'prices': [61.18000030517578, 63.04999923706055, 63.27000045776367, 62.70000076293945, 59.61000061035156, 59.560001373291016, 59.040000915527344, 58.08000183105469, 58.22999954223633, 57.810001373291016, 58.52000045776367, 58.540000915527344, 58.34000015258789, 56.7400016784668, 55.59000015258789, 54.189998626708984, 53.13999938964844, 53.47999954223633, 53.33000183105469, 52.13999938964844, 51.560001373291016, 50.11000061035156, 49.61000061035156, 50.75, 50.95000076293945, 50.31999969482422, 49.56999969482422, 49.939998626708984, 51.16999816894531, 51.41999816894531, 52.04999923706055, 52.04999923706055, 53.290000915527344, 53.779998779296875, 53.380001068115234, 51.43000030517578, 49.900001525878906, 48.72999954223633, 47.09000015258789, 44.7599983215332, 46.75, 47.18000030517578, 46.779998779296875, 45.900001525878906, 41.279998779296875, 31.1299991607666, 34.36000061035156, 32.97999954223633, 31.5, 31.729999542236328, 28.700000762939453, 26.950000762939453, 20.3700008392334, 25.219999313354492, 22.43000030517578, 23.360000610351562, 24.010000228881836, 24.489999771118164, 22.600000381469727, 21.510000228881836, 20.09000015258789, 20.479999542236328, 20.309999465942383, 25.31999969482422, 28.34000015258789, 26.079999923706055, 23.6299991607666, 25.09000015258789, 22.760000228881836, 22.40999984741211, 20.110000610351562, 19.8700008392334, 19.8700008392334, 18.270000457763672, -37.630001068115234, 10.010000228881836, 13.779999732971191, 16.5, 16.940000534057617, 12.779999732971191, 12.34000015258789, 15.0600004196167, 18.84000015258789, 19.780000686645508, 20.389999389648438, 24.559999465942383, 23.989999771118164, 23.549999237060547, 24.739999771118164, 24.139999389648438, 25.780000686645508, 25.290000915527344, 27.559999465942383, 29.43000030517578, 31.81999969482422, 32.5, 33.4900016784668, 33.91999816894531, 33.25, 34.349998474121094, 32.810001373291016, 33.709999084472656, 35.4900016784668, 35.439998626708984, 36.810001373291016, 37.290000915527344, 37.40999984741211, 39.54999923706055, 38.189998626708984, 38.939998626708984, 39.599998474121094, 36.34000015258789, 36.2599983215332, 37.119998931884766, 38.380001068115234, 37.959999084472656, 38.84000015258789, 39.75, 40.459999084472656, 40.369998931884766, 38.0099983215332, 38.720001220703125, 38.4900016784668, 39.70000076293945, 39.27000045776367, 39.81999969482422, 40.650001525878906, 40.630001068115234, 40.619998931884766, 40.900001525878906, 39.619998931884766, 40.54999923706055, 40.099998474121094, 40.290000915527344, 41.20000076293945, 40.75, 40.59000015258789, 40.810001373291016, 41.959999084472656, 41.900001525878906, 41.06999969482422, 41.290000915527344, 41.599998474121094, 41.040000915527344, 41.27000045776367, 39.91999816894531, 40.27000045776367, 41.0099983215332, 41.70000076293945, 42.189998626708984, 41.95000076293945, 41.220001220703125, 41.939998626708984, 41.61000061035156, 42.66999816894531, 42.2400016784668, 42.0099983215332, 42.88999938964844, 42.88999938964844, 42.93000030517578, 42.58000183105469, 42.34000015258789, 42.619998931884766, 43.349998474121094, 43.38999938964844, 43.040000915527344, 42.970001220703125, 42.61000061035156, 42.7599983215332, 41.5099983215332, 41.369998931884766, 39.77000045776367, 36.7599983215332, 38.04999923706055, 37.29999923706055, 37.33000183105469, 37.2599983215332, 38.279998779296875, 40.15999984741211, 40.970001220703125, 41.11000061035156, 39.310001373291016, 39.599998474121094, 39.93000030517578, 40.310001373291016, 40.25, 40.599998474121094, 39.290000915527344, 40.220001220703125, 38.720001220703125, 37.04999923706055, 39.220001220703125, 40.66999816894531, 39.95000076293945, 41.189998626708984, 40.599998474121094, 39.43000030517578, 40.20000076293945, 41.040000915527344, 40.959999084472656, 40.880001068115234, 40.83000183105469, 41.459999084472656, 40.029998779296875, 40.63999938964844, 39.849998474121094, 38.560001373291016, 39.56999969482422, 37.38999938964844, 36.16999816894531, 35.790000915527344, 36.810001373291016, 37.65999984741211, 39.150001525878906, 38.790000915527344, 37.13999938964844, 40.290000915527344, 41.36000061035156, 41.45000076293945, 41.119998931884766, 40.130001068115234, 41.34000015258789, 41.43000030517578, 41.81999969482422, 41.7400016784668, 42.150001525878906, 43.060001373291016, 44.90999984741211, 45.709999084472656, 45.529998779296875, 45.34000015258789, 44.54999923706055, 45.279998779296875, 45.63999938964844, 46.2599983215332, 45.7599983215332, 45.599998474121094, 45.52000045776367, 46.779998779296875, 46.56999969482422, 46.9900016784668, 47.619998931884766, 47.81999969482422, 48.36000061035156, 49.099998474121094, 47.7400016784668, 47.02000045776367, 48.119998931884766, 48.22999954223633, 47.619998931884766, 48.0, 48.400001525878906, 48.52000045776367, 47.619998931884766, 49.93000030517578, 50.630001068115234, 50.83000183105469, 52.2400016784668, 52.25, 53.209999084472656, 52.90999984741211, 53.56999969482422, 52.36000061035156, 52.97999954223633, 53.2400016784668, 53.130001068115234, 52.27000045776367, 52.77000045776367, 52.61000061035156, 52.849998474121094, 52.34000015258789, 52.20000076293945, 53.54999923706055, 54.7599983215332, 55.689998626708984, 56.22999954223633, 56.849998474121094, 57.970001220703125, 58.36000061035156, 58.68000030517578, 58.2400016784668, 59.470001220703125, 60.04999923706055, 61.13999938964844, 60.52000045776367, 59.2400016784668, 61.4900016784668, 61.66999816894531, 63.220001220703125, 63.529998779296875, 61.5, 60.63999938964844, 59.75, 61.279998779296875, 63.83000183105469, 66.08999633789062, 65.05000305175781, 64.01000213623047, 64.44000244140625, 66.0199966430664, 65.61000061035156, 65.38999938964844, 64.80000305175781, 64.5999984741211, 60.0, 61.41999816894531, 61.54999923706055, 57.7599983215332, 61.18000030517578, 58.560001373291016, 60.970001220703125, 61.560001373291016, 60.54999923706055, 59.15999984741211, 61.45000076293945, 58.650001525878906, 59.33000183105469, 59.77000045776367, 59.599998474121094, 59.31999969482422, 59.70000076293945, 60.18000030517578, 63.150001525878906, 63.459999084472656, 63.130001068115234, 63.380001068115234, 62.439998626708984, 61.349998474121094, 61.43000030517578, 62.13999938964844, 61.90999984741211, 62.939998626708984, 63.86000061035156, 65.01000213623047, 63.58000183105469, 64.48999786376953, 65.69000244140625, 65.62999725341797, 64.70999908447266, 64.9000015258789, 64.91999816894531, 65.27999877929688, 66.08000183105469, 63.81999969482422, 65.37000274658203, 66.2699966430664, 65.48999786376953, 63.36000061035156, 62.04999923706055, 63.58000183105469, 66.05000305175781, 66.06999969482422, 66.20999908447266, 66.8499984741211, 66.31999969482422, 67.72000122070312, 68.83000183105469, 68.80999755859375, 69.62000274658203, 69.2300033569336, 70.05000305175781, 69.95999908447266, 70.29000091552734, 70.91000366210938, 70.87999725341797, 72.12000274658203, 72.1500015258789, 71.04000091552734, 71.63999938964844, 73.66000366210938, 73.05999755859375, 73.08000183105469, 73.30000305175781, 74.05000305175781, 72.91000366210938, 72.9800033569336, 73.47000122070312, 75.2300033569336, 75.16000366210938, 73.37000274658203, 72.19999694824219, 72.94000244140625, 74.55999755859375, 74.0999984741211, 75.25, 73.12999725341797, 71.6500015258789, 71.80999755859375, 66.41999816894531, 67.41999816894531, 70.30000305175781, 71.91000366210938, 72.06999969482422, 71.91000366210938, 71.6500015258789, 72.38999938964844, 73.62000274658203, 73.94999694824219, 71.26000213623047, 70.55999755859375, 68.1500015258789, 69.08999633789062, 68.27999877929688, 66.4800033569336, 68.29000091552734, 69.25, 69.08999633789062, 68.44000244140625, 67.29000091552734, 66.58999633789062, 65.45999908447266, 63.689998626708984, 62.31999969482422, 65.63999938964844, 67.54000091552734, 68.36000061035156, 67.41999816894531, 68.73999786376953, 69.20999908447266, 68.5, 68.58999633789062, 69.98999786376953, 69.29000091552734, 68.3499984741211, 69.30000305175781, 68.13999938964844, 69.72000122070312, 70.44999694824219, 70.45999908447266, 72.61000061035156, 72.61000061035156, 71.97000122070312, 70.29000091552734, 70.55999755859375, 72.2300033569336, 73.30000305175781, 73.9800033569336, 75.44999694824219, 75.29000091552734, 74.83000183105469, 75.02999877929688, 75.87999725341797, 77.62000274658203, 78.93000030517578, 77.43000030517578, 78.30000305175781, 79.3499984741211, 80.5199966430664, 80.63999938964844, 80.44000244140625, 81.30999755859375, 82.27999877929688, 82.44000244140625, 82.95999908447266, 83.87000274658203, 82.5, 83.76000213623047, 83.76000213623047, 84.6500015258789, 82.66000366210938, 82.80999755859375, 83.56999969482422, 84.05000305175781, 83.91000366210938, 80.86000061035156, 78.80999755859375, 81.2699966430664, 81.93000030517578, 84.1500015258789, 81.33999633789062, 81.58999633789062, 80.79000091552734, 80.87999725341797, 80.76000213623047, 78.36000061035156, 79.01000213623047, 76.0999984741211, 76.75, 78.5, 78.38999938964844, 68.1500015258789, 69.94999694824219, 66.18000030517578, 65.56999969482422, 66.5, 66.26000213623047, 69.48999786376953, 72.05000305175781, 72.36000061035156, 70.94000244140625, 71.66999816894531, 71.29000091552734, 70.7300033569336, 70.87000274658203, 72.37999725341797, 70.86000061035156, 68.2300033569336, 71.12000274658203, 72.76000213623047, 73.79000091552734, 75.56999969482422, 75.9800033569336, 76.55999755859375, 76.98999786376953, 75.20999908447266, 76.08000183105469, 76.98999786376953, 77.8499984741211, 79.45999908447266, 78.9000015258789, 78.2300033569336, 81.22000122070312, 82.63999938964844, 82.12000274658203, 83.81999969482422, 85.43000030517578, 86.95999908447266, 86.9000015258789, 85.13999938964844, 83.30999755859375, 85.5999984741211, 87.3499984741211, 86.61000061035156, 86.81999969482422, 88.1500015258789, 88.19999694824219, 88.26000213623047, 90.2699966430664, 92.30999755859375, 91.31999969482422, 89.36000061035156, 89.66000366210938, 89.87999725341797, 93.0999984741211, 95.45999908447266, 92.06999969482422, 93.66000366210938, 91.76000213623047, 91.06999969482422, 92.3499984741211, 92.0999984741211, 92.80999755859375, 91.58999633789062, 95.72000122070312, 103.41000366210938, 110.5999984741211, 107.66999816894531, 115.68000030517578, 119.4000015258789, 123.69999694824219, 108.69999694824219, 106.0199966430664, 109.33000183105469, 103.01000213623047, 96.44000244140625, 95.04000091552734, 102.9800033569336, 104.69999694824219, 112.12000274658203, 111.76000213623047, 114.93000030517578, 112.33999633789062, 113.9000015258789, 105.95999908447266, 104.23999786376953, 107.81999969482422, 100.27999877929688, 99.2699966430664, 103.27999877929688, 101.95999908447266, 96.2300033569336, 96.02999877929688, 98.26000213623047, 94.2900</t>
+          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [61.18000030517578, 63.04999923706055, 63.27000045776367, 62.70000076293945, 59.61000061035156, 59.560001373291016, 59.040000915527344, 58.08000183105469, 58.22999954223633, 57.810001373291016, 58.52000045776367, 58.540000915527344, 58.34000015258789, 56.7400016784668, 55.59000015258789, 54.189998626708984, 53.13999938964844, 53.47999954223633, 53.33000183105469, 52.13999938964844, 51.560001373291016, 50.11000061035156, 49.61000061035156, 50.75, 50.95000076293945, 50.31999969482422, 49.56999969482422, 49.939998626708984, 51.16999816894531, 51.41999816894531, 52.04999923706055, 52.04999923706055, 53.290000915527344, 53.779998779296875, 53.380001068115234, 51.43000030517578, 49.900001525878906, 48.72999954223633, 47.09000015258789, 44.7599983215332, 46.75, 47.18000030517578, 46.779998779296875, 45.900001525878906, 41.279998779296875, 31.1299991607666, 34.36000061035156, 32.97999954223633, 31.5, 31.729999542236328, 28.700000762939453, 26.950000762939453, 20.3700008392334, 25.219999313354492, 22.43000030517578, 23.360000610351562, 24.010000228881836, 24.489999771118164, 22.600000381469727, 21.510000228881836, 20.09000015258789, 20.479999542236328, 20.309999465942383, 25.31999969482422, 28.34000015258789, 26.079999923706055, 23.6299991607666, 25.09000015258789, 22.760000228881836, 22.40999984741211, 20.110000610351562, 19.8700008392334, 19.8700008392334, 18.270000457763672, -37.630001068115234, 10.010000228881836, 13.779999732971191, 16.5, 16.940000534057617, 12.779999732971191, 12.34000015258789, 15.0600004196167, 18.84000015258789, 19.780000686645508, 20.389999389648438, 24.559999465942383, 23.989999771118164, 23.549999237060547, 24.739999771118164, 24.139999389648438, 25.780000686645508, 25.290000915527344, 27.559999465942383, 29.43000030517578, 31.81999969482422, 32.5, 33.4900016784668, 33.91999816894531, 33.25, 34.349998474121094, 32.810001373291016, 33.709999084472656, 35.4900016784668, 35.439998626708984, 36.810001373291016, 37.290000915527344, 37.40999984741211, 39.54999923706055, 38.189998626708984, 38.939998626708984, 39.599998474121094, 36.34000015258789, 36.2599983215332, 37.119998931884766, 38.380001068115234, 37.959999084472656, 38.84000015258789, 39.75, 40.459999084472656, 40.369998931884766, 38.0099983215332, 38.720001220703125, 38.4900016784668, 39.70000076293945, 39.27000045776367, 39.81999969482422, 40.650001525878906, 40.630001068115234, 40.619998931884766, 40.900001525878906, 39.619998931884766, 40.54999923706055, 40.099998474121094, 40.290000915527344, 41.20000076293945, 40.75, 40.59000015258789, 40.810001373291016, 41.959999084472656, 41.900001525878906, 41.06999969482422, 41.290000915527344, 41.599998474121094, 41.040000915527344, 41.27000045776367, 39.91999816894531, 40.27000045776367, 41.0099983215332, 41.70000076293945, 42.189998626708984, 41.95000076293945, 41.220001220703125, 41.939998626708984, 41.61000061035156, 42.66999816894531, 42.2400016784668, 42.0099983215332, 42.88999938964844, 42.88999938964844, 42.93000030517578, 42.58000183105469, 42.34000015258789, 42.619998931884766, 43.349998474121094, 43.38999938964844, 43.040000915527344, 42.970001220703125, 42.61000061035156, 42.7599983215332, 41.5099983215332, 41.369998931884766, 39.77000045776367, 36.7599983215332, 38.04999923706055, 37.29999923706055, 37.33000183105469, 37.2599983215332, 38.279998779296875, 40.15999984741211, 40.970001220703125, 41.11000061035156, 39.310001373291016, 39.599998474121094, 39.93000030517578, 40.310001373291016, 40.25, 40.599998474121094, 39.290000915527344, 40.220001220703125, 38.720001220703125, 37.04999923706055, 39.220001220703125, 40.66999816894531, 39.95000076293945, 41.189998626708984, 40.599998474121094, 39.43000030517578, 40.20000076293945, 41.040000915527344, 40.959999084472656, 40.880001068115234, 40.83000183105469, 41.459999084472656, 40.029998779296875, 40.63999938964844, 39.849998474121094, 38.560001373291016, 39.56999969482422, 37.38999938964844, 36.16999816894531, 35.790000915527344, 36.810001373291016, 37.65999984741211, 39.150001525878906, 38.790000915527344, 37.13999938964844, 40.290000915527344, 41.36000061035156, 41.45000076293945, 41.119998931884766, 40.130001068115234, 41.34000015258789, 41.43000030517578, 41.81999969482422, 41.7400016784668, 42.150001525878906, 43.060001373291016, 44.90999984741211, 45.709999084472656, 45.529998779296875, 45.34000015258789, 44.54999923706055, 45.279998779296875, 45.63999938964844, 46.2599983215332, 45.7599983215332, 45.599998474121094, 45.52000045776367, 46.779998779296875, 46.56999969482422, 46.9900016784668, 47.619998931884766, 47.81999969482422, 48.36000061035156, 49.099998474121094, 47.7400016784668, 47.02000045776367, 48.119998931884766, 48.22999954223633, 47.619998931884766, 48.0, 48.400001525878906, 48.52000045776367, 47.619998931884766, 49.93000030517578, 50.630001068115234, 50.83000183105469, 52.2400016784668, 52.25, 53.209999084472656, 52.90999984741211, 53.56999969482422, 52.36000061035156, 52.97999954223633, 53.2400016784668, 53.130001068115234, 52.27000045776367, 52.77000045776367, 52.61000061035156, 52.849998474121094, 52.34000015258789, 52.20000076293945, 53.54999923706055, 54.7599983215332, 55.689998626708984, 56.22999954223633, 56.849998474121094, 57.970001220703125, 58.36000061035156, 58.68000030517578, 58.2400016784668, 59.470001220703125, 60.04999923706055, 61.13999938964844, 60.52000045776367, 59.2400016784668, 61.4900016784668, 61.66999816894531, 63.220001220703125, 63.529998779296875, 61.5, 60.63999938964844, 59.75, 61.279998779296875, 63.83000183105469, 66.08999633789062, 65.05000305175781, 64.01000213623047, 64.44000244140625, 66.0199966430664, 65.61000061035156, 65.38999938964844, 64.80000305175781, 64.5999984741211, 60.0, 61.41999816894531, 61.54999923706055, 57.7599983215332, 61.18000030517578, 58.560001373291016, 60.970001220703125, 61.560001373291016, 60.54999923706055, 59.15999984741211, 61.45000076293945, 58.650001525878906, 59.33000183105469, 59.77000045776367, 59.599998474121094, 59.31999969482422, 59.70000076293945, 60.18000030517578, 63.150001525878906, 63.459999084472656, 63.130001068115234, 63.380001068115234, 62.439998626708984, 61.349998474121094, 61.43000030517578, 62.13999938964844, 61.90999984741211, 62.939998626708984, 63.86000061035156, 65.01000213623047, 63.58000183105469, 64.48999786376953, 65.69000244140625, 65.62999725341797, 64.70999908447266, 64.9000015258789, 64.91999816894531, 65.27999877929688, 66.08000183105469, 63.81999969482422, 65.37000274658203, 66.2699966430664, 65.48999786376953, 63.36000061035156, 62.04999923706055, 63.58000183105469, 66.05000305175781, 66.06999969482422, 66.20999908447266, 66.8499984741211, 66.31999969482422, 67.72000122070312, 68.83000183105469, 68.80999755859375, 69.62000274658203, 69.2300033569336, 70.05000305175781, 69.95999908447266, 70.29000091552734, 70.91000366210938, 70.87999725341797, 72.12000274658203, 72.1500015258789, 71.04000091552734, 71.63999938964844, 73.66000366210938, 73.05999755859375, 73.08000183105469, 73.30000305175781, 74.05000305175781, 72.91000366210938, 72.9800033569336, 73.47000122070312, 75.2300033569336, 75.16000366210938, 73.37000274658203, 72.19999694824219, 72.94000244140625, 74.55999755859375, 74.0999984741211, 75.25, 73.12999725341797, 71.6500015258789, 71.80999755859375, 66.41999816894531, 67.41999816894531, 70.30000305175781, 71.91000366210938, 72.06999969482422, 71.91000366210938, 71.6500015258789, 72.38999938964844, 73.62000274658203, 73.94999694824219, 71.26000213623047, 70.55999755859375, 68.1500015258789, 69.08999633789062, 68.27999877929688, 66.4800033569336, 68.29000091552734, 69.25, 69.08999633789062, 68.44000244140625, 67.29000091552734, 66.58999633789062, 65.45999908447266, 63.689998626708984, 62.31999969482422, 65.63999938964844, 67.54000091552734, 68.36000061035156, 67.41999816894531, 68.73999786376953, 69.20999908447266, 68.5, 68.58999633789062, 69.98999786376953, 69.29000091552734, 68.3499984741211, 69.30000305175781, 68.13999938964844, 69.72000122070312, 70.44999694824219, 70.45999908447266, 72.61000061035156, 72.61000061035156, 71.97000122070312, 70.29000091552734, 70.55999755859375, 72.2300033569336, 73.30000305175781, 73.9800033569336, 75.44999694824219, 75.29000091552734, 74.83000183105469, 75.02999877929688, 75.87999725341797, 77.62000274658203, 78.93000030517578, 77.43000030517578, 78.30000305175781, 79.3499984741211, 80.5199966430664, 80.63999938964844, 80.44000244140625, 81.30999755859375, 82.27999877929688, 82.44000244140625, 82.95999908447266, 83.87000274658203, 82.5, 83.76000213623047, 83.76000213623047, 84.6500015258789, 82.66000366210938, 82.80999755859375, 83.56999969482422, 84.05000305175781, 83.91000366210938, 80.86000061035156, 78.80999755859375, 81.2699966430664, 81.93000030517578, 84.1500015258789, 81.33999633789062, 81.58999633789062, 80.79000091552734, 80.87999725341797, 80.76000213623047, 78.36000061035156, 79.01000213623047, 76.0999984741211, 76.75, 78.5, 78.38999938964844, 68.1500015258789, 69.94999694824219, 66.18000030517578, 65.56999969482422, 66.5, 66.26000213623047, 69.48999786376953, 72.05000305175781, 72.36000061035156, 70.94000244140625, 71.66999816894531, 71.29000091552734, 70.7300033569336, 70.87000274658203, 72.37999725341797, 70.86000061035156, 68.2300033569336, 71.12000274658203, 72.76000213623047, 73.79000091552734, 75.56999969482422, 75.9800033569336, 76.55999755859375, 76.98999786376953, 75.20999908447266, 76.08000183105469, 76.98999786376953, 77.8499984741211, 79.45999908447266, 78.9000015258789, 78.2300033569336, 81.22000122070312, 82.63999938964844, 82.12000274658203, 83.81999969482422, 85.43000030517578, 86.95999908447266, 86.9000015258789, 85.13999938964844, 83.30999755859375, 85.5999984741211, 87.3499984741211, 86.61000061035156, 86.81999969482422, 88.1500015258789, 88.19999694824219, 88.26000213623047, 90.2699966430664, 92.30999755859375, 91.31999969482422, 89.36000061035156, 89.66000366210938, 89.87999725341797, 93.0999984741211, 95.45999908447266, 92.06999969482422, 93.66000366210938, 91.76000213623047, 91.06999969482422, 92.3499984741211, 92.0999984741211, 92.80999755859375, 91.58999633789062, 95.72000122070312, 103.41000366210938, 110.5999984741211, 107.66999816894531, 115.68000030517578, 119.4000015258789, 123.69999694824219, 108.69999694824219, 106.0199966430664, 109.33000183105469, 103.01000213623047, 96.44000244140625, 95.04000091552734, 102.9800033569336, 104.69999694824219, 112.12000274658203, 111.76000213623047, 114.93000030517578, 112.33999633789062, 113.9000015258789, 105.95999908447266, 104.23999786376953, 107.81999969482422, 1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.806999921798706</v>
+        <v>2.674000024795532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -904,70 +904,70 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-62.4%</t>
+          <t>-64.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-34.3%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-5.1%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-6.7%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-5.4%</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-34.3%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.4%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-3.1%</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-4.4%</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-2.8%</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>{'supply': ['1. 유럽 재고 수준: 난방 시즌 종료 후 재고 축축 속도 둔화', '2. LNG 수출 터미널 가동: 미국의 수출 물량 증가가 가격 하방 압력', '3. 환경 규제 강화: 메탄 배출권 비용 상승에 따른 생산 단가 증가'], 'quant': ['1. $2.0 지지선 붕괴 위험: 역사적 저점 부근에서의 지지력 테스트', '2. 계절적 변동성: 하절기 전력 수요 전까지의 비수기 패턴', '3. 가격 콘탱코 심화: 원월물 대비 근월물 약세 지속'], 'qual': ['1. 날씨 변동성: 예상보다 따뜻한 기온으로 인한 수요 급감', '2. 에너지 자립도 강조: EU의 러시아산 가스 퇴출 가속화', '3. 신재생 대체 가속: 태양광/풍력 발전에 의한 가스 발전 점유율 위축'], 'links': [{'t': 'Global Macro Report 2026', 'u': 'https://www.bloomberg.com/markets'}, {'t': 'Capital Flow Analytics', 'u': 'https://www.reuters.com/business'}]}</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.027900016307831</v>
+        <v>2.812250018119812</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.446933337052663</v>
+        <v>3.310450009504954</v>
       </c>
       <c r="R5" t="n">
-        <v>3.769033326705297</v>
+        <v>3.72731665968895</v>
       </c>
       <c r="S5" t="n">
-        <v>3.584470779090733</v>
+        <v>3.543227273148376</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -983,12 +983,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02'], 'prices': [2.121999979019165, 2.130000114440918, 2.134999990463257, 2.1619999408721924, 2.1410000324249268, 2.1659998893737793, 2.2019999027252197, 2.181999921798706, 2.187000036239624, 2.119999885559082, 2.0769999027252197, 2.003000020980835, 1.8949999809265137, 1.9049999713897705, 1.9259999990463257, 1.8930000066757202, 1.9019999504089355, 1.934000015258789, 1.8769999742507935, 1.8289999961853027, 1.840999960899353, 1.819000005722046, 1.871999979019165, 1.8609999418258667, 1.8619999885559082, 1.8580000400543213, 1.7660000324249268, 1.7879999876022339, 1.843999981880188, 1.8259999752044678, 1.8370000123977661, 1.9809999465942383, 1.9550000429153442, 1.9199999570846558, 1.9049999713897705, 1.8270000219345093, 1.847000002861023, 1.8209999799728394, 1.7519999742507935, 1.684000015258789, 1.75600004196167, 1.7999999523162842, 1.8270000219345093, 1.7719999551773071, 1.7079999446868896, 1.777999997138977, 1.9359999895095825, 1.878000020980835, 1.840999960899353, 1.86899995803833, 1.815000057220459, 1.7289999723434448, 1.6039999723434448, 1.6540000438690186, 1.6039999723434448, 1.6019999980926514, 1.652999997138977, 1.659000039100647, 1.6369999647140503, 1.6339999437332153, 1.690000057220459, 1.6399999856948853, 1.5870000123977661, 1.5520000457763672, 1.621000051498413, 1.7309999465942383, 1.8519999980926514, 1.7829999923706055, 1.7330000400543213, 1.7239999771118164, 1.649999976158142, 1.5980000495910645, 1.6859999895095825, 1.753000020980835, 1.9240000247955322, 1.8209999799728394, 1.9390000104904175, 1.815000057220459, 1.746000051498413, 1.819000005722046, 1.7940000295639038, 1.86899995803833, 1.9490000009536743, 1.8899999856948853, 1.9930000305175781, 2.134000062942505, 1.944000005722046, 1.8940000534057617, 1.8229999542236328, 1.8259999752044678, 1.7200000286102295, 1.6160000562667847, 1.680999994277954, 1.6460000276565552, 1.7829999923706055, 1.8300000429153442, 1.7710000276565552, 1.7100000381469727, 1.7309999465942383, 1.7929999828338623, 1.722000002861023, 1.8270000219345093, 1.8489999771118164, 1.7740000486373901, 1.7769999504089355, 1.8209999799728394, 1.8220000267028809, 1.781999945640564, 1.7890000343322754, 1.7669999599456787, 1.7799999713897705, 1.812999963760376, 1.7309999465942383, 1.6690000295639038, 1.6139999628067017, 1.6380000114440918, 1.6380000114440918, 1.6690000295639038, 1.6640000343322754, 1.6369999647140503, 1.597000002861023, 1.4819999933242798, 1.4950000047683716, 1.7089999914169312, 1.7510000467300415, 1.6710000038146973, 1.7339999675750732, 1.8300000429153442, 1.8760000467300415, 1.8240000009536743, 1.7790000438690186, 1.8049999475479126, 1.7389999628067017, 1.746000051498413, 1.777999997138977, 1.7230000495910645, 1.718000054359436, 1.6410000324249268, 1.6749999523162842, 1.680999994277954, 1.784999966621399, 1.8079999685287476, 1.7339999675750732, 1.7999999523162842, 1.8539999723434448, 1.8289999961853027, 1.7990000247955322, 2.1010000705718994, 2.193000078201294, 2.190999984741211, 2.1649999618530273, 2.23799991607666, 2.1530001163482666, 2.1710000038146973, 2.1519999504089355, 2.181999921798706, 2.3559999465942383, 2.3389999866485596, 2.4170000553131104, 2.4260001182556152, 2.3519999980926514, 2.447999954223633, 2.513000011444092, 2.489000082015991, 2.4609999656677246, 2.5789999961853027, 2.6570000648498535, 2.630000114440918, 2.5269999504089355, 2.4860000610351562, 2.486999988555908, 2.5880000591278076, 2.4000000953674316, 2.4059998989105225, 2.322999954223633, 2.2690000534057617, 2.309999942779541, 2.361999988555908, 2.2669999599456787, 2.0420000553131104, 2.0480000972747803, 1.8350000381469727, 1.8339999914169312, 2.125, 2.247999906539917, 2.1389999389648438, 2.1010000705718994, 2.561000108718872, 2.5269999504089355, 2.5269999504089355, 2.437999963760376, 2.615000009536743, 2.5199999809265137, 2.6059999465942383, 2.627000093460083, 2.740999937057495, 2.88100004196167, 2.8550000190734863, 2.635999917984009, 2.7750000953674316, 2.7730000019073486, 2.7950000762939453, 2.9130001068115234, 3.0230000019073486, 3.006999969482422, 2.9709999561309814, 3.0239999294281006, 3.0190000534057617, 2.996000051498413, 3.3010001182556152, 3.3540000915527344, 3.24399995803833, 3.059000015258789, 3.0460000038146973, 2.941999912261963, 2.888000011444092, 2.8589999675750732, 2.9489998817443848, 3.0309998989105225, 2.9760000705718994, 2.994999885559082, 2.697000026702881, 2.691999912261963, 2.7119998931884766, 2.5920000076293945, 2.6500000953674316, 2.7109999656677246, 2.7750000953674316, 2.8959999084472656, 2.8429999351501465, 2.881999969482422, 2.880000114440918, 2.7799999713897705, 2.506999969482422, 2.575000047683716, 2.4059998989105225, 2.3989999294281006, 2.441999912261963, 2.552999973297119, 2.5910000801086426, 2.681999921798706, 2.681999921798706, 2.677000045776367, 2.635999917984009, 2.700000047683716, 2.7049999237060547, 2.7799999713897705, 2.6080000400543213, 2.5179998874664307, 2.305000066757202, 2.4670000076293945, 2.421999931335449, 2.5390000343322754, 2.5810000896453857, 2.7019999027252197, 2.7160000801086426, 2.7290000915527344, 2.700000047683716, 2.746999979019165, 2.753000020980835, 2.7269999980926514, 2.6659998893737793, 2.736999988555908, 2.5460000038146973, 2.5390000343322754, 2.490999937057495, 2.446000099182129, 2.6019999980926514, 2.6559998989105225, 2.759999990463257, 2.6640000343322754, 2.563999891281128, 2.8499999046325684, 2.8450000286102295, 2.7890000343322754, 2.934999942779541, 2.86299991607666, 2.881999969482422, 2.8350000381469727, 2.9110000133514404, 2.868000030517578, 2.9119999408721924, 3.128999948501587, 3.2190001010894775, 3.0820000171661377, 3.069000005722046, 2.953000068664551, 2.878999948501587, 2.8540000915527344, 2.7769999504089355, 2.7709999084472656, 2.7769999504089355, 2.8389999866485596, 2.815999984741211, 2.746000051498413, 2.7009999752044678, 2.6640000343322754, 2.6619999408721924, 2.691999912261963, 2.6679999828338623, 2.5999999046325684, 2.4839999675750732, 2.562000036239624, 2.5280001163482666, 2.4809999465942383, 2.5350000858306885, 2.5820000171661377, 2.507999897003174, 2.5179998874664307, 2.569999933242798, 2.556999921798706, 2.5859999656677246, 2.622999906539917, 2.6080000400543213, 2.6389999389648438, 2.510999917984009, 2.4560000896453857, 2.5199999809265137, 2.5220000743865967, 2.5260000228881836, 2.561000108718872, 2.61899995803833, 2.618000030517578, 2.6579999923706055, 2.680000066757202, 2.749000072479248, 2.7269999980926514, 2.691999912261963, 2.749000072479248, 2.7300000190734863, 2.7899999618530273, 2.872999906539917, 2.924999952316284, 2.9110000133514404, 2.930999994277954, 2.9660000801086426, 2.9670000076293945, 2.937999963760376, 2.927999973297119, 2.9579999446868896, 2.931999921798706, 2.9549999237060547, 2.9690001010894775, 2.9730000495910645, 2.9609999656677246, 3.1089999675750732, 3.01200008392334, 2.9639999866485596, 2.924999952316284, 2.9059998989105225, 2.885999917984009, 2.9130001068115234, 2.9839999675750732, 2.9579999446868896, 2.9860000610351562, 3.1040000915527344, 3.075000047683716, 3.0409998893737793, 3.0969998836517334, 3.069999933242798, 3.128000020980835, 3.128999948501587, 3.1489999294281006, 3.2960000038146973, 3.3519999980926514, 3.240000009536743, 3.250999927520752, 3.253000020980835, 3.2149999141693115, 3.190999984741211, 3.257999897003174, 3.3329999446868896, 3.4179999828338623, 3.496000051498413, 3.617000102996826, 3.630000114440918, 3.6500000953674316, 3.6610000133514404, 3.700000047683716, 3.63700008392334, 3.5959999561309814, 3.687999963760376, 3.6740000247955322, 3.749000072479248, 3.696000099182129, 3.6600000858306885, 3.614000082015991, 3.6740000247955322, 3.7790000438690186, 3.875999927520752, 3.9590001106262207, 4.002999782562256, 4.059999942779541, 4.1020002365112305, 3.9709999561309814, 4.044000148773193, 4.059000015258789, 3.9140000343322754, 3.934999942779541, 4.0269999504089355, 4.1579999923706055, 4.139999866485596, 4.139999866485596, 4.059999942779541, 4.089000225067139, 4.059000015258789, 3.933000087738037, 3.8610000610351562, 3.946000099182129, 3.8369998931884766, 3.8519999980926514, 3.8299999237060547, 3.8510000705718994, 3.944999933242798, 3.8959999084472656, 3.8970000743865967, 4.184000015258789, 4.369999885559082, 4.304999828338623, 4.376999855041504, 4.614999771118164, 4.640999794006348, 4.711999893188477, 4.567999839782715, 4.914000034332275, 5.031000137329102, 4.938000202178955, 5.230999946594238, 5.260000228881836, 5.460000038146973, 5.335000038146973, 5.105000019073486, 4.985000133514404, 4.804999828338623, 4.804999828338623, 4.97599983215332, 5.139999866485596, 5.705999851226807, 5.841000080108643, 5.4770002365112305, 5.867000102996826, 5.61899995803833, 5.765999794006348, 6.311999797821045, 5.675000190734863, 5.677000045776367, 5.565000057220459, 5.34499979019165, 5.505000114440918, 5.590000152587891, 5.686999797821045, 5.409999847412109, 4.988999843597412, 5.0879998207092285, 5.170000076293945, 5.114999771118164, 5.28000020980835, 5.8979997634887695, 5.881999969482422, 6.202000141143799, 5.7820000648498535, 5.426000118255615, 5.185999870300293, 5.541999816894531, 5.670000076293945, 5.716000080108643, 5.515999794006348, 5.427000045776367, 4.979000091552734, 4.880000114440918, 5.14900016784668, 4.790999889373779, 5.017000198364258, 5.177000045776367, 4.815999984741211, 4.9019999504089355, 5.065000057220459, 4.789000034332275, 4.9670000076293945, 5.067999839782715, 5.447000026702881, 4.854000091552734, 4.566999912261963, 4.257999897003174, 4.056000232696533, 4.131999969482422, 3.6570000648498535, 3.7079999446868896, 3.815000057220459, 3.813999891281128, 3.924999952316284, 3.7939999103546143, 3.746999979019165, 3.802000045776367, 3.7660000324249268, 3.690000057220459, 3.8340001106262207, 3.86899995803833, 3.9760000705718994, 3.7309999465942383, 4.059999942779541, 4.054999828338623, 4.02400016784668, 3.561000108718872, 3.7300000190734863, 3.815000057220459, 3.7170000076293945, 3.881999969482422, 3.812000036239624, 3.9159998893737793, 4.078999996185303, 4.249000072479248, 4.85699987411499, 4.269999980926514, 4.26200008392334, 4.2829999923706055, 4.031000137329102, 3.802000045776367, 3.999000072479248, 4.0269999504089355, 4.052999973297119, 4.2769999504089355, 6.264999866485596, 4.638999938964844, 4.874000072479248, 4.750999927520752, 5.500999927520752, 4.888000011444092, 4.572000026702881, 4.23199987411499, 4.248000144958496, 4.008999824523926, 3.9590001106262207, 3.940999984741211, 4.195000171661377, 4.306000232696533, 4.7170000076293945, 4.486000061035156, 4.431000232696533, 4.498000144958496, 4.623000144958496, 4.567999839782715, 4.46999979019165, 4.4019999504089355, 4.572999954223633, 4.76200008392334, 4.7220001220703125, 5.015999794006348, 4.833000183105469, 4.5269999504089355, 4.52600002</t>
+          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [2.121999979019165, 2.130000114440918, 2.134999990463257, 2.1619999408721924, 2.1410000324249268, 2.1659998893737793, 2.2019999027252197, 2.181999921798706, 2.187000036239624, 2.119999885559082, 2.0769999027252197, 2.003000020980835, 1.8949999809265137, 1.9049999713897705, 1.9259999990463257, 1.8930000066757202, 1.9019999504089355, 1.934000015258789, 1.8769999742507935, 1.8289999961853027, 1.840999960899353, 1.819000005722046, 1.871999979019165, 1.8609999418258667, 1.8619999885559082, 1.8580000400543213, 1.7660000324249268, 1.7879999876022339, 1.843999981880188, 1.8259999752044678, 1.8370000123977661, 1.9809999465942383, 1.9550000429153442, 1.9199999570846558, 1.9049999713897705, 1.8270000219345093, 1.847000002861023, 1.8209999799728394, 1.7519999742507935, 1.684000015258789, 1.75600004196167, 1.7999999523162842, 1.8270000219345093, 1.7719999551773071, 1.7079999446868896, 1.777999997138977, 1.9359999895095825, 1.878000020980835, 1.840999960899353, 1.86899995803833, 1.815000057220459, 1.7289999723434448, 1.6039999723434448, 1.6540000438690186, 1.6039999723434448, 1.6019999980926514, 1.652999997138977, 1.659000039100647, 1.6369999647140503, 1.6339999437332153, 1.690000057220459, 1.6399999856948853, 1.5870000123977661, 1.5520000457763672, 1.621000051498413, 1.7309999465942383, 1.8519999980926514, 1.7829999923706055, 1.7330000400543213, 1.7239999771118164, 1.649999976158142, 1.5980000495910645, 1.6859999895095825, 1.753000020980835, 1.9240000247955322, 1.8209999799728394, 1.9390000104904175, 1.815000057220459, 1.746000051498413, 1.819000005722046, 1.7940000295639038, 1.86899995803833, 1.9490000009536743, 1.8899999856948853, 1.9930000305175781, 2.134000062942505, 1.944000005722046, 1.8940000534057617, 1.8229999542236328, 1.8259999752044678, 1.7200000286102295, 1.6160000562667847, 1.680999994277954, 1.6460000276565552, 1.7829999923706055, 1.8300000429153442, 1.7710000276565552, 1.7100000381469727, 1.7309999465942383, 1.7929999828338623, 1.722000002861023, 1.8270000219345093, 1.8489999771118164, 1.7740000486373901, 1.7769999504089355, 1.8209999799728394, 1.8220000267028809, 1.781999945640564, 1.7890000343322754, 1.7669999599456787, 1.7799999713897705, 1.812999963760376, 1.7309999465942383, 1.6690000295639038, 1.6139999628067017, 1.6380000114440918, 1.6380000114440918, 1.6690000295639038, 1.6640000343322754, 1.6369999647140503, 1.597000002861023, 1.4819999933242798, 1.4950000047683716, 1.7089999914169312, 1.7510000467300415, 1.6710000038146973, 1.7339999675750732, 1.8300000429153442, 1.8760000467300415, 1.8240000009536743, 1.7790000438690186, 1.8049999475479126, 1.7389999628067017, 1.746000051498413, 1.777999997138977, 1.7230000495910645, 1.718000054359436, 1.6410000324249268, 1.6749999523162842, 1.680999994277954, 1.784999966621399, 1.8079999685287476, 1.7339999675750732, 1.7999999523162842, 1.8539999723434448, 1.8289999961853027, 1.7990000247955322, 2.1010000705718994, 2.193000078201294, 2.190999984741211, 2.1649999618530273, 2.23799991607666, 2.1530001163482666, 2.1710000038146973, 2.1519999504089355, 2.181999921798706, 2.3559999465942383, 2.3389999866485596, 2.4170000553131104, 2.4260001182556152, 2.3519999980926514, 2.447999954223633, 2.513000011444092, 2.489000082015991, 2.4609999656677246, 2.5789999961853027, 2.6570000648498535, 2.630000114440918, 2.5269999504089355, 2.4860000610351562, 2.486999988555908, 2.5880000591278076, 2.4000000953674316, 2.4059998989105225, 2.322999954223633, 2.2690000534057617, 2.309999942779541, 2.361999988555908, 2.2669999599456787, 2.0420000553131104, 2.0480000972747803, 1.8350000381469727, 1.8339999914169312, 2.125, 2.247999906539917, 2.1389999389648438, 2.1010000705718994, 2.561000108718872, 2.5269999504089355, 2.5269999504089355, 2.437999963760376, 2.615000009536743, 2.5199999809265137, 2.6059999465942383, 2.627000093460083, 2.740999937057495, 2.88100004196167, 2.8550000190734863, 2.635999917984009, 2.7750000953674316, 2.7730000019073486, 2.7950000762939453, 2.9130001068115234, 3.0230000019073486, 3.006999969482422, 2.9709999561309814, 3.0239999294281006, 3.0190000534057617, 2.996000051498413, 3.3010001182556152, 3.3540000915527344, 3.24399995803833, 3.059000015258789, 3.0460000038146973, 2.941999912261963, 2.888000011444092, 2.8589999675750732, 2.9489998817443848, 3.0309998989105225, 2.9760000705718994, 2.994999885559082, 2.697000026702881, 2.691999912261963, 2.7119998931884766, 2.5920000076293945, 2.6500000953674316, 2.7109999656677246, 2.7750000953674316, 2.8959999084472656, 2.8429999351501465, 2.881999969482422, 2.880000114440918, 2.7799999713897705, 2.506999969482422, 2.575000047683716, 2.4059998989105225, 2.3989999294281006, 2.441999912261963, 2.552999973297119, 2.5910000801086426, 2.681999921798706, 2.681999921798706, 2.677000045776367, 2.635999917984009, 2.700000047683716, 2.7049999237060547, 2.7799999713897705, 2.6080000400543213, 2.5179998874664307, 2.305000066757202, 2.4670000076293945, 2.421999931335449, 2.5390000343322754, 2.5810000896453857, 2.7019999027252197, 2.7160000801086426, 2.7290000915527344, 2.700000047683716, 2.746999979019165, 2.753000020980835, 2.7269999980926514, 2.6659998893737793, 2.736999988555908, 2.5460000038146973, 2.5390000343322754, 2.490999937057495, 2.446000099182129, 2.6019999980926514, 2.6559998989105225, 2.759999990463257, 2.6640000343322754, 2.563999891281128, 2.8499999046325684, 2.8450000286102295, 2.7890000343322754, 2.934999942779541, 2.86299991607666, 2.881999969482422, 2.8350000381469727, 2.9110000133514404, 2.868000030517578, 2.9119999408721924, 3.128999948501587, 3.2190001010894775, 3.0820000171661377, 3.069000005722046, 2.953000068664551, 2.878999948501587, 2.8540000915527344, 2.7769999504089355, 2.7709999084472656, 2.7769999504089355, 2.8389999866485596, 2.815999984741211, 2.746000051498413, 2.7009999752044678, 2.6640000343322754, 2.6619999408721924, 2.691999912261963, 2.6679999828338623, 2.5999999046325684, 2.4839999675750732, 2.562000036239624, 2.5280001163482666, 2.4809999465942383, 2.5350000858306885, 2.5820000171661377, 2.507999897003174, 2.5179998874664307, 2.569999933242798, 2.556999921798706, 2.5859999656677246, 2.622999906539917, 2.6080000400543213, 2.6389999389648438, 2.510999917984009, 2.4560000896453857, 2.5199999809265137, 2.5220000743865967, 2.5260000228881836, 2.561000108718872, 2.61899995803833, 2.618000030517578, 2.6579999923706055, 2.680000066757202, 2.749000072479248, 2.7269999980926514, 2.691999912261963, 2.749000072479248, 2.7300000190734863, 2.7899999618530273, 2.872999906539917, 2.924999952316284, 2.9110000133514404, 2.930999994277954, 2.9660000801086426, 2.9670000076293945, 2.937999963760376, 2.927999973297119, 2.9579999446868896, 2.931999921798706, 2.9549999237060547, 2.9690001010894775, 2.9730000495910645, 2.9609999656677246, 3.1089999675750732, 3.01200008392334, 2.9639999866485596, 2.924999952316284, 2.9059998989105225, 2.885999917984009, 2.9130001068115234, 2.9839999675750732, 2.9579999446868896, 2.9860000610351562, 3.1040000915527344, 3.075000047683716, 3.0409998893737793, 3.0969998836517334, 3.069999933242798, 3.128000020980835, 3.128999948501587, 3.1489999294281006, 3.2960000038146973, 3.3519999980926514, 3.240000009536743, 3.250999927520752, 3.253000020980835, 3.2149999141693115, 3.190999984741211, 3.257999897003174, 3.3329999446868896, 3.4179999828338623, 3.496000051498413, 3.617000102996826, 3.630000114440918, 3.6500000953674316, 3.6610000133514404, 3.700000047683716, 3.63700008392334, 3.5959999561309814, 3.687999963760376, 3.6740000247955322, 3.749000072479248, 3.696000099182129, 3.6600000858306885, 3.614000082015991, 3.6740000247955322, 3.7790000438690186, 3.875999927520752, 3.9590001106262207, 4.002999782562256, 4.059999942779541, 4.1020002365112305, 3.9709999561309814, 4.044000148773193, 4.059000015258789, 3.9140000343322754, 3.934999942779541, 4.0269999504089355, 4.1579999923706055, 4.139999866485596, 4.139999866485596, 4.059999942779541, 4.089000225067139, 4.059000015258789, 3.933000087738037, 3.8610000610351562, 3.946000099182129, 3.8369998931884766, 3.8519999980926514, 3.8299999237060547, 3.8510000705718994, 3.944999933242798, 3.8959999084472656, 3.8970000743865967, 4.184000015258789, 4.369999885559082, 4.304999828338623, 4.376999855041504, 4.614999771118164, 4.640999794006348, 4.711999893188477, 4.567999839782715, 4.914000034332275, 5.031000137329102, 4.938000202178955, 5.230999946594238, 5.260000228881836, 5.460000038146973, 5.335000038146973, 5.105000019073486, 4.985000133514404, 4.804999828338623, 4.804999828338623, 4.97599983215332, 5.139999866485596, 5.705999851226807, 5.841000080108643, 5.4770002365112305, 5.867000102996826, 5.61899995803833, 5.765999794006348, 6.311999797821045, 5.675000190734863, 5.677000045776367, 5.565000057220459, 5.34499979019165, 5.505000114440918, 5.590000152587891, 5.686999797821045, 5.409999847412109, 4.988999843597412, 5.0879998207092285, 5.170000076293945, 5.114999771118164, 5.28000020980835, 5.8979997634887695, 5.881999969482422, 6.202000141143799, 5.7820000648498535, 5.426000118255615, 5.185999870300293, 5.541999816894531, 5.670000076293945, 5.716000080108643, 5.515999794006348, 5.427000045776367, 4.979000091552734, 4.880000114440918, 5.14900016784668, 4.790999889373779, 5.017000198364258, 5.177000045776367, 4.815999984741211, 4.9019999504089355, 5.065000057220459, 4.789000034332275, 4.9670000076293945, 5.067999839782715, 5.447000026702881, 4.854000091552734, 4.566999912261963, 4.257999897003174, 4.056000232696533, 4.131999969482422, 3.6570000648498535, 3.7079999446868896, 3.815000057220459, 3.813999891281128, 3.924999952316284, 3.7939999103546143, 3.746999979019165, 3.802000045776367, 3.7660000324249268, 3.690000057220459, 3.8340001106262207, 3.86899995803833, 3.9760000705718994, 3.7309999465942383, 4.059999942779541, 4.054999828338623, 4.02400016784668, 3.561000108718872, 3.7300000190734863, 3.815000057220459, 3.7170000076293945, 3.881999969482422, 3.812000036239624, 3.9159998893737793, 4.078999996185303, 4.249000072479248, 4.85699987411499, 4.269999980926514, 4.26200008392334, 4.2829999923706055, 4.031000137329102, 3.802000045776367, 3.999000072479248, 4.0269999504089355, 4.052999973297119, 4.2769999504089355, 6.264999866485596, 4.638999938964844, 4.874000072479248, 4.750999927520752, 5.500999927520752, 4.888000011444092, 4.572000026702881, 4.23199987411499, 4.248000144958496, 4.008999824523926, 3.9590001106262207, 3.940999984741211, 4.195000171661377, 4.306000232696533, 4.7170000076293945, 4.486000061035156, 4.431000232696533, 4.498000144958496, 4.623000144958496, 4.567999839782715, 4.46999979019165, 4.401</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -999,11 +999,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.68149995803833</v>
+        <v>6.114500045776367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1038,27 +1038,27 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1067,22 +1067,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>5.618299984931946</v>
+        <v>5.685150003433227</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.783458280563354</v>
+        <v>5.784674962361653</v>
       </c>
       <c r="R6" t="n">
-        <v>5.493679134051005</v>
+        <v>5.568054135640462</v>
       </c>
       <c r="S6" t="n">
-        <v>5.036818165283699</v>
+        <v>5.087461024135738</v>
       </c>
       <c r="T6" t="b">
         <v>1</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02'], 'prices': [2.8329999446868896, 2.7985000610351562, 2.80049991607666, 2.803999900817871, 2.819000005722046, 2.810499906539917, 2.81850004196167, 2.8615000247955322, 2.875999927520752, 2.869999885559082, 2.8519999980926514, 2.8494999408721924, 2.7985000610351562, 2.7669999599456787, 2.7260000705718994, 2.685499906539917, 2.5964999198913574, 2.5794999599456787, 2.553499937057495, 2.5234999656677246, 2.5199999809265137, 2.513000011444092, 2.547499895095825, 2.5789999961853027, 2.5985000133514404, 2.559000015258789, 2.557499885559082, 2.5885000228881836, 2.6059999465942383, 2.619499921798706, 2.6054999828338623, 2.609999895095825, 2.612499952316284, 2.5950000286102295, 2.618000030517578, 2.5924999713897705, 2.5964999198913574, 2.5764999389648438, 2.571500062942505, 2.5460000038146973, 2.6010000705718994, 2.5794999599456787, 2.5929999351501465, 2.5824999809265137, 2.572999954223633, 2.5239999294281006, 2.5339999198913574, 2.51200008392334, 2.4809999465942383, 2.4739999771118164, 2.3984999656677246, 2.315500020980835, 2.1605000495910645, 2.200000047683716, 2.190500020980835, 2.119499921798706, 2.197499990463257, 2.2339999675750732, 2.2079999446868896, 2.197000026702881, 2.1619999408721924, 2.240000009536743, 2.191999912261963, 2.2330000400543213, 2.2100000381469727, 2.234999895095825, 2.2885000705718994, 2.2780001163482666, 2.2774999141693115, 2.320499897003174, 2.3469998836517334, 2.3125, 2.304500102996826, 2.3534998893737793, 2.3345000743865967, 2.2669999599456787, 2.317500114440918, 2.3239998817443848, 2.3480000495910645, 2.381999969482422, 2.378999948501587, 2.374500036239624, 2.3540000915527344, 2.31850004196167, 2.3239998817443848, 2.3410000801086426, 2.3524999618530273, 2.385499954223633, 2.4084999561309814, 2.381999969482422, 2.3605000972747803, 2.3489999771118164, 2.3510000705718994, 2.3334999084472656, 2.4049999713897705, 2.4230000972747803, 2.4674999713897705, 2.4519999027252197, 2.4089999198913574, 2.438499927520752, 2.4024999141693115, 2.4130001068115234, 2.426500082015991, 2.4744999408721924, 2.494499921798706, 2.496500015258789, 2.493000030517578, 2.556999921798706, 2.569999933242798, 2.6005001068115234, 2.6570000648498535, 2.5864999294281006, 2.6015000343322754, 2.56850004196167, 2.565999984741211, 2.5920000076293945, 2.5910000801086426, 2.615000009536743, 2.6554999351501465, 2.6600000858306885, 2.6505000591278076, 2.6624999046325684, 2.671999931335449, 2.679500102996826, 2.7135000228881836, 2.7170000076293945, 2.7335000038146973, 2.7660000324249268, 2.7874999046325684, 2.814500093460083, 2.828000068664551, 2.88700008392334, 2.941999912261963, 2.9159998893737793, 2.870500087738037, 2.885999917984009, 2.887500047683716, 2.8984999656677246, 2.940999984741211, 2.9084999561309814, 2.924499988555908, 2.881999969482422, 2.888000011444092, 2.9049999713897705, 2.9054999351501465, 2.9045000076293945, 2.8589999675750732, 2.9079999923706055, 2.8894999027252197, 2.9114999771118164, 2.9054999351501465, 2.7904999256134033, 2.8585000038146973, 2.871999979019165, 2.88700008392334, 2.803999900817871, 2.8559999465942383, 2.8980000019073486, 2.9709999561309814, 3.0190000534057617, 2.9700000286102295, 2.9135000705718994, 2.922499895095825, 2.930999994277954, 2.9595000743865967, 2.9649999141693115, 2.994999885559082, 3.0409998893737793, 3.009500026702881, 3.003000020980835, 2.9579999446868896, 3.0464999675750732, 3.012500047683716, 3.0399999618530273, 2.986999988555908, 3.0339999198913574, 3.066499948501587, 3.062999963760376, 3.058000087738037, 3.066499948501587, 3.1135001182556152, 3.0295000076293945, 3.059000015258789, 2.993499994277954, 2.9690001010894775, 2.9730000495910645, 2.989500045776367, 2.9835000038146973, 3.0285000801086426, 2.8635001182556152, 2.9784998893737793, 2.9649999141693115, 2.9655001163482666, 3.0344998836517334, 3.0420000553131104, 3.0794999599456787, 3.061000108718872, 3.0425000190734863, 3.047499895095825, 3.0829999446868896, 3.065000057220459, 3.0810000896453857, 3.1435000896453857, 3.194499969482422, 3.1500000953674316, 3.125499963760376, 3.0885000228881836, 3.0899999141693115, 3.056999921798706, 3.052000045776367, 3.0434999465942383, 3.073499917984009, 3.0869998931884766, 3.1010000705718994, 3.1045000553131104, 3.1489999294281006, 3.1514999866485596, 3.1505000591278076, 3.128999948501587, 3.1429998874664307, 3.17549991607666, 3.2200000286102295, 3.196500062942505, 3.197999954223633, 3.2035000324249268, 3.2934999465942383, 3.259500026702881, 3.299999952316284, 3.312000036239624, 3.3994998931884766, 3.4205000400543213, 3.4679999351501465, 3.4749999046325684, 3.4790000915527344, 3.5139999389648438, 3.508500099182129, 3.49399995803833, 3.507999897003174, 3.570499897003174, 3.5239999294281006, 3.5220000743865967, 3.5380001068115234, 3.553999900817871, 3.5969998836517334, 3.628499984741211, 3.572999954223633, 3.5179998874664307, 3.552000045776367, 3.559999942779541, 3.569999933242798, 3.552999973297119, 3.5429999828338623, 3.5139999389648438, 3.552999973297119, 3.640500068664551, 3.6500000953674316, 3.695499897003174, 3.6735000610351562, 3.563999891281128, 3.6050000190734863, 3.617000102996826, 3.6679999828338623, 3.6029999256134033, 3.635999917984009, 3.6475000381469727, 3.6554999351501465, 3.635499954223633, 3.640500068664551, 3.628000020980835, 3.571500062942505, 3.5829999446868896, 3.573499917984009, 3.562000036239624, 3.5390000343322754, 3.5785000324249268, 3.565999984741211, 3.6389999389648438, 3.678999900817871, 3.7335000038146973, 3.7855000495910645, 3.7874999046325684, 3.802000045776367, 3.8480000495910645, 3.8359999656677246, 3.9165000915527344, 4.090000152587891, 4.152500152587891, 4.1875, 4.301000118255615, 4.265999794006348, 4.0945000648498535, 4.119500160217285, 4.231500148773193, 4.1529998779296875, 3.990999937057495, 4.086999893188477, 4.103499889373779, 4.019499778747559, 4.041999816894531, 4.14300012588501, 4.145500183105469, 4.146500110626221, 4.078999996185303, 4.127999782562256, 4.117000102996826, 4.123499870300293, 4.14900016784668, 4.0879998207092285, 4.071499824523926, 3.984999895095825, 4.078499794006348, 4.043000221252441, 3.9830000400543213, 4.002999782562256, 4.003499984741211, 4.14900016784668, 4.126500129699707, 4.064000129699707, 4.103499889373779, 4.05049991607666, 4.03000020980835, 4.043000221252441, 4.139999866485596, 4.230500221252441, 4.179999828338623, 4.25, 4.223999977111816, 4.286499977111816, 4.2804999351501465, 4.3429999351501465, 4.447999954223633, 4.743000030517578, 4.5370001792907715, 4.493000030517578, 4.479000091552734, 4.543000221252441, 4.535999774932861, 4.539000034332275, 4.61899995803833, 4.765999794006348, 4.733500003814697, 4.778500080108643, 4.752500057220459, 4.70550012588501, 4.664000034332275, 4.721499919891357, 4.735499858856201, 4.5894999504089355, 4.581999778747559, 4.495999813079834, 4.541500091552734, 4.521999835968018, 4.5329999923706055, 4.666500091552734, 4.682499885559082, 4.6620001792907715, 4.599999904632568, 4.471499919891357, 4.537499904632568, 4.534999847412109, 4.563000202178955, 4.536499977111816, 4.489999771118164, 4.541500091552734, 4.5320000648498535, 4.340000152587891, 4.392499923706055, 4.184500217437744, 4.162499904632568, 4.1875, 4.234499931335449, 4.330999851226807, 4.311500072479248, 4.298999786376953, 4.2779998779296875, 4.276500225067139, 4.296500205993652, 4.242000102996826, 4.2820000648498535, 4.257999897003174, 4.328999996185303, 4.271500110626221, 4.352499961853027, 4.322999954223633, 4.314499855041504, 4.2769999504089355, 4.333000183105469, 4.332499980926514, 4.2104997634887695, 4.273499965667725, 4.28249979019165, 4.3480000495910645, 4.406499862670898, 4.589000225067139, 4.546000003814697, 4.479000091552734, 4.519999980926514, 4.480500221252441, 4.432000160217285, 4.382999897003174, 4.329999923706055, 4.3454999923706055, 4.3454999923706055, 4.2870001792907715, 4.351500034332275, 4.363999843597412, 4.355999946594238, 4.38700008392334, 4.322000026702881, 4.199999809265137, 4.116000175476074, 4.03849983215332, 4.134500026702881, 4.234499931335449, 4.255000114440918, 4.264999866485596, 4.245999813079834, 4.316500186920166, 4.361000061035156, 4.360000133514404, 4.263000011444092, 4.289999961853027, 4.325500011444092, 4.277500152587891, 4.23199987411499, 4.2835001945495605, 4.447999954223633, 4.363500118255615, 4.317999839782715, 4.403500080108643, 4.278500080108643, 4.245500087738037, 4.117000102996826, 4.127999782562256, 4.252500057220459, 4.230999946594238, 4.287499904632568, 4.293499946594238, 4.244999885559082, 4.199999809265137, 4.090000152587891, 4.19350004196167, 4.246500015258789, 4.202000141143799, 4.1570000648498535, 4.250999927520752, 4.2829999923706055, 4.374499797821045, 4.328999996185303, 4.520500183105469, 4.631499767303467, 4.734000205993652, 4.730500221252441, 4.714000225067139, 4.75600004196167, 4.58650016784668, 4.526000022888184, 4.551499843597412, 4.486499786376953, 4.38700008392334, 4.4375, 4.375500202178955, 4.4019999504089355, 4.374000072479248, 4.326000213623047, 4.326000213623047, 4.348999977111816, 4.40500020980835, 4.380000114440918, 4.328000068664551, 4.4045000076293945, 4.45550012588501, 4.4070000648498535, 4.358500003814697, 4.2729997634887695, 4.309999942779541, 4.4085001945495605, 4.395500183105469, 4.423500061035156, 4.458000183105469, 4.281499862670898, 4.336999893188477, 4.2779998779296875, 4.247499942779541, 4.298999786376953, 4.266499996185303, 4.336999893188477, 4.3379998207092285, 4.390999794006348, 4.329999923706055, 4.2829999923706055, 4.28000020980835, 4.254000186920166, 4.179500102996826, 4.30049991607666, 4.290999889373779, 4.288000106811523, 4.3379998207092285, 4.389500141143799, 4.38700008392334, 4.465000152587891, 4.420000076293945, 4.4019999504089355, 4.384500026702881, 4.454999923706055, 4.4145002365112305, 4.466000080108643, 4.4045000076293945, 4.3480000495910645, 4.4029998779296875, 4.3445000648498535, 4.420499801635742, 4.564000129699707, 4.533999919891357, 4.411499977111816, 4.375999927520752, 4.462500095367432, 4.576499938964844, 4.512499809265137, 4.4029998779296875, 4.442999839782715, 4.504499912261963, 4.413000106811523, 4.302999973297119, 4.317999839782715, 4.428999900817871, 4.491000175476074, 4.4664998054504395, 4.483500003814697, 4.46150016784668, 4.459499835968018, 4.600500106811523, 4.65749979019165, 4.505000114440918, 4.507500171661377, 4.531499862670898, 4.540500164031982, 4.525000095367432, 4.519499778747559, 4.510000228881836, 4.481500148773193, 4.453999996185303, 4.4720001220703125, 4.444499969482422, 4.58650016784668, 4.6554999351501465, 4.771500110626221, 4.928999900817871, 4.7220001220703125, 4.700500011444092, 4.564000129699707, 4.643499851226807, 4.616000175476074, 4.512499809265137, 4.501500129699707, 4.5879998207092285, 4.690499782562256, 4.7305</t>
+          <t xml:space="preserve">{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [2.8329999446868896, 2.7985000610351562, 2.80049991607666, 2.803999900817871, 2.819000005722046, 2.810499906539917, 2.81850004196167, 2.8615000247955322, 2.875999927520752, 2.869999885559082, 2.8519999980926514, 2.8494999408721924, 2.7985000610351562, 2.7669999599456787, 2.7260000705718994, 2.685499906539917, 2.5964999198913574, 2.5794999599456787, 2.553499937057495, 2.5234999656677246, 2.5199999809265137, 2.513000011444092, 2.547499895095825, 2.5789999961853027, 2.5985000133514404, 2.559000015258789, 2.557499885559082, 2.5885000228881836, 2.6059999465942383, 2.619499921798706, 2.6054999828338623, 2.609999895095825, 2.612499952316284, 2.5950000286102295, 2.618000030517578, 2.5924999713897705, 2.5964999198913574, 2.5764999389648438, 2.571500062942505, 2.5460000038146973, 2.6010000705718994, 2.5794999599456787, 2.5929999351501465, 2.5824999809265137, 2.572999954223633, 2.5239999294281006, 2.5339999198913574, 2.51200008392334, 2.4809999465942383, 2.4739999771118164, 2.3984999656677246, 2.315500020980835, 2.1605000495910645, 2.200000047683716, 2.190500020980835, 2.119499921798706, 2.197499990463257, 2.2339999675750732, 2.2079999446868896, 2.197000026702881, 2.1619999408721924, 2.240000009536743, 2.191999912261963, 2.2330000400543213, 2.2100000381469727, 2.234999895095825, 2.2885000705718994, 2.2780001163482666, 2.2774999141693115, 2.320499897003174, 2.3469998836517334, 2.3125, 2.304500102996826, 2.3534998893737793, 2.3345000743865967, 2.2669999599456787, 2.317500114440918, 2.3239998817443848, 2.3480000495910645, 2.381999969482422, 2.378999948501587, 2.374500036239624, 2.3540000915527344, 2.31850004196167, 2.3239998817443848, 2.3410000801086426, 2.3524999618530273, 2.385499954223633, 2.4084999561309814, 2.381999969482422, 2.3605000972747803, 2.3489999771118164, 2.3510000705718994, 2.3334999084472656, 2.4049999713897705, 2.4230000972747803, 2.4674999713897705, 2.4519999027252197, 2.4089999198913574, 2.438499927520752, 2.4024999141693115, 2.4130001068115234, 2.426500082015991, 2.4744999408721924, 2.494499921798706, 2.496500015258789, 2.493000030517578, 2.556999921798706, 2.569999933242798, 2.6005001068115234, 2.6570000648498535, 2.5864999294281006, 2.6015000343322754, 2.56850004196167, 2.565999984741211, 2.5920000076293945, 2.5910000801086426, 2.615000009536743, 2.6554999351501465, 2.6600000858306885, 2.6505000591278076, 2.6624999046325684, 2.671999931335449, 2.679500102996826, 2.7135000228881836, 2.7170000076293945, 2.7335000038146973, 2.7660000324249268, 2.7874999046325684, 2.814500093460083, 2.828000068664551, 2.88700008392334, 2.941999912261963, 2.9159998893737793, 2.870500087738037, 2.885999917984009, 2.887500047683716, 2.8984999656677246, 2.940999984741211, 2.9084999561309814, 2.924499988555908, 2.881999969482422, 2.888000011444092, 2.9049999713897705, 2.9054999351501465, 2.9045000076293945, 2.8589999675750732, 2.9079999923706055, 2.8894999027252197, 2.9114999771118164, 2.9054999351501465, 2.7904999256134033, 2.8585000038146973, 2.871999979019165, 2.88700008392334, 2.803999900817871, 2.8559999465942383, 2.8980000019073486, 2.9709999561309814, 3.0190000534057617, 2.9700000286102295, 2.9135000705718994, 2.922499895095825, 2.930999994277954, 2.9595000743865967, 2.9649999141693115, 2.994999885559082, 3.0409998893737793, 3.009500026702881, 3.003000020980835, 2.9579999446868896, 3.0464999675750732, 3.012500047683716, 3.0399999618530273, 2.986999988555908, 3.0339999198913574, 3.066499948501587, 3.062999963760376, 3.058000087738037, 3.066499948501587, 3.1135001182556152, 3.0295000076293945, 3.059000015258789, 2.993499994277954, 2.9690001010894775, 2.9730000495910645, 2.989500045776367, 2.9835000038146973, 3.0285000801086426, 2.8635001182556152, 2.9784998893737793, 2.9649999141693115, 2.9655001163482666, 3.0344998836517334, 3.0420000553131104, 3.0794999599456787, 3.061000108718872, 3.0425000190734863, 3.047499895095825, 3.0829999446868896, 3.065000057220459, 3.0810000896453857, 3.1435000896453857, 3.194499969482422, 3.1500000953674316, 3.125499963760376, 3.0885000228881836, 3.0899999141693115, 3.056999921798706, 3.052000045776367, 3.0434999465942383, 3.073499917984009, 3.0869998931884766, 3.1010000705718994, 3.1045000553131104, 3.1489999294281006, 3.1514999866485596, 3.1505000591278076, 3.128999948501587, 3.1429998874664307, 3.17549991607666, 3.2200000286102295, 3.196500062942505, 3.197999954223633, 3.2035000324249268, 3.2934999465942383, 3.259500026702881, 3.299999952316284, 3.312000036239624, 3.3994998931884766, 3.4205000400543213, 3.4679999351501465, 3.4749999046325684, 3.4790000915527344, 3.5139999389648438, 3.508500099182129, 3.49399995803833, 3.507999897003174, 3.570499897003174, 3.5239999294281006, 3.5220000743865967, 3.5380001068115234, 3.553999900817871, 3.5969998836517334, 3.628499984741211, 3.572999954223633, 3.5179998874664307, 3.552000045776367, 3.559999942779541, 3.569999933242798, 3.552999973297119, 3.5429999828338623, 3.5139999389648438, 3.552999973297119, 3.640500068664551, 3.6500000953674316, 3.695499897003174, 3.6735000610351562, 3.563999891281128, 3.6050000190734863, 3.617000102996826, 3.6679999828338623, 3.6029999256134033, 3.635999917984009, 3.6475000381469727, 3.6554999351501465, 3.635499954223633, 3.640500068664551, 3.628000020980835, 3.571500062942505, 3.5829999446868896, 3.573499917984009, 3.562000036239624, 3.5390000343322754, 3.5785000324249268, 3.565999984741211, 3.6389999389648438, 3.678999900817871, 3.7335000038146973, 3.7855000495910645, 3.7874999046325684, 3.802000045776367, 3.8480000495910645, 3.8359999656677246, 3.9165000915527344, 4.090000152587891, 4.152500152587891, 4.1875, 4.301000118255615, 4.265999794006348, 4.0945000648498535, 4.119500160217285, 4.231500148773193, 4.1529998779296875, 3.990999937057495, 4.086999893188477, 4.103499889373779, 4.019499778747559, 4.041999816894531, 4.14300012588501, 4.145500183105469, 4.146500110626221, 4.078999996185303, 4.127999782562256, 4.117000102996826, 4.123499870300293, 4.14900016784668, 4.0879998207092285, 4.071499824523926, 3.984999895095825, 4.078499794006348, 4.043000221252441, 3.9830000400543213, 4.002999782562256, 4.003499984741211, 4.14900016784668, 4.126500129699707, 4.064000129699707, 4.103499889373779, 4.05049991607666, 4.03000020980835, 4.043000221252441, 4.139999866485596, 4.230500221252441, 4.179999828338623, 4.25, 4.223999977111816, 4.286499977111816, 4.2804999351501465, 4.3429999351501465, 4.447999954223633, 4.743000030517578, 4.5370001792907715, 4.493000030517578, 4.479000091552734, 4.543000221252441, 4.535999774932861, 4.539000034332275, 4.61899995803833, 4.765999794006348, 4.733500003814697, 4.778500080108643, 4.752500057220459, 4.70550012588501, 4.664000034332275, 4.721499919891357, 4.735499858856201, 4.5894999504089355, 4.581999778747559, 4.495999813079834, 4.541500091552734, 4.521999835968018, 4.5329999923706055, 4.666500091552734, 4.682499885559082, 4.6620001792907715, 4.599999904632568, 4.471499919891357, 4.537499904632568, 4.534999847412109, 4.563000202178955, 4.536499977111816, 4.489999771118164, 4.541500091552734, 4.5320000648498535, 4.340000152587891, 4.392499923706055, 4.184500217437744, 4.162499904632568, 4.1875, 4.234499931335449, 4.330999851226807, 4.311500072479248, 4.298999786376953, 4.2779998779296875, 4.276500225067139, 4.296500205993652, 4.242000102996826, 4.2820000648498535, 4.257999897003174, 4.328999996185303, 4.271500110626221, 4.352499961853027, 4.322999954223633, 4.314499855041504, 4.2769999504089355, 4.333000183105469, 4.332499980926514, 4.2104997634887695, 4.273499965667725, 4.28249979019165, 4.3480000495910645, 4.406499862670898, 4.589000225067139, 4.546000003814697, 4.479000091552734, 4.519999980926514, 4.480500221252441, 4.432000160217285, 4.382999897003174, 4.329999923706055, 4.3454999923706055, 4.3454999923706055, 4.2870001792907715, 4.351500034332275, 4.363999843597412, 4.355999946594238, 4.38700008392334, 4.322000026702881, 4.199999809265137, 4.116000175476074, 4.03849983215332, 4.134500026702881, 4.234499931335449, 4.255000114440918, 4.264999866485596, 4.245999813079834, 4.316500186920166, 4.361000061035156, 4.360000133514404, 4.263000011444092, 4.289999961853027, 4.325500011444092, 4.277500152587891, 4.23199987411499, 4.2835001945495605, 4.447999954223633, 4.363500118255615, 4.317999839782715, 4.403500080108643, 4.278500080108643, 4.245500087738037, 4.117000102996826, 4.127999782562256, 4.252500057220459, 4.230999946594238, 4.287499904632568, 4.293499946594238, 4.244999885559082, 4.199999809265137, 4.090000152587891, 4.19350004196167, 4.246500015258789, 4.202000141143799, 4.1570000648498535, 4.250999927520752, 4.2829999923706055, 4.374499797821045, 4.328999996185303, 4.520500183105469, 4.631499767303467, 4.734000205993652, 4.730500221252441, 4.714000225067139, 4.75600004196167, 4.58650016784668, 4.526000022888184, 4.551499843597412, 4.486499786376953, 4.38700008392334, 4.4375, 4.375500202178955, 4.4019999504089355, 4.374000072479248, 4.326000213623047, 4.326000213623047, 4.348999977111816, 4.40500020980835, 4.380000114440918, 4.328000068664551, 4.4045000076293945, 4.45550012588501, 4.4070000648498535, 4.358500003814697, 4.2729997634887695, 4.309999942779541, 4.4085001945495605, 4.395500183105469, 4.423500061035156, 4.458000183105469, 4.281499862670898, 4.336999893188477, 4.2779998779296875, 4.247499942779541, 4.298999786376953, 4.266499996185303, 4.336999893188477, 4.3379998207092285, 4.390999794006348, 4.329999923706055, 4.2829999923706055, 4.28000020980835, 4.254000186920166, 4.179500102996826, 4.30049991607666, 4.290999889373779, 4.288000106811523, 4.3379998207092285, 4.389500141143799, 4.38700008392334, 4.465000152587891, 4.420000076293945, 4.4019999504089355, 4.384500026702881, 4.454999923706055, 4.4145002365112305, 4.466000080108643, 4.4045000076293945, 4.3480000495910645, 4.4029998779296875, 4.3445000648498535, 4.420499801635742, 4.564000129699707, 4.533999919891357, 4.411499977111816, 4.375999927520752, 4.462500095367432, 4.576499938964844, 4.512499809265137, 4.4029998779296875, 4.442999839782715, 4.504499912261963, 4.413000106811523, 4.302999973297119, 4.317999839782715, 4.428999900817871, 4.491000175476074, 4.4664998054504395, 4.483500003814697, 4.46150016784668, 4.459499835968018, 4.600500106811523, 4.65749979019165, 4.505000114440918, 4.507500171661377, 4.531499862670898, 4.540500164031982, 4.525000095367432, 4.519499778747559, 4.510000228881836, 4.481500148773193, 4.453999996185303, 4.4720001220703125, 4.444499969482422, 4.58650016784668, 4.6554999351501465, 4.771500110626221, 4.928999900817871, 4.7220001220703125, 4.700500011444092, </t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.313000202178955</v>
+        <v>4.245999813079834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.285949993133545</v>
+        <v>4.327749991416932</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.198649986584981</v>
+        <v>4.215983327229818</v>
       </c>
       <c r="R7" t="n">
-        <v>4.146183333794276</v>
+        <v>4.170541663964589</v>
       </c>
       <c r="S7" t="n">
-        <v>4.262561683530931</v>
+        <v>4.250538956035268</v>
       </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>1</v>
@@ -1197,16 +1197,16 @@
         <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02'], 'prices': [1.8819999694824219, 1.7879999876022339, 1.8109999895095825, 1.8270000219345093, 1.8739999532699585, 1.8580000400543213, 1.8250000476837158, 1.8480000495910645, 1.8179999589920044, 1.7879999876022339, 1.809000015258789, 1.8359999656677246, 1.7690000534057617, 1.7690000534057617, 1.7400000095367432, 1.680999994277954, 1.6050000190734863, 1.6410000324249268, 1.593999981880188, 1.5579999685287476, 1.5199999809265137, 1.5199999809265137, 1.6030000448226929, 1.6490000486373901, 1.6440000534057617, 1.5779999494552612, 1.5470000505447388, 1.590000033378601, 1.6299999952316284, 1.6169999837875366, 1.5880000591278076, 1.555999994277954, 1.5700000524520874, 1.524999976158142, 1.4709999561309814, 1.3769999742507935, 1.3300000429153442, 1.309999942779541, 1.2990000247955322, 1.1269999742507935, 1.0880000591278076, 1.0099999904632568, 0.9919999837875366, 0.9259999990463257, 0.7059999704360962, 0.49900001287460327, 0.7480000257492065, 0.8199999928474426, 0.8489999771118164, 0.9509999752044678, 0.7279999852180481, 0.996999979019165, 1.2660000324249268, 1.11899995803833, 0.9380000233650208, 0.7639999985694885, 0.8159999847412109, 0.8579999804496765, 0.8109999895095825, 0.7490000128746033, 0.6700000166893005, 0.6980000138282776, 0.6349999904632568, 0.6269999742507935, 0.5870000123977661, 0.6759999990463257, 0.7360000014305115, 0.7639999985694885, 0.7289999723434448, 0.7490000128746033, 0.7519999742507935, 0.6380000114440918, 0.609000027179718, 0.6539999842643738, 0.6259999871253967, 0.5709999799728394, 0.6190000176429749, 0.6129999756813049, 0.5960000157356262, 0.656000018119812, 0.6100000143051147, 0.6269999742507935, 0.621999979019165, 0.6420000195503235, 0.6370000243186951, 0.6570000052452087, 0.7110000252723694, 0.6309999823570251, 0.6819999814033508, 0.7260000109672546, 0.6779999732971191, 0.6489999890327454, 0.6190000176429749, 0.6399999856948853, 0.7440000176429749, 0.7110000252723694, 0.6800000071525574, 0.6769999861717224, 0.6570000052452087, 0.6980000138282776, 0.6800000071525574, 0.7049999833106995, 0.6480000019073486, 0.6620000004768372, 0.6800000071525574, 0.7609999775886536, 0.8199999928474426, 0.9039999842643738, 0.8840000033378601, 0.8289999961853027, 0.7480000257492065, 0.652999997138977, 0.6990000009536743, 0.7020000219345093, 0.7559999823570251, 0.7329999804496765, 0.6940000057220459, 0.6970000267028809, 0.7039999961853027, 0.7089999914169312, 0.6840000152587891, 0.6740000247955322, 0.6359999775886536, 0.6359999775886536, 0.652999997138977, 0.6819999814033508, 0.6690000295639038, 0.6840000152587891, 0.6499999761581421, 0.652999997138977, 0.6050000190734863, 0.6330000162124634, 0.6399999856948853, 0.6150000095367432, 0.6299999952316284, 0.6119999885559082, 0.628000020980835, 0.6200000047683716, 0.6069999933242798, 0.5950000286102295, 0.5820000171661377, 0.5889999866485596, 0.609000027179718, 0.5809999704360962, 0.5789999961853027, 0.5410000085830688, 0.5360000133514404, 0.5630000233650208, 0.5149999856948853, 0.5429999828338623, 0.5360000133514404, 0.5619999766349792, 0.5740000009536743, 0.6579999923706055, 0.6700000166893005, 0.7160000205039978, 0.7089999914169312, 0.6830000281333923, 0.6690000295639038, 0.675000011920929, 0.6439999938011169, 0.6399999856948853, 0.6460000276565552, 0.6819999814033508, 0.6869999766349792, 0.7459999918937683, 0.7289999723434448, 0.6930000185966492, 0.671999990940094, 0.6510000228881836, 0.621999979019165, 0.7210000157356262, 0.6840000152587891, 0.703000009059906, 0.6850000023841858, 0.6690000295639038, 0.6710000038146973, 0.6790000200271606, 0.6869999766349792, 0.6840000152587891, 0.6940000057220459, 0.6710000038146973, 0.6639999747276306, 0.6759999990463257, 0.6660000085830688, 0.6589999794960022, 0.6629999876022339, 0.6449999809265137, 0.6769999861717224, 0.6769999861717224, 0.6959999799728394, 0.7620000243186951, 0.7419999837875366, 0.7850000262260437, 0.7649999856948853, 0.7749999761581421, 0.7770000100135803, 0.7269999980926514, 0.722000002861023, 0.7310000061988831, 0.7440000176429749, 0.7609999775886536, 0.796999990940094, 0.8159999847412109, 0.8479999899864197, 0.8410000205039978, 0.8009999990463257, 0.777999997138977, 0.781000018119812, 0.8349999785423279, 0.8600000143051147, 0.8489999771118164, 0.8820000290870667, 0.7680000066757202, 0.7760000228881836, 0.8199999928474426, 0.9580000042915344, 0.972000002861023, 0.9580000042915344, 0.8849999904632568, 0.8930000066757202, 0.906000018119812, 0.871999979019165, 0.8820000290870667, 0.8539999723434448, 0.8289999961853027, 0.8569999933242798, 0.8820000290870667, 0.878000020980835, 0.8420000076293945, 0.843999981880188, 0.9340000152587891, 0.9480000138282776, 0.9200000166893005, 0.968999981880188, 0.9279999732971191, 0.9129999876022339, 0.9409999847412109, 0.9079999923706055, 0.8930000066757202, 0.8920000195503235, 0.9229999780654907, 0.9200000166893005, 0.9300000071525574, 0.9480000138282776, 0.9409999847412109, 0.9179999828338623, 0.9549999833106995, 0.9279999732971191, 0.9330000281333923, 0.9350000023841858, 0.9259999990463257, 0.9169999957084656, 0.9169999957084656, 0.9549999833106995, 1.0420000553131104, 1.0709999799728394, 1.1050000190734863, 1.1319999694824219, 1.1380000114440918, 1.0880000591278076, 1.128999948501587, 1.097000002861023, 1.0920000076293945, 1.090000033378601, 1.1089999675750732, 1.090999960899353, 1.0399999618530273, 1.0399999618530273, 1.0140000581741333, 1.0570000410079956, 1.093000054359436, 1.0770000219345093, 1.1050000190734863, 1.13100004196167, 1.1390000581741333, 1.1699999570846558, 1.159999966621399, 1.156999945640564, 1.1330000162124634, 1.1579999923706055, 1.2000000476837158, 1.2990000247955322, 1.3009999990463257, 1.2869999408721924, 1.3450000286102295, 1.3700000047683716, 1.3619999885559082, 1.3890000581741333, 1.5180000066757202, 1.4600000381469727, 1.4459999799728394, 1.4149999618530273, 1.4700000286102295, 1.5499999523162842, 1.5540000200271606, 1.5959999561309814, 1.5460000038146973, 1.5199999809265137, 1.5269999504089355, 1.6349999904632568, 1.6069999933242798, 1.621000051498413, 1.6410000324249268, 1.7300000190734863, 1.7319999933242798, 1.684000015258789, 1.6380000114440918, 1.6139999628067017, 1.6139999628067017, 1.659999966621399, 1.7209999561309814, 1.7259999513626099, 1.746000051498413, 1.6790000200271606, 1.7200000286102295, 1.656000018119812, 1.652999997138977, 1.6319999694824219, 1.6660000085830688, 1.6749999523162842, 1.6230000257492065, 1.6380000114440918, 1.5299999713897705, 1.5729999542236328, 1.6009999513626099, 1.562000036239624, 1.5640000104904175, 1.5540000200271606, 1.5670000314712524, 1.5700000524520874, 1.621999979019165, 1.6200000047683716, 1.6399999856948853, 1.63100004196167, 1.6069999933242798, 1.5920000076293945, 1.5839999914169312, 1.5609999895095825, 1.5770000219345093, 1.6019999980926514, 1.6239999532699585, 1.6950000524520874, 1.6679999828338623, 1.6349999904632568, 1.6399999856948853, 1.6419999599456787, 1.6829999685287476, 1.6339999437332153, 1.6319999694824219, 1.6080000400543213, 1.5640000104904175, 1.5740000009536743, 1.6100000143051147, 1.5809999704360962, 1.6150000095367432, 1.590999960899353, 1.625, 1.559999942779541, 1.569000005722046, 1.527999997138977, 1.4889999628067017, 1.4589999914169312, 1.4620000123977661, 1.5010000467300415, 1.4989999532699585, 1.569000005722046, 1.5110000371932983, 1.4500000476837158, 1.4839999675750732, 1.472000002861023, 1.4869999885559082, 1.4869999885559082, 1.5360000133514404, 1.4780000448226929, 1.4800000190734863, 1.4429999589920044, 1.4800000190734863, 1.430999994277954, 1.3700000047683716, 1.3209999799728394, 1.2879999876022339, 1.3559999465942383, 1.3630000352859497, 1.4149999618530273, 1.3559999465942383, 1.2970000505447388, 1.2999999523162842, 1.180999994277954, 1.2089999914169312, 1.2799999713897705, 1.2649999856948853, 1.2860000133514404, 1.2760000228881836, 1.2339999675750732, 1.2610000371932983, 1.2690000534057617, 1.2389999628067017, 1.1740000247955322, 1.1759999990463257, 1.184000015258789, 1.2170000076293945, 1.2899999618530273, 1.3170000314712524, 1.3420000076293945, 1.3289999961853027, 1.3669999837875366, 1.2970000505447388, 1.2569999694824219, 1.2580000162124634, 1.2730000019073486, 1.2419999837875366, 1.2599999904632568, 1.2549999952316284, 1.2899999618530273, 1.3420000076293945, 1.3420000076293945, 1.312000036239624, 1.284999966621399, 1.3040000200271606, 1.3020000457763672, 1.2940000295639038, 1.3220000267028809, 1.3700000047683716, 1.3339999914169312, 1.2990000247955322, 1.340999960899353, 1.3240000009536743, 1.2769999504089355, 1.3040000200271606, 1.3309999704360962, 1.3700000047683716, 1.309000015258789, 1.3240000009536743, 1.3359999656677246, 1.409999966621399, 1.4600000381469727, 1.4839999675750732, 1.534000039100647, 1.5410000085830688, 1.5290000438690186, 1.4789999723434448, 1.4809999465942383, 1.5290000438690186, 1.5240000486373901, 1.5709999799728394, 1.6050000190734863, 1.6139999628067017, 1.5800000429153442, 1.5490000247955322, 1.5190000534057617, 1.5759999752044678, 1.5839999914169312, 1.6349999904632568, 1.6360000371932983, 1.6759999990463257, 1.6549999713897705, 1.6349999904632568, 1.61899995803833, 1.5290000438690186, 1.5679999589920044, 1.5570000410079956, 1.5750000476837158, 1.5490000247955322, 1.5789999961853027, 1.5240000486373901, 1.4529999494552612, 1.496999979019165, 1.4320000410079956, 1.559999942779541, 1.559999942779541, 1.5820000171661377, 1.6230000257492065, 1.6339999437332153, 1.6039999723434448, 1.5889999866485596, 1.5360000133514404, 1.625, 1.6670000553131104, 1.6449999809265137, 1.4819999933242798, 1.5299999713897705, 1.4429999589920044, 1.434000015258789, 1.4479999542236328, 1.343000054359436, 1.434000015258789, 1.4800000190734863, 1.5089999437332153, 1.4869999885559082, 1.4889999628067017, 1.4240000247955322, 1.437999963760376, 1.4630000591278076, 1.4220000505447388, 1.4019999504089355, 1.4190000295639038, 1.4869999885559082, 1.4570000171661377, 1.4930000305175781, 1.4809999465942383, 1.4809999465942383, 1.5429999828338623, 1.5149999856948853, 1.5119999647140503, 1.628000020980835, 1.6679999828338623, 1.7050000429153442, 1.7330000400543213, 1.7710000276565552, 1.7799999713897705, 1.746000051498413, 1.725000023841858, 1.7109999656677246, 1.7719999551773071, 1.8650000095367432, 1.8270000219345093, 1.8329999446868896, 1.746999979019165, 1.7350000143051147, 1.7829999923706055, 1.8480000495910645, 1.8070000410079956, 1.781999945640564, 1.781999945640564, 1.7999999523162842, 1.7660000324249268, 1.8270000219345093, 1.9299999475479126, 1.9160000085830688, 1.9539999961853027, 1.9290000200271606, 2.0309998989105225, 1.9550000429153442, 1.996000051498413, 2.0450000762939453, 2.046999931335449, 1.972000002861023, 1.9320000410079956, 1.9479999542236328, 1.9769999980926514, 1.968999981880188, 1.9859999418258667, </t>
+          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [1.8819999694824219, 1.7879999876022339, 1.8109999895095825, 1.8270000219345093, 1.8739999532699585, 1.8580000400543213, 1.8250000476837158, 1.8480000495910645, 1.8179999589920044, 1.7879999876022339, 1.809000015258789, 1.8359999656677246, 1.7690000534057617, 1.7690000534057617, 1.7400000095367432, 1.680999994277954, 1.6050000190734863, 1.6410000324249268, 1.593999981880188, 1.5579999685287476, 1.5199999809265137, 1.5199999809265137, 1.6030000448226929, 1.6490000486373901, 1.6440000534057617, 1.5779999494552612, 1.5470000505447388, 1.590000033378601, 1.6299999952316284, 1.6169999837875366, 1.5880000591278076, 1.555999994277954, 1.5700000524520874, 1.524999976158142, 1.4709999561309814, 1.3769999742507935, 1.3300000429153442, 1.309999942779541, 1.2990000247955322, 1.1269999742507935, 1.0880000591278076, 1.0099999904632568, 0.9919999837875366, 0.9259999990463257, 0.7059999704360962, 0.49900001287460327, 0.7480000257492065, 0.8199999928474426, 0.8489999771118164, 0.9509999752044678, 0.7279999852180481, 0.996999979019165, 1.2660000324249268, 1.11899995803833, 0.9380000233650208, 0.7639999985694885, 0.8159999847412109, 0.8579999804496765, 0.8109999895095825, 0.7490000128746033, 0.6700000166893005, 0.6980000138282776, 0.6349999904632568, 0.6269999742507935, 0.5870000123977661, 0.6759999990463257, 0.7360000014305115, 0.7639999985694885, 0.7289999723434448, 0.7490000128746033, 0.7519999742507935, 0.6380000114440918, 0.609000027179718, 0.6539999842643738, 0.6259999871253967, 0.5709999799728394, 0.6190000176429749, 0.6129999756813049, 0.5960000157356262, 0.656000018119812, 0.6100000143051147, 0.6269999742507935, 0.621999979019165, 0.6420000195503235, 0.6370000243186951, 0.6570000052452087, 0.7110000252723694, 0.6309999823570251, 0.6819999814033508, 0.7260000109672546, 0.6779999732971191, 0.6489999890327454, 0.6190000176429749, 0.6399999856948853, 0.7440000176429749, 0.7110000252723694, 0.6800000071525574, 0.6769999861717224, 0.6570000052452087, 0.6980000138282776, 0.6800000071525574, 0.7049999833106995, 0.6480000019073486, 0.6620000004768372, 0.6800000071525574, 0.7609999775886536, 0.8199999928474426, 0.9039999842643738, 0.8840000033378601, 0.8289999961853027, 0.7480000257492065, 0.652999997138977, 0.6990000009536743, 0.7020000219345093, 0.7559999823570251, 0.7329999804496765, 0.6940000057220459, 0.6970000267028809, 0.7039999961853027, 0.7089999914169312, 0.6840000152587891, 0.6740000247955322, 0.6359999775886536, 0.6359999775886536, 0.652999997138977, 0.6819999814033508, 0.6690000295639038, 0.6840000152587891, 0.6499999761581421, 0.652999997138977, 0.6050000190734863, 0.6330000162124634, 0.6399999856948853, 0.6150000095367432, 0.6299999952316284, 0.6119999885559082, 0.628000020980835, 0.6200000047683716, 0.6069999933242798, 0.5950000286102295, 0.5820000171661377, 0.5889999866485596, 0.609000027179718, 0.5809999704360962, 0.5789999961853027, 0.5410000085830688, 0.5360000133514404, 0.5630000233650208, 0.5149999856948853, 0.5429999828338623, 0.5360000133514404, 0.5619999766349792, 0.5740000009536743, 0.6579999923706055, 0.6700000166893005, 0.7160000205039978, 0.7089999914169312, 0.6830000281333923, 0.6690000295639038, 0.675000011920929, 0.6439999938011169, 0.6399999856948853, 0.6460000276565552, 0.6819999814033508, 0.6869999766349792, 0.7459999918937683, 0.7289999723434448, 0.6930000185966492, 0.671999990940094, 0.6510000228881836, 0.621999979019165, 0.7210000157356262, 0.6840000152587891, 0.703000009059906, 0.6850000023841858, 0.6690000295639038, 0.6710000038146973, 0.6790000200271606, 0.6869999766349792, 0.6840000152587891, 0.6940000057220459, 0.6710000038146973, 0.6639999747276306, 0.6759999990463257, 0.6660000085830688, 0.6589999794960022, 0.6629999876022339, 0.6449999809265137, 0.6769999861717224, 0.6769999861717224, 0.6959999799728394, 0.7620000243186951, 0.7419999837875366, 0.7850000262260437, 0.7649999856948853, 0.7749999761581421, 0.7770000100135803, 0.7269999980926514, 0.722000002861023, 0.7310000061988831, 0.7440000176429749, 0.7609999775886536, 0.796999990940094, 0.8159999847412109, 0.8479999899864197, 0.8410000205039978, 0.8009999990463257, 0.777999997138977, 0.781000018119812, 0.8349999785423279, 0.8600000143051147, 0.8489999771118164, 0.8820000290870667, 0.7680000066757202, 0.7760000228881836, 0.8199999928474426, 0.9580000042915344, 0.972000002861023, 0.9580000042915344, 0.8849999904632568, 0.8930000066757202, 0.906000018119812, 0.871999979019165, 0.8820000290870667, 0.8539999723434448, 0.8289999961853027, 0.8569999933242798, 0.8820000290870667, 0.878000020980835, 0.8420000076293945, 0.843999981880188, 0.9340000152587891, 0.9480000138282776, 0.9200000166893005, 0.968999981880188, 0.9279999732971191, 0.9129999876022339, 0.9409999847412109, 0.9079999923706055, 0.8930000066757202, 0.8920000195503235, 0.9229999780654907, 0.9200000166893005, 0.9300000071525574, 0.9480000138282776, 0.9409999847412109, 0.9179999828338623, 0.9549999833106995, 0.9279999732971191, 0.9330000281333923, 0.9350000023841858, 0.9259999990463257, 0.9169999957084656, 0.9169999957084656, 0.9549999833106995, 1.0420000553131104, 1.0709999799728394, 1.1050000190734863, 1.1319999694824219, 1.1380000114440918, 1.0880000591278076, 1.128999948501587, 1.097000002861023, 1.0920000076293945, 1.090000033378601, 1.1089999675750732, 1.090999960899353, 1.0399999618530273, 1.0399999618530273, 1.0140000581741333, 1.0570000410079956, 1.093000054359436, 1.0770000219345093, 1.1050000190734863, 1.13100004196167, 1.1390000581741333, 1.1699999570846558, 1.159999966621399, 1.156999945640564, 1.1330000162124634, 1.1579999923706055, 1.2000000476837158, 1.2990000247955322, 1.3009999990463257, 1.2869999408721924, 1.3450000286102295, 1.3700000047683716, 1.3619999885559082, 1.3890000581741333, 1.5180000066757202, 1.4600000381469727, 1.4459999799728394, 1.4149999618530273, 1.4700000286102295, 1.5499999523162842, 1.5540000200271606, 1.5959999561309814, 1.5460000038146973, 1.5199999809265137, 1.5269999504089355, 1.6349999904632568, 1.6069999933242798, 1.621000051498413, 1.6410000324249268, 1.7300000190734863, 1.7319999933242798, 1.684000015258789, 1.6380000114440918, 1.6139999628067017, 1.6139999628067017, 1.659999966621399, 1.7209999561309814, 1.7259999513626099, 1.746000051498413, 1.6790000200271606, 1.7200000286102295, 1.656000018119812, 1.652999997138977, 1.6319999694824219, 1.6660000085830688, 1.6749999523162842, 1.6230000257492065, 1.6380000114440918, 1.5299999713897705, 1.5729999542236328, 1.6009999513626099, 1.562000036239624, 1.5640000104904175, 1.5540000200271606, 1.5670000314712524, 1.5700000524520874, 1.621999979019165, 1.6200000047683716, 1.6399999856948853, 1.63100004196167, 1.6069999933242798, 1.5920000076293945, 1.5839999914169312, 1.5609999895095825, 1.5770000219345093, 1.6019999980926514, 1.6239999532699585, 1.6950000524520874, 1.6679999828338623, 1.6349999904632568, 1.6399999856948853, 1.6419999599456787, 1.6829999685287476, 1.6339999437332153, 1.6319999694824219, 1.6080000400543213, 1.5640000104904175, 1.5740000009536743, 1.6100000143051147, 1.5809999704360962, 1.6150000095367432, 1.590999960899353, 1.625, 1.559999942779541, 1.569000005722046, 1.527999997138977, 1.4889999628067017, 1.4589999914169312, 1.4620000123977661, 1.5010000467300415, 1.4989999532699585, 1.569000005722046, 1.5110000371932983, 1.4500000476837158, 1.4839999675750732, 1.472000002861023, 1.4869999885559082, 1.4869999885559082, 1.5360000133514404, 1.4780000448226929, 1.4800000190734863, 1.4429999589920044, 1.4800000190734863, 1.430999994277954, 1.3700000047683716, 1.3209999799728394, 1.2879999876022339, 1.3559999465942383, 1.3630000352859497, 1.4149999618530273, 1.3559999465942383, 1.2970000505447388, 1.2999999523162842, 1.180999994277954, 1.2089999914169312, 1.2799999713897705, 1.2649999856948853, 1.2860000133514404, 1.2760000228881836, 1.2339999675750732, 1.2610000371932983, 1.2690000534057617, 1.2389999628067017, 1.1740000247955322, 1.1759999990463257, 1.184000015258789, 1.2170000076293945, 1.2899999618530273, 1.3170000314712524, 1.3420000076293945, 1.3289999961853027, 1.3669999837875366, 1.2970000505447388, 1.2569999694824219, 1.2580000162124634, 1.2730000019073486, 1.2419999837875366, 1.2599999904632568, 1.2549999952316284, 1.2899999618530273, 1.3420000076293945, 1.3420000076293945, 1.312000036239624, 1.284999966621399, 1.3040000200271606, 1.3020000457763672, 1.2940000295639038, 1.3220000267028809, 1.3700000047683716, 1.3339999914169312, 1.2990000247955322, 1.340999960899353, 1.3240000009536743, 1.2769999504089355, 1.3040000200271606, 1.3309999704360962, 1.3700000047683716, 1.309000015258789, 1.3240000009536743, 1.3359999656677246, 1.409999966621399, 1.4600000381469727, 1.4839999675750732, 1.534000039100647, 1.5410000085830688, 1.5290000438690186, 1.4789999723434448, 1.4809999465942383, 1.5290000438690186, 1.5240000486373901, 1.5709999799728394, 1.6050000190734863, 1.6139999628067017, 1.5800000429153442, 1.5490000247955322, 1.5190000534057617, 1.5759999752044678, 1.5839999914169312, 1.6349999904632568, 1.6360000371932983, 1.6759999990463257, 1.6549999713897705, 1.6349999904632568, 1.61899995803833, 1.5290000438690186, 1.5679999589920044, 1.5570000410079956, 1.5750000476837158, 1.5490000247955322, 1.5789999961853027, 1.5240000486373901, 1.4529999494552612, 1.496999979019165, 1.4320000410079956, 1.559999942779541, 1.559999942779541, 1.5820000171661377, 1.6230000257492065, 1.6339999437332153, 1.6039999723434448, 1.5889999866485596, 1.5360000133514404, 1.625, 1.6670000553131104, 1.6449999809265137, 1.4819999933242798, 1.5299999713897705, 1.4429999589920044, 1.434000015258789, 1.4479999542236328, 1.343000054359436, 1.434000015258789, 1.4800000190734863, 1.5089999437332153, 1.4869999885559082, 1.4889999628067017, 1.4240000247955322, 1.437999963760376, 1.4630000591278076, 1.4220000505447388, 1.4019999504089355, 1.4190000295639038, 1.4869999885559082, 1.4570000171661377, 1.4930000305175781, 1.4809999465942383, 1.4809999465942383, 1.5429999828338623, 1.5149999856948853, 1.5119999647140503, 1.628000020980835, 1.6679999828338623, 1.7050000429153442, 1.7330000400543213, 1.7710000276565552, 1.7799999713897705, 1.746000051498413, 1.725000023841858, 1.7109999656677246, 1.7719999551773071, 1.8650000095367432, 1.8270000219345093, 1.8329999446868896, 1.746999979019165, 1.7350000143051147, 1.7829999923706055, 1.8480000495910645, 1.8070000410079956, 1.781999945640564, 1.781999945640564, 1.7999999523162842, 1.7660000324249268, 1.8270000219345093, 1.9299999475479126, 1.9160000085830688, 1.9539999961853027, 1.9290000200271606, 2.0309998989105225, 1.9550000429153442, 1.996000051498413, 2.045000076293945</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66931.1015625</v>
+        <v>75726.2109375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1285,22 +1285,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>69339.068359375</v>
+        <v>71252.51953125</v>
       </c>
       <c r="Q8" t="n">
-        <v>68785.1142578125</v>
+        <v>69633.28736979167</v>
       </c>
       <c r="R8" t="n">
-        <v>79004.41018880208</v>
+        <v>76909.24117838542</v>
       </c>
       <c r="S8" t="n">
-        <v>97660.39981990666</v>
+        <v>96029.8325005073</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="b">
         <v>0</v>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-01', '2020-01-02', '2020-01-03', '2020-01-04', '2020-01-05', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-11', '2020-01-12', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-18', '2020-01-19', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-25', '2020-01-26', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-01', '2020-02-02', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-08', '2020-02-09', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-15', '2020-02-16', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-22', '2020-02-23', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-02-29', '2020-03-01', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-07', '2020-03-08', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-14', '2020-03-15', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-21', '2020-03-22', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-28', '2020-03-29', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-04', '2020-04-05', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-10', '2020-04-11', '2020-04-12', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-18', '2020-04-19', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-25', '2020-04-26', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-02', '2020-05-03', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-09', '2020-05-10', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-16', '2020-05-17', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-23', '2020-05-24', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-05-30', '2020-05-31', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-06', '2020-06-07', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-13', '2020-06-14', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-20', '2020-06-21', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-27', '2020-06-28', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-03', '2020-07-04', '2020-07-05', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-11', '2020-07-12', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-18', '2020-07-19', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-25', '2020-07-26', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-01', '2020-08-02', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-08', '2020-08-09', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-15', '2020-08-16', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-22', '2020-08-23', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-29', '2020-08-30', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-05', '2020-09-06', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-12', '2020-09-13', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-19', '2020-09-20', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-26', '2020-09-27', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-03', '2020-10-04', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-10', '2020-10-11', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-17', '2020-10-18', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-24', '2020-10-25', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-10-31', '2020-11-01', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-07', '2020-11-08', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-14', '2020-11-15', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-21', '2020-11-22', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-28', '2020-11-29', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-05', '2020-12-06', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-12', '2020-12-13', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-19', '2020-12-20', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-25', '2020-12-26', '2020-12-27', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-01', '2021-01-02', '2021-01-03', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-09', '2021-01-10', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-16', '2021-01-17', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-23', '2021-01-24', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-01-30', '2021-01-31', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-06', '2021-02-07', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-13', '2021-02-14', '2021-02-15', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-20', '2021-02-21', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-02-27', '2021-02-28', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-06', '2021-03-07', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-13', '2021-03-14', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-20', '2021-03-21', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-27', '2021-03-28', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-02', '2021-04-03', '2021-04-04', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-10', '2021-04-11', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-17', '2021-04-18', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-24', '2021-04-25', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-01', '2021-05-02', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-08', '2021-05-09', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-15', '2021-05-16', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-22', '2021-05-23', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-29', '2021-05-30', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-05', '2021-06-06', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-12', '2021-06-13', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-19', '2021-06-20', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-26', '2021-06-27', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-03', '2021-07-04', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-10', '2021-07-11', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-17', '2021-07-18', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-24', '2021-07-25', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-07-31', '2021-08-01', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-07', '2021-08-08', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-14', '2021-08-15', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-21', '2021-08-22', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-28', '2021-08-29', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-04', '2021-09-05', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-11', '2021-09-12', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-18', '2021-09-19', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-25', '2021-09-26', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-02', '2021-10-03', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-09', '2021-10-10', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-16', '2021-10-17', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-23', '2021-10-24', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-10-30', '2021-10-31', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-06', '2021-11-07', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-13', '2021-11-14', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-20', '2021-11-21', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-27', '2021-11-28', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-04', '2021-12-05', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-11', '2021-12-12', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-18', '2021-12-19', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-25', '2021-12-26', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-01', '2022-01-02', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-08', '2022-01-09', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-15', '2022-01-16', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-22', '2022-01-23', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-29', '2022-01-30', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-05', '2022-02-06', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-12', '2022-02-13', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-19', '2022-02-20', '2022-02-21', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-26', '2022-02-27', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-05', '2022-03-06', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-12', '2022-03-13', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-19', '2022-03-20', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-26', '2022-03-27', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-02', '2022-04-03', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-09', '2022-04-10', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-15', '2022-04-16', '2022-04-17', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-23', '2022-04-24', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-04-30', '2022-05-01', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-07', '2022-05-08', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-14', '2022-05-15', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-21', '2022-05-22', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-28', '2022-05-29', '2022-05-30', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-04', '2022-06-05', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-11', '2022-06-12', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-18', '2022-06-19', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-25', '2022-06-26', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-02', '2022-07-03', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-09', '2022-07-10', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-16', '2022-07-17', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-23', '2022-07-24', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-07-30', '2022-07-31', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-06', '2022-08-07', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-13', '2022-08-14', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-20', '2022-08-21', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-27', '2022-08-28', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-03', '2022-09-04', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-10', '2022-09-11', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-17', '2022-09-18', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-24', '2022-09-25', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-01', '2022-10-02', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-08', '2022-10-09', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-15', '2022-10-16', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-22', '2022-10-23', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-29', '2022-10-30', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-05', '2022-11-06', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-12', '2022-11-13', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-19', '2022-11-20', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-24', '2022-11-25', '2022-11-26', '2022-11-27', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-03', '2022-12-04', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-10', '2022-12-11', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-17', '2022-12-18', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-24', '2022-12-25', '2022-12-26', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2022-12-31', '2023-01-01', '2023-01-02', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-07', '2023-01-08', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-14', '2023-01-15', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-21', '2023-01-22', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-28', '2023-01-29', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-04', '2023-02-05', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-11', '2023-02-12', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-18', '2023-02-19', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-25', '2023-02-26', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-04', '2023-03-05', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-11', '2023-03-12', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-18', '2023-03-19', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-25', '2023-03-26', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-01', '2023-04-02', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-07', '2023-04-08', '2023-04-09', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-15', '2023-04-16', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-22', '2023-04-23', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-04-29', '2023-04-30', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-06', '2023-05-07', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-13', '2023-05-14', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-20', '2023-05-21', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-27', '2023-05-28', '2023-05-29', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-03', '2023-06-04', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-10', '2023-06-11', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-17', '2023-06-18', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-24', '2023-06-25', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-01', '2023-07-02', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-08', '2023-07-09', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-15', '2023-07-16', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-22', '2023-07-23', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-29', '2023-07-30', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-05', '2023-08-06', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-12', '2023-08-13', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-19', '2023-08-20', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-26', '2023-08-27', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-02', '2023-09-03', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-09', '2023-09-10', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-16', '2023-09-17', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-23', '2023-09-24', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-09-30', '2023-10-01', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-07', '2023-10-08', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-14', '2023-10-15', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-21', '2023-10-22', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-28', '2023-10-29', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-04', '2023-11-05', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-11', '2023-11-12', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-18', '2023-11-19', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-25', '2023-11-26', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-02', '2023-12-03', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-09', '2023-12-10', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-16', '2023-12-17', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-23', '2023-12-24', '2023-12-25', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2023-12-30', '2023-12-31', '2024-01-01', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-06', '2024-01-07', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-13', '2024-01-14', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-20', '2024-01-21', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-27', '2024-01-28', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-03', '2024-02-04', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-10', '2024-02-11', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-17', '2024-02-18', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-24', '2024-02-25', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-02', '2024-03-03', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-09', '2024-03-10', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-16', '2024-03-17', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-23', '2024-03-24', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-03-29', '2024-03-30', '2024-03-31', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-06', '2024-04-07', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-13', '2024-04-14', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-20', '2024-04-21', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-27', '2024-04-28', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-04', '2024-05-05', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-11', '2024-05-12', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-18', '2024-05-19', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-25', '2024-05-26', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-01', '2024-06-02', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-08', '2024-06-09', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-15', '2024-06-16', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-22', '2024-06-23', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-06-29', '2024-06-30', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-06', '2024-07-07', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-13', '2024-07-14', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-20', '2024-07-21', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-27', '2024-07-28', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-03', '2024-08-04', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-10', '2024-08-11', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-17', '2024-08-18', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-24', '2024-08-25', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-08-31', '2024-09-01', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-07', '2024-09-08', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-14', '2024-09-15', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-21', '2024-09-22', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-28', '2024-09-29', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-05', '2024-10-06', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-12', '2024-10-13', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-19', '2024-10-20', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-26', '2024-10-27', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-02', '2024-11-03', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-09', '2024-11-10', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-16', '2024-11-17', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-23', '2024-11-24', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-11-30', '2024-12-01', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-07', '2024-12-08', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-14', '2024-12-15', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-21', '2024-12-22', '2024-12-23', '2024-12-24', '2024-12-25', '2024-12-26', '2024-12-27', '2024-12-28', '2024-12-29', '2024-12-30', '2024-12-31', '2025-01-01', '2025-01-02', '2025-01-03', '2025-01-04', '2025-01-05', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-11', '2025-01-12', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-18', '2025-01-19', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-25', '2025-01-26', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-01', '2025-02-02', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-08', '2025-02-09', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-15', '2025-02-16', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-22', '2025-02-23', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-01', '2025-03-02', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-08', '2025-03-09', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-15', '2025-03-16', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-22', '2025-03-23', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-29', '2025-03-30', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-05', '2025-04-06', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-12', '2025-04-13', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-18', '2025-04-19', '2025-04-20', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-26', '2025-04-27', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-03', '2025-05-04', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-10', '2025-05-11', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-17', '2025-05-18', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-24', '2025-05-25', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-05-31', '2025-06-01', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-07', '2025-06-08', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-14', '2025-06-15', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-21', '2025-06-22', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-28', '2025-06-29', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-05', '2025-07-06', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-12', '2025-07-13', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-19', '2025-07-20', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-26', '2025-07-27', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-02', '2025-08-03', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-09', '2025-08-10', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-16', '2025-08-17', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-23', '2025-08-24', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-08-30', '2025-08-31', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-06', '2025-09-07', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-13', '2025-09-14', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-20', '2025-09-21', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-27', '2025-09-28', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-04', '2025-10-05', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-11', '2025-10-12', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-18', '2025-10-19', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-25', '2025-10-26', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-01', '2025-11-02', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-08', '2025-11-09', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-15', '2025-11-16', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-22', '2025-11-23', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-11-29', '2025-11-30', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-06', '2025-12-07', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-13', '2025-12-14', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-20', '2025-12-21', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-25', '2025-12-26', '2025-12-27', '2025-12-28', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-01', '2026-01-02', '2026-01-03', '2026-01-04', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-10', '2026-01-11', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-17', '2026-01-18', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-24', '2026-01-25', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-01-31', '2026-02-01', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-07', '2026-02-08', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-14', '2026-02-15', '2026-02-16', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-21', '2026-02-22', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-02-28', '2026-03-01', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-07', '2026-03-08', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-14', '2026-03-15', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-21', '2026-03-22', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-28', '2026-03-29', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-03'], 'prices': [7200.17431640625, 6985.47021484375, 7344.88427734375, 7410.65673828125, 7411.3173828125, 7769.21923828125, 8163.6923828125, 8079.86279296875, 7879.0712890625, 8166.55419921875, 8037.53759765625, 8192.494140625, 8144.1943359375, 8827.7646484375, 8807.0107421875, 8723.7861328125, 8929.0380859375, 8942.80859375, 8706.2451171875, 8657.642578125, 8745.89453125, 8680.8759765625, 8406.515625, 8445.4345703125, 8367.84765625, 8596.830078125, 8909.8193359375, 9358.58984375, 9316.6298828125, 9508.9931640625, 9350.529296875, 9392.875, 9344.365234375, 9293.521484375, 9180.962890625, 9613.423828125, 9729.8017578125, 9795.943359375, 9865.119140625, 10116.673828125, 9856.611328125, 10208.236328125, 10326.0546875, 10214.3798828125, 10312.1162109375, 9889.424804</t>
+          <t>{'dates': ['2020-01-01', '2020-01-02', '2020-01-03', '2020-01-04', '2020-01-05', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-11', '2020-01-12', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-18', '2020-01-19', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-25', '2020-01-26', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-01', '2020-02-02', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-08', '2020-02-09', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-15', '2020-02-16', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-22', '2020-02-23', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-02-29', '2020-03-01', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-07', '2020-03-08', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-14', '2020-03-15', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-21', '2020-03-22', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-28', '2020-03-29', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-04', '2020-04-05', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-10', '2020-04-11', '2020-04-12', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-18', '2020-04-19', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-25', '2020-04-26', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-02', '2020-05-03', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-09', '2020-05-10', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-16', '2020-05-17', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-23', '2020-05-24', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-05-30', '2020-05-31', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-06', '2020-06-07', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-13', '2020-06-14', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-20', '2020-06-21', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-27', '2020-06-28', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-03', '2020-07-04', '2020-07-05', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-11', '2020-07-12', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-18', '2020-07-19', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-25', '2020-07-26', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-01', '2020-08-02', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-08', '2020-08-09', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-15', '2020-08-16', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-22', '2020-08-23', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-29', '2020-08-30', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-05', '2020-09-06', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-12', '2020-09-13', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-19', '2020-09-20', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-26', '2020-09-27', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-03', '2020-10-04', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-10', '2020-10-11', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-17', '2020-10-18', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-24', '2020-10-25', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-10-31', '2020-11-01', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-07', '2020-11-08', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-14', '2020-11-15', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-21', '2020-11-22', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-28', '2020-11-29', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-05', '2020-12-06', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-12', '2020-12-13', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-19', '2020-12-20', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-25', '2020-12-26', '2020-12-27', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-01', '2021-01-02', '2021-01-03', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-09', '2021-01-10', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-16', '2021-01-17', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-23', '2021-01-24', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-01-30', '2021-01-31', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-06', '2021-02-07', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-13', '2021-02-14', '2021-02-15', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-20', '2021-02-21', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-02-27', '2021-02-28', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-06', '2021-03-07', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-13', '2021-03-14', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-20', '2021-03-21', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-27', '2021-03-28', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-02', '2021-04-03', '2021-04-04', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-10', '2021-04-11', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-17', '2021-04-18', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-24', '2021-04-25', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-01', '2021-05-02', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-08', '2021-05-09', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-15', '2021-05-16', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-22', '2021-05-23', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-29', '2021-05-30', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-05', '2021-06-06', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-12', '2021-06-13', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-19', '2021-06-20', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-26', '2021-06-27', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-03', '2021-07-04', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-10', '2021-07-11', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-17', '2021-07-18', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-24', '2021-07-25', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-07-31', '2021-08-01', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-07', '2021-08-08', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-14', '2021-08-15', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-21', '2021-08-22', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-28', '2021-08-29', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-04', '2021-09-05', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-11', '2021-09-12', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-18', '2021-09-19', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-25', '2021-09-26', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-02', '2021-10-03', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-09', '2021-10-10', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-16', '2021-10-17', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-23', '2021-10-24', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-10-30', '2021-10-31', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-06', '2021-11-07', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-13', '2021-11-14', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-20', '2021-11-21', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-27', '2021-11-28', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-04', '2021-12-05', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-11', '2021-12-12', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-18', '2021-12-19', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-25', '2021-12-26', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-01', '2022-01-02', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-08', '2022-01-09', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-15', '2022-01-16', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-22', '2022-01-23', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-29', '2022-01-30', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-05', '2022-02-06', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-12', '2022-02-13', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-19', '2022-02-20', '2022-02-21', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-26', '2022-02-27', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-05', '2022-03-06', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-12', '2022-03-13', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-19', '2022-03-20', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-26', '2022-03-27', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-02', '2022-04-03', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-09', '2022-04-10', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-15', '2022-04-16', '2022-04-17', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-23', '2022-04-24', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-04-30', '2022-05-01', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-07', '2022-05-08', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-14', '2022-05-15', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-21', '2022-05-22', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-28', '2022-05-29', '2022-05-30', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-04', '2022-06-05', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-11', '2022-06-12', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-18', '2022-06-19', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-25', '2022-06-26', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-02', '2022-07-03', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-09', '2022-07-10', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-16', '2022-07-17', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-23', '2022-07-24', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-07-30', '2022-07-31', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-06', '2022-08-07', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-13', '2022-08-14', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-20', '2022-08-21', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-27', '2022-08-28', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-03', '2022-09-04', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-10', '2022-09-11', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-17', '2022-09-18', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-24', '2022-09-25', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-01', '2022-10-02', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-08', '2022-10-09', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-15', '2022-10-16', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-22', '2022-10-23', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-29', '2022-10-30', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-05', '2022-11-06', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-12', '2022-11-13', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-19', '2022-11-20', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-24', '2022-11-25', '2022-11-26', '2022-11-27', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-03', '2022-12-04', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-10', '2022-12-11', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-17', '2022-12-18', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-24', '2022-12-25', '2022-12-26', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2022-12-31', '2023-01-01', '2023-01-02', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-07', '2023-01-08', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-14', '2023-01-15', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-21', '2023-01-22', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-28', '2023-01-29', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-04', '2023-02-05', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-11', '2023-02-12', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-18', '2023-02-19', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-25', '2023-02-26', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-04', '2023-03-05', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-11', '2023-03-12', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-18', '2023-03-19', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-25', '2023-03-26', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-01', '2023-04-02', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-07', '2023-04-08', '2023-04-09', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-15', '2023-04-16', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-22', '2023-04-23', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-04-29', '2023-04-30', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-06', '2023-05-07', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-13', '2023-05-14', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-20', '2023-05-21', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-27', '2023-05-28', '2023-05-29', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-03', '2023-06-04', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-10', '2023-06-11', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-17', '2023-06-18', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-24', '2023-06-25', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-01', '2023-07-02', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-08', '2023-07-09', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-15', '2023-07-16', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-22', '2023-07-23', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-29', '2023-07-30', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-05', '2023-08-06', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-12', '2023-08-13', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-19', '2023-08-20', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-26', '2023-08-27', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-02', '2023-09-03', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-09', '2023-09-10', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-16', '2023-09-17', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-23', '2023-09-24', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-09-30', '2023-10-01', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-07', '2023-10-08', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-14', '2023-10-15', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-21', '2023-10-22', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-28', '2023-10-29', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-04', '2023-11-05', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-11', '2023-11-12', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-18', '2023-11-19', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-25', '2023-11-26', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-02', '2023-12-03', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-09', '2023-12-10', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-16', '2023-12-17', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-23', '2023-12-24', '2023-12-25', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2023-12-30', '2023-12-31', '2024-01-01', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-06', '2024-01-07', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-13', '2024-01-14', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-20', '2024-01-21', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-27', '2024-01-28', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-03', '2024-02-04', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-10', '2024-02-11', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-17', '2024-02-18', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-24', '2024-02-25', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-02', '2024-03-03', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-09', '2024-03-10', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-16', '2024-03-17', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-23', '2024-03-24', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-03-29', '2024-03-30', '2024-03-31', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-06', '2024-04-07', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-13', '2024-04-14', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-20', '2024-04-21', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-27', '2024-04-28', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-04', '2024-05-05', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-11', '2024-05-12', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-18', '2024-05-19', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-25', '2024-05-26', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-01', '2024-06-02', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-08', '2024-06-09', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-15', '2024-06-16', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-22', '2024-06-23', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-06-29', '2024-06-30', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-06', '2024-07-07', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-13', '2024-07-14', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-20', '2024-07-21', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-27', '2024-07-28', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-03', '2024-08-04', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-10', '2024-08-11', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-17', '2024-08-18', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-24', '2024-08-25', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-08-31', '2024-09-01', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-07', '2024-09-08', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-14', '2024-09-15', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-21', '2024-09-22', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-28', '2024-09-29', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-05', '2024-10-06', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-12', '2024-10-13', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-19', '2024-10-20', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-26', '2024-10-27', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-02', '2024-11-03', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-09', '2024-11-10', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-16', '2024-11-17', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-23', '2024-11-24', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-11-30', '2024-12-01', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-07', '2024-12-08', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-14', '2024-12-15', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-21', '2024-12-22', '2024-12-23', '2024-12-24', '2024-12-25', '2024-12-26', '2024-12-27', '2024-12-28', '2024-12-29', '2024-12-30', '2024-12-31', '2025-01-01', '2025-01-02', '2025-01-03', '2025-01-04', '2025-01-05', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-11', '2025-01-12', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-18', '2025-01-19', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-25', '2025-01-26', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-01', '2025-02-02', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-08', '2025-02-09', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-15', '2025-02-16', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-22', '2025-02-23', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-01', '2025-03-02', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-08', '2025-03-09', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-15', '2025-03-16', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-22', '2025-03-23', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-29', '2025-03-30', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-05', '2025-04-06', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-12', '2025-04-13', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-18', '2025-04-19', '2025-04-20', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-26', '2025-04-27', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-03', '2025-05-04', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-10', '2025-05-11', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-17', '2025-05-18', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-24', '2025-05-25', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-05-31', '2025-06-01', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-07', '2025-06-08', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-14', '2025-06-15', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-21', '2025-06-22', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-28', '2025-06-29', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-05', '2025-07-06', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-12', '2025-07-13', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-19', '2025-07-20', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-26', '2025-07-27', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-02', '2025-08-03', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-09', '2025-08-10', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-16', '2025-08-17', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-23', '2025-08-24', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-08-30', '2025-08-31', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-06', '2025-09-07', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-13', '2025-09-14', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-20', '2025-09-21', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-27', '2025-09-28', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-04', '2025-10-05', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-11', '2025-10-12', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-18', '2025-10-19', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-25', '2025-10-26', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-01', '2025-11-02', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-08', '2025-11-09', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-15', '2025-11-16', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-22', '2025-11-23', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-11-29', '2025-11-30', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-06', '2025-12-07', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-13', '2025-12-14', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-20', '2025-12-21', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-25', '2025-12-26', '2025-12-27', '2025-12-28', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-01', '2026-01-02', '2026-01-03', '2026-01-04', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-10', '2026-01-11', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-17', '2026-01-18', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-24', '2026-01-25', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-01-31', '2026-02-01', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-07', '2026-02-08', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-14', '2026-02-15', '2026-02-16', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-21', '2026-02-22', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-02-28', '2026-03-01', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-07', '2026-03-08', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-14', '2026-03-15', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-21', '2026-03-22', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-28', '2026-03-29', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-03', '2026-04-04', '2026-04-05', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-11', '2026-04-12', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-18'], 'prices': [7200.17431640625, 6985.47021484375, 7344.88427734375, 7410.65673828125, 7411.3173828125, 7769.21923828125, 8163.6923828125, 8079.86279296875, 7879.0712890625, 8166.55419921875, 8037.53759765625, 8192.494140625, 8144.1943359375, 8827.7646484375, 8807.0107421875, 8723.7861328125, 8929.0380859375, 8942.80859375, 8706.2451171875, 8657.642578125, 8745.89453125, 8680.8759765625, 8406.515625, 8445.4345703125, 8367.84765625, 8596.830078125, 8909.8193359375, 9358.58984375, 9316.6298828125, 9508.9931640625, 9350.529296875, 9392.875, 9344.365234375,</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -1467,11 +1467,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6582.68994140625</v>
+        <v>7126.06005859375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1506,27 +1506,27 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1535,37 +1535,37 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>6607.838525390625</v>
+        <v>6690.448046875</v>
       </c>
       <c r="Q2" t="n">
-        <v>6806.910823567709</v>
+        <v>6797.972664388021</v>
       </c>
       <c r="R2" t="n">
-        <v>6798.318737792969</v>
+        <v>6814.759997558594</v>
       </c>
       <c r="S2" t="n">
-        <v>6343.255543894582</v>
+        <v>6372.318237304688</v>
       </c>
       <c r="T2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="b">
         <v>1</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02'], 'prices': [3257.85009765625, 3234.85009765625, 3246.280029296875, 3237.179931640625, 3253.050048828125, 3274.699951171875, 3265.35009765625, 3288.1298828125, 3283.14990234375, 3289.2900390625, 3316.81005859375, 3329.6201171875, 3320.7900390625, 3321.75, 3325.5400390625, 3295.469970703125, 3243.6298828125, 3276.239990234375, 3273.39990234375, 3283.659912109375, 3225.52001953125, 3248.919921875, 3297.590087890625, 3334.68994140625, 3345.780029296875, 3327.7099609375, 3352.090087890625, 3357.75, 3379.449951171875, 3373.93994140625, 3380.159912109375, 3370.2900390625, 3386.14990234375, 3373.22998046875, 3337.75, 3225.889892578125, 3128.2099609375, 3116.389892578125, 2978.760009765625, 2954.219970703125, 3090.22998046875, 3003.3701171875, 3130.1201171875, 3023.93994140625, 2972.3701171875, 2746.56005859375, 2882.22998046875, 2741.3798828125, 2480.639892578125, 2711.02001953125, 2386.1298828125, 2529.18994140625, 2398.10009765625, 2409.389892578125, 2304.919921875, 2237.39990234375, 2447.330078125, 2475.56005859375, 2630.070068359375, 2541.469970703125, 2626.64990234375, 2584.590087890625, 2470.5, 2526.89990234375, 2488.64990234375, 2663.679931640625, 2659.409912109375, 2749.97998046875, 2789.820068359375, 2761.6298828125, 2846.06005859375, 2783.360107421875, 2799.550048828125, 2874.56005859375, 2823.159912109375, 2736.56005859375, 2799.31005859375, 2797.800048828125, 2836.739990234375, 2878.47998046875, 2863.389892578125, 2939.510009765625, 2912.429931640625, 2830.7099609375, 2842.739990234375, 2868.43994140625, 2848.419921875, 2881.18994140625, 2929.800048828125, 2930.18994140625, 2870.1201171875, 2820.0, 2852.5, 2863.699951171875, 2953.909912109375, 2922.93994140625, 2971.610107421875, 2948.510009765625, 2955.449951171875, 2991.77001953125, 3036.1298828125, 3029.72998046875, 3044.31005859375, 3055.72998046875, 3080.820068359375, 3122.8701171875, 3112.35009765625, 3193.929931640625, 3232.389892578125, 3207.179931640625, 3190.139892578125, 3002.10009765625, 3041.31005859375, 3066.590087890625, 3124.739990234375, 3113.489990234375, 3115.340087890625, 3097.739990234375, 3117.860107421875, 3131.2900390625, 3050.330078125, 3083.760009765625, 3009.050048828125, 3053.239990234375, 3100.2900390625, 3115.860107421875, 3130.010009765625, 3179.719970703125, 3145.320068359375, 3169.93994140625, 3152.050048828125, 3185.0400390625, 3155.219970703125, 3197.52001953125, 3226.56005859375, 3215.570068359375, 3224.72998046875, 3251.840087890625, 3257.300048828125, 3276.02001953125, 3235.659912109375, 3215.6298828125, 3239.409912109375, 3218.43994140625, 3258.43994140625, 3246.219970703125, 3271.1201171875, 3294.610107421875, 3306.510009765625, 3327.77001953125, 3349.159912109375, 3351.280029296875, 3360.469970703125, 3333.68994140625, 3380.35009765625, 3373.429931640625, 3372.85009765625, 3381.989990234375, 3389.780029296875, 3374.85009765625, 3385.510009765625, 3397.159912109375, 3431.280029296875, 3443.6201171875, 3478.72998046875, 3484.550048828125, 3508.010009765625, 3500.31005859375, 3526.64990234375, 3580.840087890625, 3455.06005859375, 3426.9599609375, 3331.840087890625, 3398.9599609375, 3339.18994140625, 3340.969970703125, 3383.5400390625, 3401.199951171875, 3385.489990234375, 3357.010009765625, 3319.469970703125, 3281.06005859375, 3315.570068359375, 3236.919921875, 3246.590087890625, 3298.4599609375, 3351.60009765625, 3335.469970703125, 3363.0, 3380.800048828125, 3348.419921875, 3408.60009765625, 3360.969970703125, 3419.43994140625, 3446.830078125, 3477.139892578125, 3534.219970703125, 3511.929931640625, 3488.669921875, 3483.340087890625, 3483.81005859375, 3426.919921875, 3443.1201171875, 3435.56005859375, 3453.489990234375, 3465.389892578125, 3400.969970703125, 3390.679931640625, 3271.030029296875, 3310.110107421875, 3269.9599609375, 3310.239990234375, 3369.159912109375, 3443.43994140625, 3510.449951171875, 3509.43994140625, 3550.5, 3545.530029296875, 3572.659912109375, 3537.010009765625, 3585.14990234375, 3626.909912109375, 3609.530029296875, 3567.7900390625, 3581.8701171875, 3557.5400390625, 3577.590087890625, 3635.409912109375, 3629.64990234375, 3638.35009765625, 3621.6298828125, 3662.449951171875, 3669.010009765625, 3666.719970703125, 3699.1201171875, 3691.9599609375, 3702.25, 3672.820068359375, 3668.10009765625, 3663.4599609375, 3647.489990234375, 3694.6201171875, 3701.169921875, 3722.47998046875, 3709.409912109375, 3694.919921875, 3687.260009765625, 3690.010009765625, 3703.06005859375, 3735.360107421875, 3727.0400390625, 3732.0400390625, 3756.070068359375, 3700.64990234375, 3726.860107421875, 3748.139892578125, 3803.7900390625, 3824.679931640625, 3799.610107421875, 3801.18994140625, 3809.840087890625, 3795.5400390625, 3768.25, 3798.909912109375, 3851.85009765625, 3853.070068359375, 3841.469970703125, 3855.360107421875, 3849.6201171875, 3750.77001953125, 3787.3798828125, 3714.239990234375, 3773.860107421875, 3826.31005859375, 3830.169921875, 3871.739990234375, 3886.830078125, 3915.590087890625, 3911.22998046875, 3909.8798828125, 3916.3798828125, 3934.830078125, 3932.590087890625, 3931.330078125, 3913.969970703125, 3906.7099609375, 3876.5, 3881.3701171875, 3925.429931640625, 3829.340087890625, 3811.14990234375, 3901.820068359375, 3870.2900390625, 3819.719970703125, 3768.469970703125, 3841.93994140625, 3821.35009765625, 3875.43994140625, 3898.81005859375, 3939.340087890625, 3943.340087890625, 3968.93994140625, 3962.7099609375, 3974.1201171875, 3915.4599609375, 3913.10009765625, 3940.590087890625, 3910.52001953125, 3889.139892578125, 3909.52001953125, 3974.5400390625, 3971.090087890625, 3958.550048828125, 3972.889892578125, 4019.8701171875, 4077.909912109375, 4073.93994140625, 4079.949951171875, 4097.169921875, 4128.7998046875, 4127.990234375, 4141.58984375, 4124.66015625, 4170.419921875, 4185.47021484375, 4163.259765625, 4134.93994140625, 4173.419921875, 4134.97998046875, 4180.169921875, 4187.6201171875, 4186.72021484375, 4183.18017578125, 4211.47021484375, 4181.169921875, 4192.66015625, 4164.66015625, 4167.58984375, 4201.6201171875, 4232.60009765625, 4188.43017578125, 4152.10009765625, 4063.0400390625, 4112.5, 4173.85009765625, 4163.2900390625, 4127.830078125, 4115.68017578125, 4159.1201171875, 4155.85986328125, 4197.0498046875, 4188.1298828125, 4195.990234375, 4200.8798828125, 4204.10986328125, 4202.0400390625, 4208.1201171875, 4192.85009765625, 4229.89013671875, 4226.52001953125, 4227.259765625, 4219.5498046875, 4239.18017578125, 4247.43994140625, 4255.14990234375, 4246.58984375, 4223.7001953125, 4221.85986328125, 4166.4501953125, 4224.7900390625, 4246.43994140625, 4241.83984375, 4266.490234375, 4280.7001953125, 4290.60986328125, 4291.7998046875, 4297.5, 4319.93994140625, 4352.33984375, 4343.5400390625, 4358.1298828125, 4320.81982421875, 4369.5498046875, 4384.6298828125, 4369.2099609375, 4374.2998046875, 4360.02978515625, 4327.16015625, 4258.490234375, 4323.06005859375, 4358.68994140625, 4367.47998046875, 4411.7900390625, 4422.2998046875, 4401.4599609375, 4400.64013671875, 4419.14990234375, 4395.259765625, 4387.16015625, 4423.14990234375, 4402.66015625, 4429.10009765625, 4436.52001953125, 4432.35009765625, 4436.75, 4442.41015625, 4460.830078125, 4468.0, 4479.7099609375, 4448.080078125, 4400.27001953125, 4405.7998046875, 4441.669921875, 4479.52978515625, 4486.22998046875, 4496.18994140625, 4470.0, 4509.3701171875, 4528.7900390625, 4522.68017578125, 4524.08984375, 4536.9501953125, 4535.43017578125, 4520.02978515625, 4514.06982421875, 4493.27978515625, 4458.580078125, 4468.72998046875, 4443.0498046875, 4480.7001953125, 4473.75, 4432.990234375, 4357.72998046875, 4354.18994140625, 4395.64013671875, 4448.97998046875, 4455.47998046875, 4443.10986328125, 4352.6298828125, 4359.4599609375, 4307.5400390625, 4357.0400390625, 4300.4599609375, 4345.72021484375, 4363.5498046875, 4399.759765625, 4391.33984375, 4361.18994140625, 4350.64990234375, 4363.7998046875, 4438.259765625, 4471.3701171875, 4486.4599609375, 4519.6298828125, 4536.18994140625, 4549.77978515625, 4544.89990234375, 4566.47998046875, 4574.7900390625, 4551.68017578125, 4596.419921875, 4605.3798828125, 4613.669921875, 4630.64990234375, 4660.56982421875, 4680.06005859375, 4697.52978515625, 4701.7001953125, 4685.25, 4646.7099609375, 4649.27001953125, 4682.85009765625, 4682.7998046875, 4700.89990234375, 4688.669921875, 4704.5400390625, 4697.9599609375, 4682.93994140625, 4690.7001953125, 4701.4599609375, 4594.6201171875, 4655.27001953125, 4567.0, 4513.0400390625, 4577.10009765625, 4538.43017578125, 4591.669921875, 4686.75, 4701.2099609375, 4667.4501953125, 4712.02001953125, 4668.97021484375, 4634.08984375, 4709.85009765625, 4668.669921875, 4620.64013671875, 4568.02001953125, 4649.22998046875, 4696.56005859375, 4725.7900390625, 4791.18994140625, 4786.35009765625, 4793.06005859375, 4778.72998046875, 4766.18017578125, 4796.56005859375, 4793.5400390625, 4700.580078125, 4696.0498046875, 4677.02978515625, 4670.2900390625, 4713.06982421875, 4726.35009765625, 4659.02978515625, 4662.85009765625, 4577.10986328125, 4532.759765625, 4482.72998046875, 4397.93994140625, 4410.1298828125, 4356.4501953125, 4349.93017578125, 4326.509765625, 4431.85009765625, 4515.5498046875, 4546.5400390625, 4589.3798828125, 4477.43994140625, 4500.52978515625, 4483.8701171875, 4521.5400390625, 4587.18017578125, 4504.080078125, 4418.64013671875, 4401.669921875, 4471.06982421875, 4475.009765625, 4380.259765625, 4348.8701171875, 4304.759765625, 4225.5, 4288.7001953125, 4384.64990234375, 4373.93994140625, 4306.259765625, 4386.5400390625, 4363.490234375, 4328.8701171875, 4201.08984375, 4170.7001953125, 4277.8798828125, 4259.52001953125, 4204.31005859375, 4173.10986328125, 4262.4501953125, 4357.85986328125, 4411.669921875, 4463.1201171875, 4461.18017578125, 4511.60986328125, 4456.240234375, 4520.16015625, 4543.06005859375, 4575.52001953125, 4631.60009765625, 4602.4501953125, 4530.41015625, 4545.85986328125, 4582.64013671875, 4525.1201171875, 4481.14990234375, 4500.2099609375, 4488.27978515625, 4412.52978515625, 4397.4501953125, 4446.58984375, 4392.58984375, 4391.68994140625, 4462.2099609375, 4459.4501953125, 4393.66015625, 4271.77978515625, 4296.1201171875, 4175.2001953125, 4183.9599609375, 4287.5, 4131.93017578125, 4155.3798828125, 4175.47998046875, 4300.169921875, 4146.8701171875, 4123.33984375, 3991.239990234375, 4001.050048828125, 3935.179931640625, 3930.080078125, 4023.889892578125, 4008.010009765625, 4088.85009765625, 3923.679931640625, 3900.7900390625, 3901.360107421875, 3973.75, 3941.47998046875, 3978.72998046875, 4057.840087890625, 4158.240234375, 4132.14990234375, 4101.22998046875, 4176.81982421875, 4108.5400390625, 4121.43017578125, 4160.68017578125, 4115.77001953125, 4017.820068359375, 3900.860107421875, 3749.6298828125, 3735.47998046875, 3789.9899</t>
+          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [3257.85009765625, 3234.85009765625, 3246.280029296875, 3237.179931640625, 3253.050048828125, 3274.699951171875, 3265.35009765625, 3288.1298828125, 3283.14990234375, 3289.2900390625, 3316.81005859375, 3329.6201171875, 3320.7900390625, 3321.75, 3325.5400390625, 3295.469970703125, 3243.6298828125, 3276.239990234375, 3273.39990234375, 3283.659912109375, 3225.52001953125, 3248.919921875, 3297.590087890625, 3334.68994140625, 3345.780029296875, 3327.7099609375, 3352.090087890625, 3357.75, 3379.449951171875, 3373.93994140625, 3380.159912109375, 3370.2900390625, 3386.14990234375, 3373.22998046875, 3337.75, 3225.889892578125, 3128.2099609375, 3116.389892578125, 2978.760009765625, 2954.219970703125, 3090.22998046875, 3003.3701171875, 3130.1201171875, 3023.93994140625, 2972.3701171875, 2746.56005859375, 2882.22998046875, 2741.3798828125, 2480.639892578125, 2711.02001953125, 2386.1298828125, 2529.18994140625, 2398.10009765625, 2409.389892578125, 2304.919921875, 2237.39990234375, 2447.330078125, 2475.56005859375, 2630.070068359375, 2541.469970703125, 2626.64990234375, 2584.590087890625, 2470.5, 2526.89990234375, 2488.64990234375, 2663.679931640625, 2659.409912109375, 2749.97998046875, 2789.820068359375, 2761.6298828125, 2846.06005859375, 2783.360107421875, 2799.550048828125, 2874.56005859375, 2823.159912109375, 2736.56005859375, 2799.31005859375, 2797.800048828125, 2836.739990234375, 2878.47998046875, 2863.389892578125, 2939.510009765625, 2912.429931640625, 2830.7099609375, 2842.739990234375, 2868.43994140625, 2848.419921875, 2881.18994140625, 2929.800048828125, 2930.18994140625, 2870.1201171875, 2820.0, 2852.5, 2863.699951171875, 2953.909912109375, 2922.93994140625, 2971.610107421875, 2948.510009765625, 2955.449951171875, 2991.77001953125, 3036.1298828125, 3029.72998046875, 3044.31005859375, 3055.72998046875, 3080.820068359375, 3122.8701171875, 3112.35009765625, 3193.929931640625, 3232.389892578125, 3207.179931640625, 3190.139892578125, 3002.10009765625, 3041.31005859375, 3066.590087890625, 3124.739990234375, 3113.489990234375, 3115.340087890625, 3097.739990234375, 3117.860107421875, 3131.2900390625, 3050.330078125, 3083.760009765625, 3009.050048828125, 3053.239990234375, 3100.2900390625, 3115.860107421875, 3130.010009765625, 3179.719970703125, 3145.320068359375, 3169.93994140625, 3152.050048828125, 3185.0400390625, 3155.219970703125, 3197.52001953125, 3226.56005859375, 3215.570068359375, 3224.72998046875, 3251.840087890625, 3257.300048828125, 3276.02001953125, 3235.659912109375, 3215.6298828125, 3239.409912109375, 3218.43994140625, 3258.43994140625, 3246.219970703125, 3271.1201171875, 3294.610107421875, 3306.510009765625, 3327.77001953125, 3349.159912109375, 3351.280029296875, 3360.469970703125, 3333.68994140625, 3380.35009765625, 3373.429931640625, 3372.85009765625, 3381.989990234375, 3389.780029296875, 3374.85009765625, 3385.510009765625, 3397.159912109375, 3431.280029296875, 3443.6201171875, 3478.72998046875, 3484.550048828125, 3508.010009765625, 3500.31005859375, 3526.64990234375, 3580.840087890625, 3455.06005859375, 3426.9599609375, 3331.840087890625, 3398.9599609375, 3339.18994140625, 3340.969970703125, 3383.5400390625, 3401.199951171875, 3385.489990234375, 3357.010009765625, 3319.469970703125, 3281.06005859375, 3315.570068359375, 3236.919921875, 3246.590087890625, 3298.4599609375, 3351.60009765625, 3335.469970703125, 3363.0, 3380.800048828125, 3348.419921875, 3408.60009765625, 3360.969970703125, 3419.43994140625, 3446.830078125, 3477.139892578125, 3534.219970703125, 3511.929931640625, 3488.669921875, 3483.340087890625, 3483.81005859375, 3426.919921875, 3443.1201171875, 3435.56005859375, 3453.489990234375, 3465.389892578125, 3400.969970703125, 3390.679931640625, 3271.030029296875, 3310.110107421875, 3269.9599609375, 3310.239990234375, 3369.159912109375, 3443.43994140625, 3510.449951171875, 3509.43994140625, 3550.5, 3545.530029296875, 3572.659912109375, 3537.010009765625, 3585.14990234375, 3626.909912109375, 3609.530029296875, 3567.7900390625, 3581.8701171875, 3557.5400390625, 3577.590087890625, 3635.409912109375, 3629.64990234375, 3638.35009765625, 3621.6298828125, 3662.449951171875, 3669.010009765625, 3666.719970703125, 3699.1201171875, 3691.9599609375, 3702.25, 3672.820068359375, 3668.10009765625, 3663.4599609375, 3647.489990234375, 3694.6201171875, 3701.169921875, 3722.47998046875, 3709.409912109375, 3694.919921875, 3687.260009765625, 3690.010009765625, 3703.06005859375, 3735.360107421875, 3727.0400390625, 3732.0400390625, 3756.070068359375, 3700.64990234375, 3726.860107421875, 3748.139892578125, 3803.7900390625, 3824.679931640625, 3799.610107421875, 3801.18994140625, 3809.840087890625, 3795.5400390625, 3768.25, 3798.909912109375, 3851.85009765625, 3853.070068359375, 3841.469970703125, 3855.360107421875, 3849.6201171875, 3750.77001953125, 3787.3798828125, 3714.239990234375, 3773.860107421875, 3826.31005859375, 3830.169921875, 3871.739990234375, 3886.830078125, 3915.590087890625, 3911.22998046875, 3909.8798828125, 3916.3798828125, 3934.830078125, 3932.590087890625, 3931.330078125, 3913.969970703125, 3906.7099609375, 3876.5, 3881.3701171875, 3925.429931640625, 3829.340087890625, 3811.14990234375, 3901.820068359375, 3870.2900390625, 3819.719970703125, 3768.469970703125, 3841.93994140625, 3821.35009765625, 3875.43994140625, 3898.81005859375, 3939.340087890625, 3943.340087890625, 3968.93994140625, 3962.7099609375, 3974.1201171875, 3915.4599609375, 3913.10009765625, 3940.590087890625, 3910.52001953125, 3889.139892578125, 3909.52001953125, 3974.5400390625, 3971.090087890625, 3958.550048828125, 3972.889892578125, 4019.8701171875, 4077.909912109375, 4073.93994140625, 4079.949951171875, 4097.169921875, 4128.7998046875, 4127.990234375, 4141.58984375, 4124.66015625, 4170.419921875, 4185.47021484375, 4163.259765625, 4134.93994140625, 4173.419921875, 4134.97998046875, 4180.169921875, 4187.6201171875, 4186.72021484375, 4183.18017578125, 4211.47021484375, 4181.169921875, 4192.66015625, 4164.66015625, 4167.58984375, 4201.6201171875, 4232.60009765625, 4188.43017578125, 4152.10009765625, 4063.0400390625, 4112.5, 4173.85009765625, 4163.2900390625, 4127.830078125, 4115.68017578125, 4159.1201171875, 4155.85986328125, 4197.0498046875, 4188.1298828125, 4195.990234375, 4200.8798828125, 4204.10986328125, 4202.0400390625, 4208.1201171875, 4192.85009765625, 4229.89013671875, 4226.52001953125, 4227.259765625, 4219.5498046875, 4239.18017578125, 4247.43994140625, 4255.14990234375, 4246.58984375, 4223.7001953125, 4221.85986328125, 4166.4501953125, 4224.7900390625, 4246.43994140625, 4241.83984375, 4266.490234375, 4280.7001953125, 4290.60986328125, 4291.7998046875, 4297.5, 4319.93994140625, 4352.33984375, 4343.5400390625, 4358.1298828125, 4320.81982421875, 4369.5498046875, 4384.6298828125, 4369.2099609375, 4374.2998046875, 4360.02978515625, 4327.16015625, 4258.490234375, 4323.06005859375, 4358.68994140625, 4367.47998046875, 4411.7900390625, 4422.2998046875, 4401.4599609375, 4400.64013671875, 4419.14990234375, 4395.259765625, 4387.16015625, 4423.14990234375, 4402.66015625, 4429.10009765625, 4436.52001953125, 4432.35009765625, 4436.75, 4442.41015625, 4460.830078125, 4468.0, 4479.7099609375, 4448.080078125, 4400.27001953125, 4405.7998046875, 4441.669921875, 4479.52978515625, 4486.22998046875, 4496.18994140625, 4470.0, 4509.3701171875, 4528.7900390625, 4522.68017578125, 4524.08984375, 4536.9501953125, 4535.43017578125, 4520.02978515625, 4514.06982421875, 4493.27978515625, 4458.580078125, 4468.72998046875, 4443.0498046875, 4480.7001953125, 4473.75, 4432.990234375, 4357.72998046875, 4354.18994140625, 4395.64013671875, 4448.97998046875, 4455.47998046875, 4443.10986328125, 4352.6298828125, 4359.4599609375, 4307.5400390625, 4357.0400390625, 4300.4599609375, 4345.72021484375, 4363.5498046875, 4399.759765625, 4391.33984375, 4361.18994140625, 4350.64990234375, 4363.7998046875, 4438.259765625, 4471.3701171875, 4486.4599609375, 4519.6298828125, 4536.18994140625, 4549.77978515625, 4544.89990234375, 4566.47998046875, 4574.7900390625, 4551.68017578125, 4596.419921875, 4605.3798828125, 4613.669921875, 4630.64990234375, 4660.56982421875, 4680.06005859375, 4697.52978515625, 4701.7001953125, 4685.25, 4646.7099609375, 4649.27001953125, 4682.85009765625, 4682.7998046875, 4700.89990234375, 4688.669921875, 4704.5400390625, 4697.9599609375, 4682.93994140625, 4690.7001953125, 4701.4599609375, 4594.6201171875, 4655.27001953125, 4567.0, 4513.0400390625, 4577.10009765625, 4538.43017578125, 4591.669921875, 4686.75, 4701.2099609375, 4667.4501953125, 4712.02001953125, 4668.97021484375, 4634.08984375, 4709.85009765625, 4668.669921875, 4620.64013671875, 4568.02001953125, 4649.22998046875, 4696.56005859375, 4725.7900390625, 4791.18994140625, 4786.35009765625, 4793.06005859375, 4778.72998046875, 4766.18017578125, 4796.56005859375, 4793.5400390625, 4700.580078125, 4696.0498046875, 4677.02978515625, 4670.2900390625, 4713.06982421875, 4726.35009765625, 4659.02978515625, 4662.85009765625, 4577.10986328125, 4532.759765625, 4482.72998046875, 4397.93994140625, 4410.1298828125, 4356.4501953125, 4349.93017578125, 4326.509765625, 4431.85009765625, 4515.5498046875, 4546.5400390625, 4589.3798828125, 4477.43994140625, 4500.52978515625, 4483.8701171875, 4521.5400390625, 4587.18017578125, 4504.080078125, 4418.64013671875, 4401.669921875, 4471.06982421875, 4475.009765625, 4380.259765625, 4348.8701171875, 4304.759765625, 4225.5, 4288.7001953125, 4384.64990234375, 4373.93994140625, 4306.259765625, 4386.5400390625, 4363.490234375, 4328.8701171875, 4201.08984375, 4170.7001953125, 4277.8798828125, 4259.52001953125, 4204.31005859375, 4173.10986328125, 4262.4501953125, 4357.85986328125, 4411.669921875, 4463.1201171875, 4461.18017578125, 4511.60986328125, 4456.240234375, 4520.16015625, 4543.06005859375, 4575.52001953125, 4631.60009765625, 4602.4501953125, 4530.41015625, 4545.85986328125, 4582.64013671875, 4525.1201171875, 4481.14990234375, 4500.2099609375, 4488.27978515625, 4412.52978515625, 4397.4501953125, 4446.58984375, 4392.58984375, 4391.68994140625, 4462.2099609375, 4459.4501953125, 4393.66015625, 4271.77978515625, 4296.1201171875, 4175.2001953125, 4183.9599609375, 4287.5, 4131.93017578125, 4155.3798828125, 4175.47998046875, 4300.169921875, 4146.8701171875, 4123.33984375, 3991.239990234375, 4001.050048828125, 3935.179931640625, 3930.080078125, 4023.889892578125, 4008.010009765625, 4088.85009765625, 3923.679931640625, 3900.7900390625, 3901.360107421875, 3973.75, 3941.47998046875, 3978.72998046875, 4057.840087890625, 4158.240234375, 4132.14990234375, 4101.22998046875, 4176.81982421875, 4108.54003906</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -1576,11 +1576,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21879.1796875</v>
+        <v>24468.48046875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1615,27 +1615,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1644,37 +1644,37 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>21987.946875</v>
+        <v>22376.621484375</v>
       </c>
       <c r="Q3" t="n">
-        <v>22763.03880208333</v>
+        <v>22711.51865234375</v>
       </c>
       <c r="R3" t="n">
-        <v>22971.70919596354</v>
+        <v>23011.915625</v>
       </c>
       <c r="S3" t="n">
-        <v>20985.78394505885</v>
+        <v>21103.43514737216</v>
       </c>
       <c r="T3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02'], 'prices': [9092.1904296875, 9020.76953125, 9071.4697265625, 9068.580078125, 9129.240234375, 9203.4296875, 9178.8603515625, 9273.9296875, 9251.330078125, 9258.7001953125, 9357.1298828125, 9388.9404296875, 9370.8095703125, 9383.76953125, 9402.48046875, 9314.91015625, 9139.3095703125, 9269.6796875, 9275.16015625, 9298.9296875, 9150.9404296875, 9273.400390625, 9467.9697265625, 9508.6796875, 9572.150390625, 9520.509765625, 9628.3896484375, 9638.9404296875, 9725.9599609375, 9711.9697265625, 9731.1796875, 9732.740234375, 9817.1796875, 9750.9697265625, 9576.58984375, 9221.2802734375, 8965.6103515625, 8980.7802734375, 8566.48046875, 8567.3701171875, 8952.169921875, 8684.08984375, 9018.08984375, 8738.58984375, 8575.6201171875, 7950.68017578125, 8344.25, 7952.0498046875, 7201.7998046875, 7874.8798828125, 6904.58984375, 7334.77978515625, 6989.83984375, 7150.580078125, 6879.52001953125, 6860.669921875, 7417.85986328125, 7384.2998046875, 7797.5400390625, 7502.3798828125, 7774.14990234375, 7700.10009765625, 7360.580078125, 7487.31005859375, 7373.080078125, 7913.240234375, 7887.259765625, 8090.89990234375, 8153.580078125, 8192.419921875, 8515.740234375, 8393.1796875, 8532.3603515625, 8650.1396484375, 8560.73046875, 8263.23046875, 8495.3798828125, 8494.75, 8634.51953125, 8730.16015625, 8607.73046875, 8914.7099609375, 8889.5498046875, 8604.9501953125, 8710.7099609375, 8809.1201171875, 8854.3896484375, 8979.66015625, 9121.3203125, 9192.33984375, 9002.5498046875, 8863.169921875, 8943.7197265625, 9014.5595703125, 9234.830078125, 9185.099609375, 9375.7802734375, 9284.8798828125, 9324.58984375, 9340.2197265625, 9412.3603515625, 9368.990234375, 9489.8701171875, 9552.0498046875, 9608.3798828125, 9682.91015625, 9615.8095703125, 9814.080078125, 9924.75, 9953.75, 10020.349609375, 9492.73046875, 9588.8095703125, 9726.01953125, 9895.8701171875, 9910.5302734375, 9943.0498046875, 9946.1201171875, 10056.48046875, 10131.3701171875, 9909.169921875, 10017.0, 9757.2197265625, 9874.150390625, 10058.76953125, 10154.6298828125, 10207.6298828125, 10433.650390625, 10343.8896484375, 10492.5, 10547.75, 10617.4404296875, 10390.83984375, 10488.580078125, 10550.490234375, 10473.830078125, 10503.1904296875, 10767.08984375, 10680.3603515625, 10706.1298828125, 10461.419921875, 10363.1796875, 10536.26953125, 10402.08984375, 10542.9404296875, 10587.8095703125, 10745.26953125, 10902.7998046875, 10941.169921875, 10998.400390625, 11108.0703125, 11010.98046875, 10968.3603515625, 10782.8203125, 11012.240234375, 11042.5, 11019.2998046875, 11129.73046875, 11210.83984375, 11146.4599609375, 11264.9501953125, 11311.7998046875, 11379.7197265625, 11466.4697265625, 11665.0595703125, 11625.33984375, 11695.6298828125, 11775.4599609375, 11939.669921875, 12056.4404296875, 11458.099609375, 11313.1298828125, 10847.6904296875, 11141.5595703125, 10919.58984375, 10853.5498046875, 11056.650390625, 11190.3203125, 11050.4697265625, 10910.2802734375, 10793.2802734375, 10778.7998046875, 10963.6396484375, 10632.990234375, 10672.26953125, 10913.5595703125, 11117.5302734375, 11085.25, 11167.509765625, 11326.509765625, 11075.01953125, 11332.490234375, 11154.599609375, 11364.599609375, 11420.98046875, 11579.9404296875, 11876.259765625, 11863.900390625, 11768.73046875, 11713.8701171875, 11671.5595703125, 11478.8798828125, 11516.490234375, 11484.6904296875, 11506.009765625, 11548.2802734375, 11358.9404296875, 11431.349609375, 11004.8701171875, 11185.58984375, 10911.58984375, 10957.6103515625, 11160.5703125, 11590.7802734375, 11890.9296875, 11895.23046875, 11713.7802734375, 11553.8603515625, 11786.4296875, 11709.58984375, 11829.2900390625, 11924.1298828125, 11899.33984375, 11801.599609375, 11904.7099609375, 11854.9697265625, 11880.6298828125, 12036.7900390625, 12094.400390625, 12205.849609375, 12198.740234375, 12355.1103515625, 12349.3701171875, 12377.1796875, 12464.23046875, 12519.9501953125, 12582.76953125, 12338.9501953125, 12405.8095703125, 12377.8701171875, 12440.0400390625, 12595.0595703125, 12658.1904296875, 12764.75, 12755.6396484375, 12742.51953125, 12807.919921875, 12771.1103515625, 12804.73046875, 12899.419921875, 12850.2197265625, 12870.0, 12888.2802734375, 12698.4501953125, 12818.9599609375, 12740.7900390625, 13067.48046875, 13201.98046875, 13036.4296875, 13072.4296875, 13128.9501953125, 13112.6396484375, 12998.5, 13197.1796875, 13457.25, 13530.91015625, 13543.0595703125, 13635.990234375, 13626.0595703125, 13270.599609375, 13337.16015625, 13070.6904296875, 13403.3896484375, 13612.7802734375, 13610.5400390625, 13777.740234375, 13856.2998046875, 13987.6396484375, 14007.7001953125, 13972.5302734375, 14025.76953125, 14095.4697265625, 14047.5, 13965.490234375, 13865.3603515625, 13874.4599609375, 13533.0498046875, 13465.2001953125, 13597.9697265625, 13119.4296875, 13192.349609375, 13588.830078125, 13358.7900390625, 12997.75, 12723.4697265625, 12920.150390625, 12609.16015625, 13073.8203125, 13068.830078125, 13398.669921875, 13319.8603515625, 13459.7099609375, 13471.5703125, 13525.2001953125, 13116.169921875, 13215.240234375, 13377.5400390625, 13227.7001953125, 12961.8896484375, 12977.6796875, 13138.73046875, 13059.650390625, 13045.3896484375, 13246.8701171875, 13480.1103515625, 13705.58984375, 13698.3798828125, 13688.83984375, 13829.3095703125, 13900.1904296875, 13850.0, 13996.099609375, 13857.83984375, 14038.759765625, 14052.33984375, 13914.76953125, 13786.26953125, 13950.2197265625, 13818.41015625, 14016.8095703125, 14138.7802734375, 14090.2197265625, 14051.0302734375, 14082.5498046875, 13962.6796875, 13895.1201171875, 13633.5, 13582.419921875, 13632.83984375, 13752.240234375, 13401.8603515625, 13389.4296875, 13031.6796875, 13124.990234375, 13429.98046875, 13379.0498046875, 13303.6396484375, 13299.740234375, 13535.740234375, 13470.990234375, 13661.169921875, 13657.169921875, 13738.0, 13736.2802734375, 13748.740234375, 13736.48046875, 13756.330078125, 13614.509765625, 13814.490234375, 13881.7197265625, 13924.91015625, 13911.75, 14020.330078125, 14069.419921875, 14174.1396484375, 14072.8603515625, 14039.6796875, 14161.349609375, 14030.3798828125, 14141.48046875, 14253.26953125, 14271.73046875, 14369.7099609375, 14360.3896484375, 14500.509765625, 14528.330078125, 14503.9501953125, 14522.3798828125, 14639.330078125, 14663.6396484375, 14665.0595703125, 14559.7802734375, 14701.919921875, 14733.240234375, 14677.650390625, 14644.9501953125, 14543.1298828125, 14427.240234375, 14274.98046875, 14498.8798828125, 14631.9501953125, 14684.599609375, 14836.990234375, 14840.7099609375, 14660.580078125, 14762.580078125, 14778.259765625, 14672.6796875, 14681.0703125, 14761.2900390625, 14780.5302734375, 14895.1201171875, 14835.759765625, 14860.1796875, 14788.08984375, 14765.1396484375, 14816.259765625, 14822.900390625, 14793.759765625, 14656.1796875, 14525.91015625, 14541.7900390625, 14714.66015625, 14942.650390625, 15019.7998046875, 15041.8603515625, 14945.8095703125, 15129.5, 15265.8896484375, 15259.240234375, 15309.3798828125, 15331.1796875, 15363.51953125, 15374.330078125, 15286.6396484375, 15248.25, 15115.490234375, 15105.580078125, 15037.759765625, 15161.5302734375, 15181.919921875, 15043.9697265625, 14713.900390625, 14746.400390625, 14896.849609375, 15052.240234375, 15047.7001953125, 14969.9697265625, 14546.6796875, 14512.4404296875, 14448.580078125, 14566.7001953125, 14255.48046875, 14433.830078125, 14501.91015625, 14654.01953125, 14579.5400390625, 14486.2001953125, 14465.919921875, 14571.6396484375, 14823.4296875, 14897.33984375, 15021.8095703125, 15129.08984375, 15121.6796875, 15215.7001953125, 15090.2001953125, 15226.7099609375, 15235.7099609375, 15235.83984375, 15448.1201171875, 15498.3896484375, 15595.919921875, 15649.599609375, 15811.580078125, 15940.3095703125, 15971.58984375, 15982.3603515625, 15886.5400390625, 15622.7099609375, 15704.2802734375, 15860.9599609375, 15853.849609375, 15973.8603515625, 15921.5703125, 15993.7099609375, 16057.4404296875, 15854.759765625, 15775.1396484375, 15845.23046875, 15491.66015625, 15782.830078125, 15537.6904296875, 15254.0498046875, 15381.3203125, 15085.4697265625, 15225.150390625, 15686.919921875, 15786.990234375, 15517.3701171875, 15630.599609375, 15413.2802734375, 15237.6396484375, 15565.580078125, 15180.4296875, 15169.6796875, 14980.9404296875, 15341.08984375, 15521.8896484375, 15653.3701171875, 15871.259765625, 15781.7197265625, 15766.2197265625, 15741.5595703125, 15644.9697265625, 15832.7998046875, 15622.7197265625, 15100.169921875, 15080.8603515625, 14935.900390625, 14942.830078125, 15153.4501953125, 15188.3896484375, 14806.8095703125, 14893.75, 14506.900390625, 14340.259765625, 14154.01953125, 13768.919921875, 13855.1298828125, 13539.2900390625, 13542.1201171875, 13352.7802734375, 13770.5703125, 14239.8798828125, 14346.0, 14417.5498046875, 13878.8203125, 14098.009765625, 14015.669921875, 14194.4501953125, 14490.3701171875, 14185.6396484375, 13791.150390625, 13790.919921875, 14139.759765625, 14124.08984375, 13716.7197265625, 13548.0703125, 13381.51953125, 13037.490234375, 13473.58984375, 13694.6201171875, 13751.400390625, 13532.4599609375, 13752.01953125, 13537.9404296875, 13313.4404296875, 12830.9599609375, 12795.5498046875, 13255.5498046875, 13129.9599609375, 12843.8095703125, 12581.2197265625, 12948.6201171875, 13436.5498046875, 13614.7802734375, 13893.83984375, 13838.4599609375, 14108.8203125, 13922.599609375, 14191.83984375, 14169.2998046875, 14354.900390625, 14619.6396484375, 14442.26953125, 14220.51953125, 14261.5, 14532.5498046875, 14204.169921875, 13888.8203125, 13897.2998046875, 13711.0, 13411.9599609375, 13371.5703125, 13643.58984375, 13351.080078125, 13332.3603515625, 13619.66015625, 13453.0703125, 13174.650390625, 12839.2900390625, 13004.849609375, 12490.740234375, 12488.9296875, 12871.5302734375, 12334.6396484375, 12536.01953125, 12563.759765625, 12964.8603515625, 12317.6904296875, 12144.66015625, 11623.25, 11737.669921875, 11364.240234375, 11370.9599609375, 11805.0, 11662.7900390625, 11984.51953125, 11418.150390625, 11388.5, 11354.6201171875, 11535.26953125, 11264.4501953125, 11434.740234375, 11740.650390625, 12131.1298828125, 12081.3896484375, 11994.4599609375, 12316.900390625, 12012.73046875, 12061.3701171875, 12175.23046875, 12086.26953125, 11754.23046875, 11340.01953125, 10809.23046875, 10828.349609375, 11099.150390625, 10646.099609375, 10798.349609375, 11069.2998046875, 11053.080078125, 11232.1904296875, 11607.6201171875, 11524.5498046875, 11181.5400390625, 11177.8896484375, 11028.740234375, 11127.849609375, 11322.240234375, 11361.849609375, 11621.349609375, 11635.3095703125, 11372.599609375, 11264.73046875, 11247.580078125, 11251.1904296875, 11452.419921875, 11360.0498046875, 11713.150390625, 11897.650390625, 12059.6103515625, 11834.1103515625, 11782.669921875, 11562.5703125,</t>
+          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-01', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-01', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-12', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-12', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-05', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [9092.1904296875, 9020.76953125, 9071.4697265625, 9068.580078125, 9129.240234375, 9203.4296875, 9178.8603515625, 9273.9296875, 9251.330078125, 9258.7001953125, 9357.1298828125, 9388.9404296875, 9370.8095703125, 9383.76953125, 9402.48046875, 9314.91015625, 9139.3095703125, 9269.6796875, 9275.16015625, 9298.9296875, 9150.9404296875, 9273.400390625, 9467.9697265625, 9508.6796875, 9572.150390625, 9520.509765625, 9628.3896484375, 9638.9404296875, 9725.9599609375, 9711.9697265625, 9731.1796875, 9732.740234375, 9817.1796875, 9750.9697265625, 9576.58984375, 9221.2802734375, 8965.6103515625, 8980.7802734375, 8566.48046875, 8567.3701171875, 8952.169921875, 8684.08984375, 9018.08984375, 8738.58984375, 8575.6201171875, 7950.68017578125, 8344.25, 7952.0498046875, 7201.7998046875, 7874.8798828125, 6904.58984375, 7334.77978515625, 6989.83984375, 7150.580078125, 6879.52001953125, 6860.669921875, 7417.85986328125, 7384.2998046875, 7797.5400390625, 7502.3798828125, 7774.14990234375, 7700.10009765625, 7360.580078125, 7487.31005859375, 7373.080078125, 7913.240234375, 7887.259765625, 8090.89990234375, 8153.580078125, 8192.419921875, 8515.740234375, 8393.1796875, 8532.3603515625, 8650.1396484375, 8560.73046875, 8263.23046875, 8495.3798828125, 8494.75, 8634.51953125, 8730.16015625, 8607.73046875, 8914.7099609375, 8889.5498046875, 8604.9501953125, 8710.7099609375, 8809.1201171875, 8854.3896484375, 8979.66015625, 9121.3203125, 9192.33984375, 9002.5498046875, 8863.169921875, 8943.7197265625, 9014.5595703125, 9234.830078125, 9185.099609375, 9375.7802734375, 9284.8798828125, 9324.58984375, 9340.2197265625, 9412.3603515625, 9368.990234375, 9489.8701171875, 9552.0498046875, 9608.3798828125, 9682.91015625, 9615.8095703125, 9814.080078125, 9924.75, 9953.75, 10020.349609375, 9492.73046875, 9588.8095703125, 9726.01953125, 9895.8701171875, 9910.5302734375, 9943.0498046875, 9946.1201171875, 10056.48046875, 10131.3701171875, 9909.169921875, 10017.0, 9757.2197265625, 9874.150390625, 10058.76953125, 10154.6298828125, 10207.6298828125, 10433.650390625, 10343.8896484375, 10492.5, 10547.75, 10617.4404296875, 10390.83984375, 10488.580078125, 10550.490234375, 10473.830078125, 10503.1904296875, 10767.08984375, 10680.3603515625, 10706.1298828125, 10461.419921875, 10363.1796875, 10536.26953125, 10402.08984375, 10542.9404296875, 10587.8095703125, 10745.26953125, 10902.7998046875, 10941.169921875, 10998.400390625, 11108.0703125, 11010.98046875, 10968.3603515625, 10782.8203125, 11012.240234375, 11042.5, 11019.2998046875, 11129.73046875, 11210.83984375, 11146.4599609375, 11264.9501953125, 11311.7998046875, 11379.7197265625, 11466.4697265625, 11665.0595703125, 11625.33984375, 11695.6298828125, 11775.4599609375, 11939.669921875, 12056.4404296875, 11458.099609375, 11313.1298828125, 10847.6904296875, 11141.5595703125, 10919.58984375, 10853.5498046875, 11056.650390625, 11190.3203125, 11050.4697265625, 10910.2802734375, 10793.2802734375, 10778.7998046875, 10963.6396484375, 10632.990234375, 10672.26953125, 10913.5595703125, 11117.5302734375, 11085.25, 11167.509765625, 11326.509765625, 11075.01953125, 11332.490234375, 11154.599609375, 11364.599609375, 11420.98046875, 11579.9404296875, 11876.259765625, 11863.900390625, 11768.73046875, 11713.8701171875, 11671.5595703125, 11478.8798828125, 11516.490234375, 11484.6904296875, 11506.009765625, 11548.2802734375, 11358.9404296875, 11431.349609375, 11004.8701171875, 11185.58984375, 10911.58984375, 10957.6103515625, 11160.5703125, 11590.7802734375, 11890.9296875, 11895.23046875, 11713.7802734375, 11553.8603515625, 11786.4296875, 11709.58984375, 11829.2900390625, 11924.1298828125, 11899.33984375, 11801.599609375, 11904.7099609375, 11854.9697265625, 11880.6298828125, 12036.7900390625, 12094.400390625, 12205.849609375, 12198.740234375, 12355.1103515625, 12349.3701171875, 12377.1796875, 12464.23046875, 12519.9501953125, 12582.76953125, 12338.9501953125, 12405.8095703125, 12377.8701171875, 12440.0400390625, 12595.0595703125, 12658.1904296875, 12764.75, 12755.6396484375, 12742.51953125, 12807.919921875, 12771.1103515625, 12804.73046875, 12899.419921875, 12850.2197265625, 12870.0, 12888.2802734375, 12698.4501953125, 12818.9599609375, 12740.7900390625, 13067.48046875, 13201.98046875, 13036.4296875, 13072.4296875, 13128.9501953125, 13112.6396484375, 12998.5, 13197.1796875, 13457.25, 13530.91015625, 13543.0595703125, 13635.990234375, 13626.0595703125, 13270.599609375, 13337.16015625, 13070.6904296875, 13403.3896484375, 13612.7802734375, 13610.5400390625, 13777.740234375, 13856.2998046875, 13987.6396484375, 14007.7001953125, 13972.5302734375, 14025.76953125, 14095.4697265625, 14047.5, 13965.490234375, 13865.3603515625, 13874.4599609375, 13533.0498046875, 13465.2001953125, 13597.9697265625, 13119.4296875, 13192.349609375, 13588.830078125, 13358.7900390625, 12997.75, 12723.4697265625, 12920.150390625, 12609.16015625, 13073.8203125, 13068.830078125, 13398.669921875, 13319.8603515625, 13459.7099609375, 13471.5703125, 13525.2001953125, 13116.169921875, 13215.240234375, 13377.5400390625, 13227.7001953125, 12961.8896484375, 12977.6796875, 13138.73046875, 13059.650390625, 13045.3896484375, 13246.8701171875, 13480.1103515625, 13705.58984375, 13698.3798828125, 13688.83984375, 13829.3095703125, 13900.1904296875, 13850.0, 13996.099609375, 13857.83984375, 14038.759765625, 14052.33984375, 13914.76953125, 13786.26953125, 13950.2197265625, 13818.41015625, 14016.8095703125, 14138.7802734375, 14090.2197265625, 14051.0302734375, 14082.5498046875, 13962.6796875, 13895.1201171875, 13633.5, 13582.419921875, 13632.83984375, 13752.240234375, 13401.8603515625, 13389.4296875, 13031.6796875, 13124.990234375, 13429.98046875, 13379.0498046875, 13303.6396484375, 13299.740234375, 13535.740234375, 13470.990234375, 13661.169921875, 13657.169921875, 13738.0, 13736.2802734375, 13748.740234375, 13736.48046875, 13756.330078125, 13614.509765625, 13814.490234375, 13881.7197265625, 13924.91015625, 13911.75, 14020.330078125, 14069.419921875, 14174.1396484375, 14072.8603515625, 14039.6796875, 14161.349609375, 14030.3798828125, 14141.48046875, 14253.26953125, 14271.73046875, 14369.7099609375, 14360.3896484375, 14500.509765625, 14528.330078125, 14503.9501953125, 14522.3798828125, 14639.330078125, 14663.6396484375, 14665.0595703125, 14559.7802734375, 14701.919921875, 14733.240234375, 14677.650390625, 14644.9501953125, 14543.1298828125, 14427.240234375, 14274.98046875, 14498.8798828125, 14631.9501953125, 14684.599609375, 14836.990234375, 14840.7099609375, 14660.580078125, 14762.580078125, 14778.259765625, 14672.6796875, 14681.0703125, 14761.2900390625, 14780.5302734375, 14895.1201171875, 14835.759765625, 14860.1796875, 14788.08984375, 14765.1396484375, 14816.259765625, 14822.900390625, 14793.759765625, 14656.1796875, 14525.91015625, 14541.7900390625, 14714.66015625, 14942.650390625, 15019.7998046875, 15041.8603515625, 14945.8095703125, 15129.5, 15265.8896484375, 15259.240234375, 15309.3798828125, 15331.1796875, 15363.51953125, 15374.330078125, 15286.6396484375, 15248.25, 15115.490234375, 15105.580078125, 15037.759765625, 15161.5302734375, 15181.919921875, 15043.9697265625, 14713.900390625, 14746.400390625, 14896.849609375, 15052.240234375, 15047.7001953125, 14969.9697265625, 14546.6796875, 14512.4404296875, 14448.580078125, 14566.7001953125, 14255.48046875, 14433.830078125, 14501.91015625, 14654.01953125, 14579.5400390625, 14486.2001953125, 14465.919921875, 14571.6396484375, 14823.4296875, 14897.33984375, 15021.8095703125, 15129.08984375, 15121.6796875, 15215.7001953125, 15090.2001953125, 15226.7099609375, 15235.7099609375, 15235.83984375, 15448.1201171875, 15498.3896484375, 15595.919921875, 15649.599609375, 15811.580078125, 15940.3095703125, 15971.58984375, 15982.3603515625, 15886.5400390625, 15622.7099609375, 15704.2802734375, 15860.9599609375, 15853.849609375, 15973.8603515625, 15921.5703125, 15993.7099609375, 16057.4404296875, 15854.759765625, 15775.1396484375, 15845.23046875, 15491.66015625, 15782.830078125, 15537.6904296875, 15254.0498046875, 15381.3203125, 15085.4697265625, 15225.150390625, 15686.919921875, 15786.990234375, 15517.3701171875, 15630.599609375, 15413.2802734375, 15237.6396484375, 15565.580078125, 15180.4296875, 15169.6796875, 14980.9404296875, 15341.08984375, 15521.8896484375, 15653.3701171875, 15871.259765625, 15781.7197265625, 15766.2197265625, 15741.5595703125, 15644.9697265625, 15832.7998046875, 15622.7197265625, 15100.169921875, 15080.8603515625, 14935.900390625, 14942.830078125, 15153.4501953125, 15188.3896484375, 14806.8095703125, 14893.75, 14506.900390625, 14340.259765625, 14154.01953125, 13768.919921875, 13855.1298828125, 13539.2900390625, 13542.1201171875, 13352.7802734375, 13770.5703125, 14239.8798828125, 14346.0, 14417.5498046875, 13878.8203125, 14098.009765625, 14015.669921875, 14194.4501953125, 14490.3701171875, 14185.6396484375, 13791.150390625, 13790.919921875, 14139.759765625, 14124.08984375, 13716.7197265625, 13548.0703125, 13381.51953125, 13037.490234375, 13473.58984375, 13694.6201171875, 13751.400390625, 13532.4599609375, 13752.01953125, 13537.9404296875, 13313.4404296875, 12830.9599609375, 12795.5498046875, 13255.5498046875, 13129.9599609375, 12843.8095703125, 12581.2197265625, 12948.6201171875, 13436.5498046875, 13614.7802734375, 13893.83984375, 13838.4599609375, 14108.8203125, 13922.599609375, 14191.83984375, 14169.2998046875, 14354.900390625, 14619.6396484375, 14442.26953125, 14220.51953125, 14261.5, 14532.5498046875, 14204.169921875, 13888.8203125, 13897.2998046875, 13711.0, 13411.9599609375, 13371.5703125, 13643.58984375, 13351.080078125, 13332.3603515625, 13619.66015625, 13453.0703125, 13174.650390625, 12839.2900390625, 13004.849609375, 12490.740234375, 12488.9296875, 12871.5302734375, 12334.6396484375, 12536.01953125, 12563.759765625, 12964.8603515625, 12317.6904296875, 12144.66015625, 11623.25, 11737.669921875, 11364.240234375, 11370.9599609375, 11805.0, 11662.7900390625, 11984.51953125, 11418.150390625, 11388.5, 11354.6201171875, 11535.26953125, 11264.4501953125, 11434.740234375, 11740.650390625, 12131.1298828125, 12081.3896484375, 11994.4599609375, 12316.900390625, 12012.73046875, 12061.3701171875, 12175.23046875, 12086.26953125, 11754.23046875, 11340.01953125, 10809.23046875, 10828.349609375, 11099.150390625, 10646.099609375, 10798.349609375, 11069.2998046875, 11053.080078125, 11232.1904296875, 11607.6201171875, 11524.5498046875, 11181.5400390625, 11177.8896484375, 11028.740234375, 11127.849609375, 11322.240234375, 11361.849609375, 11621.349609375, 11635.3095703125, 11372.599609375, 11264.73046875, 11247.580078125, 11251.19042968</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -1685,11 +1685,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5377.2998046875</v>
+        <v>6191.919921875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1724,27 +1724,27 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>-3.0%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>5.7%</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-2.6%</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>5502.285009765625</v>
+        <v>5633.053955078125</v>
       </c>
       <c r="Q4" t="n">
-        <v>5317.826668294271</v>
+        <v>5516.849153645833</v>
       </c>
       <c r="R4" t="n">
-        <v>4658.613094075521</v>
+        <v>4839.922589111328</v>
       </c>
       <c r="S4" t="n">
-        <v>3542.340817141842</v>
+        <v>3653.38321913682</v>
       </c>
       <c r="T4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="b">
         <v>1</v>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-10', '2020-04-13', '2020-04-14', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-05-04', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-03', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-15', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-02', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-21', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-15', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-06', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-30', '2022-05-31', '2022-06-02', '2022-06-03', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-24', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-26', '2022-12-27', '2022-12-28', '2022-12-29', '2023-01-02', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-07', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-03-29', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-02', '2024-05-03', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-02', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-18', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-02', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-04', '2025-06-05', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-03'], 'prices': [2175.169921875, 2176.4599609375, 2155.070068359375, 2175.5400390625, 2151.31005859375, 2186.449951171875, 2206.389892578125, 2229.260009765625, 2238.8798828125, 2230.97998046875, 2248.050048828125, 2250.570068359375, 2262.639892578125, 2239.68994140625, 2267.25, 2246.1298828125, 2176.719970703125, 2185.280029296875, 2148.0, 2119.010009765625, 2118.8798828125, 2157.89990234375, 2165.6298828125, 2227.93994140625, 2211.949951171875, 2201.070068359375, 2223.1201171875, 2238.3798828125, 2232.9599609375, 2243.590087890625, 2242.169921875, 2208.8798828125, 2210.340087890625, 2195.5, 2162.840087890625, 2079.0400390625, 2103.610107421875, 2076.77001953125, 2054.889892578125, 1987.010009765625, 2002.510009765625, 2014.1500244140625, 2059.330078125, 2085.260009765625, 2040.219970703125, 1954.77001953125, 1962.9300537109375, 1908.27001953125, 1834.3299560546875, 1771.43994140625, 1714.8599853515625, 1672.43994140625, 1591.199951171875, 1457.6400146484375, 1566.1500244140625, 1482.4599609375, 1609.969970703125, 1704.760009765625, 1686.239990234375, 1717.72998046875, 1717.1199951171875, 1754.6400146484375, 1685.4599609375, 1724.8599853515625, 1725.43994140625, 1791.8800048828125, 1823.5999755859375, 1807.1400146484375, 1836.2099609375, 1860.699951171875, 1825.760009765625, 1857.0799560546875, 1857.0699462890625, 1914.530029296875, 1898.3599853515625, 1879.3800048828125, 1896.1500244140625, 1914.72998046875, 1889.010009765625, 1922.77001953125, 1934.0899658203125, 1947.56005859375, 1895.3699951171875, 1928.760009765625, 1928.6099853515625, 1945.8199462890625, 1935.4000244140625, 1922.1700439453125, 1940.4200439453125, 1924.9599609375, 1927.280029296875, 1937.1099853515625, 1980.6099853515625, 1989.6400146484375, 1998.31005859375, 1970.1300048828125, 1994.5999755859375, 2029.780029296875, 2031.199951171875, 2028.5400390625, 2029.5999755859375, 2065.080078125, 2087.18994140625, 2147.0, 2151.179931640625, 2181.8701171875, 2184.2900390625, 2188.919921875, 2195.68994140625, 2176.780029296875, 2132.300048828125, 2030.8199462890625, 2138.050048828125, 2141.050048828125, 2133.47998046875, 2141.320068359375, 2126.72998046875, 2131.239990234375, 2161.510009765625, 2112.3701171875, 2134.64990234375, 2093.47998046875, 2108.330078125, 2106.699951171875, 2135.3701171875, 2152.409912109375, 2187.929931640625, 2164.169921875, 2158.8798828125, 2167.89990234375, 2150.25, 2186.06005859375, 2183.610107421875, 2201.8798828125, 2183.760009765625, 2201.18994140625, 2198.199951171875, 2228.830078125, 2228.659912109375, 2216.18994140625, 2200.43994140625, 2217.860107421875, 2256.989990234375, 2263.159912109375, 2267.010009765625, 2249.3701171875, 2251.0400390625, 2279.969970703125, 2311.860107421875, 2342.610107421875, 2351.669921875, 2386.3798828125, 2418.669921875, 2432.35009765625, 2437.530029296875, 2407.489990234375, 2348.239990234375, 2360.5400390625, 2274.219970703125, 2304.590087890625, 2329.830078125, 2366.72998046875, 2369.320068359375, 2344.449951171875, 2353.800048828125, 2326.169921875, 2349.550048828125, 2364.3701171875, 2395.89990234375, 2368.25, 2384.219970703125, 2401.909912109375, 2375.81005859375, 2396.47998046875, 2396.68994140625, 2427.909912109375, 2443.580078125, 2435.919921875, 2406.169921875, 2412.39990234375, 2389.389892578125, 2332.590087890625, 2333.239990234375, 2272.699951171875, 2278.7900390625, 2308.080078125, 2327.889892578125, 2358.0, 2365.89990234375, 2386.93994140625, 2391.9599609375, 2403.72998046875, 2403.14990234375, 2380.47998046875, 2361.2099609375, 2341.530029296875, 2346.739990234375, 2358.409912109375, 2370.860107421875, 2355.050048828125, 2360.81005859375, 2343.909912109375, 2330.840087890625, 2345.260009765625, 2326.669921875, 2267.14990234375, 2300.159912109375, 2343.31005859375, 2357.320068359375, 2413.7900390625, 2416.5, 2447.199951171875, 2452.830078125, 2485.8701171875, 2475.6201171875, 2493.8701171875, 2543.030029296875, 2539.14990234375, 2545.639892578125, 2547.419921875, 2553.5, 2602.590087890625, 2617.760009765625, 2601.5400390625, 2625.909912109375, 2633.449951171875, 2591.340087890625, 2634.25, 2675.89990234375, 2696.219970703125, 2731.449951171875, 2745.43994140625, 2700.929931640625, 2755.469970703125, 2746.4599609375, 2770.06005859375, 2762.199951171875, 2756.820068359375, 2771.7900390625, 2770.429931640625, 2772.179931640625, 2778.64990234375, 2733.679931640625, 2759.820068359375, 2806.860107421875, 2808.60009765625, 2820.510009765625, 2873.469970703125, 2944.449951171875, 2990.570068359375, 2968.2099609375, 3031.679931640625, 3152.179931640625, 3148.449951171875, 3125.949951171875, 3148.2900390625, 3149.929931640625, 3085.89990234375, 3013.929931640625, 3092.659912109375, 3114.550048828125, 3160.840087890625, 3140.6298828125, 3208.989990234375, 3140.31005859375, 3122.56005859375, 3069.050048828125, 2976.2099609375, 3056.530029296875, 3096.81005859375, 3129.679931640625, 3087.550048828125, 3120.6298828125, 3091.239990234375, 3084.669921875, 3100.580078125, 3147.0, 3163.25, 3133.72998046875, 3086.659912109375, 3107.6201171875, 3079.75, 3070.090087890625, 2994.97998046875, 3099.68994140625, 3012.949951171875, 3043.8701171875, 3082.989990234375, 3043.489990234375, 3026.260009765625, 2996.110107421875, 2976.1201171875, 2958.1201171875, 3013.699951171875, 3054.389892578125, 3045.7099609375, 3067.169921875, 3047.5, 3066.010009765625, 3039.530029296875, 3035.4599609375, 3004.739990234375, 2996.35009765625, 3008.330078125, 3041.010009765625, 3036.0400390625, 3070.0, 3061.419921875, 3087.39990234375, 3112.800048828125, 3120.830078125, 3127.080078125, 3137.409912109375, 3143.260009765625, 3131.8798828125, 3135.590087890625, 3169.080078125, 3182.3798828125, 3194.330078125, 3198.6201171875, 3198.840087890625, 3220.699951171875, 3171.659912109375, 3177.52001953125, 3181.080078125, 3217.530029296875, 3215.419921875, 3181.469970703125, 3174.070068359375, 3147.860107421875, 3127.199951171875, 3147.3701171875, 3160.429931640625, 3197.199951171875, 3249.300048828125, 3209.429931640625, 3161.659912109375, 3122.110107421875, 3153.320068359375, 3134.52001953125, 3173.050048828125, 3162.280029296875, 3156.419921875, 3144.300048828125, 3171.320068359375, 3168.429931640625, 3165.510009765625, 3188.72998046875, 3203.919921875, 3221.8701171875, 3224.22998046875, 3247.429931640625, 3240.080078125, 3252.1201171875, 3247.830078125, 3216.179931640625, 3224.639892578125, 3249.320068359375, 3252.1298828125, 3258.6298828125, 3278.679931640625, 3264.9599609375, 3267.929931640625, 3240.7900390625, 3263.8798828125, 3276.18994140625, 3286.10009765625, 3302.840087890625, 3301.889892578125, 3286.679931640625, 3296.679931640625, 3282.06005859375, 3281.780029296875, 3293.2099609375, 3305.2099609375, 3285.340087890625, 3252.679931640625, 3217.949951171875, 3246.469970703125, 3271.3798828125, 3264.81005859375, 3286.219970703125, 3276.909912109375, 3244.0400390625, 3232.699951171875, 3215.909912109375, 3250.2099609375, 3254.419921875, 3224.949951171875, 3232.530029296875, 3236.860107421875, 3242.64990234375, 3202.320068359375, 3223.0400390625, 3237.139892578125, 3280.3798828125, 3276.1298828125, 3270.360107421875, 3260.419921875, 3243.18994140625, 3220.6201171875, 3208.3798828125, 3171.2900390625, 3143.090087890625, 3158.929931640625, 3097.830078125, 3060.510009765625, 3090.2099609375, 3138.300048828125, 3146.81005859375, 3128.530029296875, 3133.89990234375, 3144.18994140625, 3199.27001953125, 3207.02001953125, 3175.85009765625, 3201.06005859375, 3203.330078125, 3187.419921875, 3162.989990234375, 3114.699951171875, 3125.760009765625, 3127.860107421875, 3148.830078125, 3153.39990234375, 3130.090087890625, 3140.510009765625, 3127.580078125, 3125.239990234375, 3133.639892578125, 3097.919921875, 3060.27001953125, 3068.820068359375, 3019.179931640625, 2962.169921875, 2908.31005859375, 2959.4599609375, 2956.300048828125, 2916.3798828125, 2944.409912109375, 2988.639892578125, 3015.06005859375, 3006.679931640625, 3029.0400390625, 3013.1298828125, 3007.330078125, 3006.159912109375, 3020.5400390625, 3049.080078125, 3025.489990234375, 3009.550048828125, 2970.679931640625, 2978.93994140625, 3013.489990234375, 2975.7099609375, 2983.219970703125, 2969.27001953125, 2960.199951171875, 2962.4599609375, 2930.169921875, 2924.919921875, 2968.800048828125, 2999.52001953125, 2997.2099609375, 2962.419921875, 2947.3798828125, 2971.02001953125, 3013.25, 2997.330078125, 2994.2900390625, 2980.27001953125, 2936.43994140625, 2909.320068359375, 2839.010009765625, 2899.719970703125, 2945.27001953125, 2968.330078125, 2973.25, 2991.719970703125, 3001.800048828125, 3029.570068359375, 3010.22998046875, 3001.659912109375, 2987.949951171875, 2989.389892578125, 3006.409912109375, 3017.72998046875, 2963.0, 2975.030029296875, 2984.47998046875, 2998.169921875, 3012.429931640625, 2999.550048828125, 3020.239990234375, 2993.2900390625, 2977.64990234375, 2989.239990234375, 2953.969970703125, 2920.530029296875, 2954.889892578125, 2926.719970703125, 2927.3798828125, 2972.47998046875, 2962.090087890625, 2921.919921875, 2890.10009765625, 2864.239990234375, 2842.280029296875, 2862.679931640625, 2834.2900390625, 2792.0, 2720.389892578125, 2709.239990234375, 2614.489990234375, 2663.340087890625, 2707.820068359375, 2750.260009765625, 2745.06005859375, 2746.469970703125, 2768.85009765625, 2771.929931640625, 2747.7099609375, 2704.47998046875, 2676.5400390625, 2729.679931640625, 2744.090087890625, 2744.52001953125, 2743.800048828125, 2706.7900390625, 2719.530029296875, 2648.800048828125, 2676.760009765625, 2699.179931640625, 2703.52001953125, 2747.080078125, 2713.429931640625, 2651.31005859375, 2622.39990234375, 2680.320068359375, 2661.280029296875, 2645.64990234375, 2621.530029296875, 2659.22998046875, 2694.510009765625, 2707.02001953125, 2686.050048828125, 2710.0, 2735.050048828125, 2729.659912109375, 2729.97998046875, 2729.56005859375, 2741.070068359375, 2746.739990234375, 2757.64990234375, 2739.85009765625, 2757.89990234375, 2759.199951171875, 2735.030029296875, 2695.860107421875, 2700.389892578125, 2693.10009765625, 2666.760009765625, 2716.489990234375, 2716.7099609375, 2696.06005859375, 2693.2099609375, 2718.889892578125, 2718.68994140625, 2728.2099609375, 2704.7099609375, 2657.1298828125, 2668.31005859375, 2639.06005859375, 2667.489990234375, 2695.050048828125, 2687.449951171875, 2680.4599609375, 2677.570068359375, 2644.510009765625, 2596.56005859375, 2592.27001953125, 2550.080078125, 2604.239990234375, 2596.580078125, 2620.43994140625, 2625.97998046875, 2592.340087890625, 2639.2900390625, 2647.3798828125, 2605.8701171875, 2617.219970703125, 2612.449951171875, 2638.050048828125, 2669.659912109375, 2685.89990234375, 2658.989990234375, 2670.64990234375, 2626.340087890625, 2626.14990234375, 2625.43994140625, 2595.8701171875, 2504.510009765625, 2492.969970703125, 2447.3798828125, 2451.409912109375, 2440.929931640625, 2391.030029296875, 2408.929931640625, 2342.81005859375, 2314.320068359375, 2366.60009765625, 2401.919921875, 2422.090087890625, 2377.989990234375, 2332.639892578125, 2305.419921875, 2300.340087890625, 2341.780029296875, 2292.010009765625, 2334.27001953125, 2350.610107421875, 2340.27001953125, 2317.760009765625, 2328.610107421875, 2322.320068359375, 2330.97998046875, 2375.25, 2370.969970703125, 2386.85009765625, 2409.15991210937</t>
+          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-10', '2020-04-13', '2020-04-14', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-05-04', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-03', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-15', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-02', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-21', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-15', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-06', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-30', '2022-05-31', '2022-06-02', '2022-06-03', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-24', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-26', '2022-12-27', '2022-12-28', '2022-12-29', '2023-01-02', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-07', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-03-29', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-02', '2024-05-03', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-02', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-18', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-02', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-04', '2025-06-05', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-03', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [2175.169921875, 2176.4599609375, 2155.070068359375, 2175.5400390625, 2151.31005859375, 2186.449951171875, 2206.389892578125, 2229.260009765625, 2238.8798828125, 2230.97998046875, 2248.050048828125, 2250.570068359375, 2262.639892578125, 2239.68994140625, 2267.25, 2246.1298828125, 2176.719970703125, 2185.280029296875, 2148.0, 2119.010009765625, 2118.8798828125, 2157.89990234375, 2165.6298828125, 2227.93994140625, 2211.949951171875, 2201.070068359375, 2223.1201171875, 2238.3798828125, 2232.9599609375, 2243.590087890625, 2242.169921875, 2208.8798828125, 2210.340087890625, 2195.5, 2162.840087890625, 2079.0400390625, 2103.610107421875, 2076.77001953125, 2054.889892578125, 1987.010009765625, 2002.510009765625, 2014.1500244140625, 2059.330078125, 2085.260009765625, 2040.219970703125, 1954.77001953125, 1962.9300537109375, 1908.27001953125, 1834.3299560546875, 1771.43994140625, 1714.8599853515625, 1672.43994140625, 1591.199951171875, 1457.6400146484375, 1566.1500244140625, 1482.4599609375, 1609.969970703125, 1704.760009765625, 1686.239990234375, 1717.72998046875, 1717.1199951171875, 1754.6400146484375, 1685.4599609375, 1724.8599853515625, 1725.43994140625, 1791.8800048828125, 1823.5999755859375, 1807.1400146484375, 1836.2099609375, 1860.699951171875, 1825.760009765625, 1857.0799560546875, 1857.0699462890625, 1914.530029296875, 1898.3599853515625, 1879.3800048828125, 1896.1500244140625, 1914.72998046875, 1889.010009765625, 1922.77001953125, 1934.0899658203125, 1947.56005859375, 1895.3699951171875, 1928.760009765625, 1928.6099853515625, 1945.8199462890625, 1935.4000244140625, 1922.1700439453125, 1940.4200439453125, 1924.9599609375, 1927.280029296875, 1937.1099853515625, 1980.6099853515625, 1989.6400146484375, 1998.31005859375, 1970.1300048828125, 1994.5999755859375, 2029.780029296875, 2031.199951171875, 2028.5400390625, 2029.5999755859375, 2065.080078125, 2087.18994140625, 2147.0, 2151.179931640625, 2181.8701171875, 2184.2900390625, 2188.919921875, 2195.68994140625, 2176.780029296875, 2132.300048828125, 2030.8199462890625, 2138.050048828125, 2141.050048828125, 2133.47998046875, 2141.320068359375, 2126.72998046875, 2131.239990234375, 2161.510009765625, 2112.3701171875, 2134.64990234375, 2093.47998046875, 2108.330078125, 2106.699951171875, 2135.3701171875, 2152.409912109375, 2187.929931640625, 2164.169921875, 2158.8798828125, 2167.89990234375, 2150.25, 2186.06005859375, 2183.610107421875, 2201.8798828125, 2183.760009765625, 2201.18994140625, 2198.199951171875, 2228.830078125, 2228.659912109375, 2216.18994140625, 2200.43994140625, 2217.860107421875, 2256.989990234375, 2263.159912109375, 2267.010009765625, 2249.3701171875, 2251.0400390625, 2279.969970703125, 2311.860107421875, 2342.610107421875, 2351.669921875, 2386.3798828125, 2418.669921875, 2432.35009765625, 2437.530029296875, 2407.489990234375, 2348.239990234375, 2360.5400390625, 2274.219970703125, 2304.590087890625, 2329.830078125, 2366.72998046875, 2369.320068359375, 2344.449951171875, 2353.800048828125, 2326.169921875, 2349.550048828125, 2364.3701171875, 2395.89990234375, 2368.25, 2384.219970703125, 2401.909912109375, 2375.81005859375, 2396.47998046875, 2396.68994140625, 2427.909912109375, 2443.580078125, 2435.919921875, 2406.169921875, 2412.39990234375, 2389.389892578125, 2332.590087890625, 2333.239990234375, 2272.699951171875, 2278.7900390625, 2308.080078125, 2327.889892578125, 2358.0, 2365.89990234375, 2386.93994140625, 2391.9599609375, 2403.72998046875, 2403.14990234375, 2380.47998046875, 2361.2099609375, 2341.530029296875, 2346.739990234375, 2358.409912109375, 2370.860107421875, 2355.050048828125, 2360.81005859375, 2343.909912109375, 2330.840087890625, 2345.260009765625, 2326.669921875, 2267.14990234375, 2300.159912109375, 2343.31005859375, 2357.320068359375, 2413.7900390625, 2416.5, 2447.199951171875, 2452.830078125, 2485.8701171875, 2475.6201171875, 2493.8701171875, 2543.030029296875, 2539.14990234375, 2545.639892578125, 2547.419921875, 2553.5, 2602.590087890625, 2617.760009765625, 2601.5400390625, 2625.909912109375, 2633.449951171875, 2591.340087890625, 2634.25, 2675.89990234375, 2696.219970703125, 2731.449951171875, 2745.43994140625, 2700.929931640625, 2755.469970703125, 2746.4599609375, 2770.06005859375, 2762.199951171875, 2756.820068359375, 2771.7900390625, 2770.429931640625, 2772.179931640625, 2778.64990234375, 2733.679931640625, 2759.820068359375, 2806.860107421875, 2808.60009765625, 2820.510009765625, 2873.469970703125, 2944.449951171875, 2990.570068359375, 2968.2099609375, 3031.679931640625, 3152.179931640625, 3148.449951171875, 3125.949951171875, 3148.2900390625, 3149.929931640625, 3085.89990234375, 3013.929931640625, 3092.659912109375, 3114.550048828125, 3160.840087890625, 3140.6298828125, 3208.989990234375, 3140.31005859375, 3122.56005859375, 3069.050048828125, 2976.2099609375, 3056.530029296875, 3096.81005859375, 3129.679931640625, 3087.550048828125, 3120.6298828125, 3091.239990234375, 3084.669921875, 3100.580078125, 3147.0, 3163.25, 3133.72998046875, 3086.659912109375, 3107.6201171875, 3079.75, 3070.090087890625, 2994.97998046875, 3099.68994140625, 3012.949951171875, 3043.8701171875, 3082.989990234375, 3043.489990234375, 3026.260009765625, 2996.110107421875, 2976.1201171875, 2958.1201171875, 3013.699951171875, 3054.389892578125, 3045.7099609375, 3067.169921875, 3047.5, 3066.010009765625, 3039.530029296875, 3035.4599609375, 3004.739990234375, 2996.35009765625, 3008.330078125, 3041.010009765625, 3036.0400390625, 3070.0, 3061.419921875, 3087.39990234375, 3112.800048828125, 3120.830078125, 3127.080078125, 3137.409912109375, 3143.260009765625, 3131.8798828125, 3135.590087890625, 3169.080078125, 3182.3798828125, 3194.330078125, 3198.6201171875, 3198.840087890625, 3220.699951171875, 3171.659912109375, 3177.52001953125, 3181.080078125, 3217.530029296875, 3215.419921875, 3181.469970703125, 3174.070068359375, 3147.860107421875, 3127.199951171875, 3147.3701171875, 3160.429931640625, 3197.199951171875, 3249.300048828125, 3209.429931640625, 3161.659912109375, 3122.110107421875, 3153.320068359375, 3134.52001953125, 3173.050048828125, 3162.280029296875, 3156.419921875, 3144.300048828125, 3171.320068359375, 3168.429931640625, 3165.510009765625, 3188.72998046875, 3203.919921875, 3221.8701171875, 3224.22998046875, 3247.429931640625, 3240.080078125, 3252.1201171875, 3247.830078125, 3216.179931640625, 3224.639892578125, 3249.320068359375, 3252.1298828125, 3258.6298828125, 3278.679931640625, 3264.9599609375, 3267.929931640625, 3240.7900390625, 3263.8798828125, 3276.18994140625, 3286.10009765625, 3302.840087890625, 3301.889892578125, 3286.679931640625, 3296.679931640625, 3282.06005859375, 3281.780029296875, 3293.2099609375, 3305.2099609375, 3285.340087890625, 3252.679931640625, 3217.949951171875, 3246.469970703125, 3271.3798828125, 3264.81005859375, 3286.219970703125, 3276.909912109375, 3244.0400390625, 3232.699951171875, 3215.909912109375, 3250.2099609375, 3254.419921875, 3224.949951171875, 3232.530029296875, 3236.860107421875, 3242.64990234375, 3202.320068359375, 3223.0400390625, 3237.139892578125, 3280.3798828125, 3276.1298828125, 3270.360107421875, 3260.419921875, 3243.18994140625, 3220.6201171875, 3208.3798828125, 3171.2900390625, 3143.090087890625, 3158.929931640625, 3097.830078125, 3060.510009765625, 3090.2099609375, 3138.300048828125, 3146.81005859375, 3128.530029296875, 3133.89990234375, 3144.18994140625, 3199.27001953125, 3207.02001953125, 3175.85009765625, 3201.06005859375, 3203.330078125, 3187.419921875, 3162.989990234375, 3114.699951171875, 3125.760009765625, 3127.860107421875, 3148.830078125, 3153.39990234375, 3130.090087890625, 3140.510009765625, 3127.580078125, 3125.239990234375, 3133.639892578125, 3097.919921875, 3060.27001953125, 3068.820068359375, 3019.179931640625, 2962.169921875, 2908.31005859375, 2959.4599609375, 2956.300048828125, 2916.3798828125, 2944.409912109375, 2988.639892578125, 3015.06005859375, 3006.679931640625, 3029.0400390625, 3013.1298828125, 3007.330078125, 3006.159912109375, 3020.5400390625, 3049.080078125, 3025.489990234375, 3009.550048828125, 2970.679931640625, 2978.93994140625, 3013.489990234375, 2975.7099609375, 2983.219970703125, 2969.27001953125, 2960.199951171875, 2962.4599609375, 2930.169921875, 2924.919921875, 2968.800048828125, 2999.52001953125, 2997.2099609375, 2962.419921875, 2947.3798828125, 2971.02001953125, 3013.25, 2997.330078125, 2994.2900390625, 2980.27001953125, 2936.43994140625, 2909.320068359375, 2839.010009765625, 2899.719970703125, 2945.27001953125, 2968.330078125, 2973.25, 2991.719970703125, 3001.800048828125, 3029.570068359375, 3010.22998046875, 3001.659912109375, 2987.949951171875, 2989.389892578125, 3006.409912109375, 3017.72998046875, 2963.0, 2975.030029296875, 2984.47998046875, 2998.169921875, 3012.429931640625, 2999.550048828125, 3020.239990234375, 2993.2900390625, 2977.64990234375, 2989.239990234375, 2953.969970703125, 2920.530029296875, 2954.889892578125, 2926.719970703125, 2927.3798828125, 2972.47998046875, 2962.090087890625, 2921.919921875, 2890.10009765625, 2864.239990234375, 2842.280029296875, 2862.679931640625, 2834.2900390625, 2792.0, 2720.389892578125, 2709.239990234375, 2614.489990234375, 2663.340087890625, 2707.820068359375, 2750.260009765625, 2745.06005859375, 2746.469970703125, 2768.85009765625, 2771.929931640625, 2747.7099609375, 2704.47998046875, 2676.5400390625, 2729.679931640625, 2744.090087890625, 2744.52001953125, 2743.800048828125, 2706.7900390625, 2719.530029296875, 2648.800048828125, 2676.760009765625, 2699.179931640625, 2703.52001953125, 2747.080078125, 2713.429931640625, 2651.31005859375, 2622.39990234375, 2680.320068359375, 2661.280029296875, 2645.64990234375, 2621.530029296875, 2659.22998046875, 2694.510009765625, 2707.02001953125, 2686.050048828125, 2710.0, 2735.050048828125, 2729.659912109375, 2729.97998046875, 2729.56005859375, 2741.070068359375, 2746.739990234375, 2757.64990234375, 2739.85009765625, 2757.89990234375, 2759.199951171875, 2735.030029296875, 2695.860107421875, 2700.389892578125, 2693.10009765625, 2666.760009765625, 2716.489990234375, 2716.7099609375, 2696.06005859375, 2693.2099609375, 2718.889892578125, 2718.68994140625, 2728.2099609375, 2704.7099609375, 2657.1298828125, 2668.31005859375, 2639.06005859375, 2667.489990234375, 2695.050048828125, 2687.449951171875, 2680.4599609375, 2677.570068359375, 2644.510009765625, 2596.56005859375, 2592.27001953125, 2550.080078125, 2604.239990234375, 2596.580078125, 2620.43994140625, 2625.97998046875, 2592.340087890625, 2639.2900390625, 2647.3798828125, 2605.8701171875, 2617.219970703125, 2612.449951171875, 2638.050048828125, 2669.659912109375, 2685.89990234375, 2658.989990234375, 2670.64990234375, 2626.340087890625, 2626.14990234375, 2625.43994140625, 2595.8701171875, 2504.510009765625, 2492.969970703125, 2447.3798828125, 2451.409912109375, 2440.929931640625, 2391.030029296875, 2408.929931640625, 2342.81005859375, 2314.320068359375, 2366.60009765625, 2401.919921875, 2422.090087890625, 2377.989990234375, 2332.639892578125, 2305.419921875, 2300.340087890625, 2341.780029296875, 2292.010009765625, 2334.27001953125, 2350.610107421875, 2340.2700195312</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -1794,11 +1794,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1063.75</v>
+        <v>1170.0400390625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1833,27 +1833,27 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1862,22 +1862,22 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1123.725006103516</v>
+        <v>1105.124005126953</v>
       </c>
       <c r="Q5" t="n">
-        <v>1086.788666788737</v>
+        <v>1112.46066792806</v>
       </c>
       <c r="R5" t="n">
-        <v>993.632334391276</v>
+        <v>1013.727834574382</v>
       </c>
       <c r="S5" t="n">
-        <v>850.7215257124467</v>
+        <v>863.9651620047433</v>
       </c>
       <c r="T5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-10', '2020-04-13', '2020-04-14', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-05-04', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-03', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-15', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-02', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-21', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-15', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-06', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-30', '2022-05-31', '2022-06-02', '2022-06-03', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-24', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2023-01-02', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-07', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-03-29', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-02', '2024-05-03', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-02', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-18', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-02', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-04', '2025-06-05', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-03'], 'prices': [674.02001953125, 669.9299926757812, 655.3099975585938, 663.4400024414062, 640.9400024414062, 666.0900268554688, 673.030029296875, 679.219970703125, 678.7100219726562, 679.1599731445312, 686.52001953125, 688.4099731445312, 683.469970703125, 676.52001953125, 688.25, 685.5700073242188, 664.7000122070312, 670.1799926757812, 656.3900146484375, 642.47998046875, 646.8499755859375, 661.239990234375, 661.3200073242188, 672.6900024414062, 672.6300048828125, 676.0700073242188, 682.3400268554688, 686.5900268554688, 687.6099853515625, 688.9099731445312, 692.5900268554688, 682.9199829101562, 684.780029296875, 681.6599731445312, 667.989990234375, 639.2899780273438, 656.9500122070312, 654.6300048828125, 638.1699829101562, 610.72998046875, 627.6599731445312, 626.8200073242188, 641.72998046875, 650.1900024414062, 642.719970703125, 614.5999755859375, 619.969970703125, 595.6099853515625, 563.489990234375, 524.0, 504.510009765625, 514.72998046875, 485.1400146484375, 428.3500061035156, 467.75, 443.760009765625, 480.3999938964844, 505.67999267578125, 516.6099853515625, 522.8300170898438, 542.1099853515625, 569.0700073242188, 551.8400268554688, 567.7000122070312, 573.010009765625, 597.2100219726562, 606.9000244140625, 607.3699951171875, 615.9500122070312, 611.260009765625, 596.7100219726562, 610.2899780273438, 623.4299926757812, 634.7899780273438, 637.8200073242188, 628.77001953125, 635.1599731445312, 643.7899780273438, 632.9600219726562, 646.8599853515625, 644.9299926757812, 645.1799926757812, 641.9099731445312, 658.4000244140625, 668.1699829101562, 682.2999877929688, 685.0399780273438, 684.2100219726562, 691.530029296875, 690.5700073242188, 691.9299926757812, 690.8499755859375, 696.3599853515625, 708.760009765625, 716.02001953125, 708.5800170898438, 719.8900146484375, 729.1099853515625, 724.5900268554688, 708.75, 713.6799926757812, 735.719970703125, 743.5800170898438, 737.6599731445312, 742.3699951171875, 749.3099975585938, 753.0399780273438, 753.8200073242188, 758.6199951171875, 757.0599975585938, 746.0599975585938, 693.1500244140625, 735.3800048828125, 735.4000244140625, 737.3300170898438, 742.030029296875, 751.6400146484375, 753.22998046875, 759.5, 750.3599853515625, 750.5800170898438, 734.6900024414062, 737.969970703125, 727.5800170898438, 742.5499877929688, 752.1799926757812, 759.9000244140625, 759.1599731445312, 765.9600219726562, 772.9000244140625, 772.8099975585938, 781.1900024414062, 778.3900146484375, 781.2899780273438, 775.0700073242188, 783.219970703125, 781.9600219726562, 790.5800170898438, 794.989990234375, 801.6900024414062, 794.7999877929688, 801.22998046875, 807.8499755859375, 808.5900268554688, 814.1900024414062, 815.2999877929688, 827.5700073242188, 835.3499755859375, 847.280029296875, 854.1199951171875, 857.6300048828125, 862.760009765625, 860.22998046875, 845.5999755859375, 854.77001953125, 835.030029296875, 800.219970703125, 818.739990234375, 791.1400146484375, 796.010009765625, 815.739990234375, 836.3099975585938, 841.3499755859375, 836.4000244140625, 841.2999877929688, 848.239990234375, 853.3699951171875, 866.739990234375, 874.1300048828125, 866.0399780273438, 878.8800048828125, 878.2899780273438, 869.469970703125, 884.2999877929688, 888.4400024414062, 894.1699829101562, 899.4600219726562, 896.280029296875, 885.1799926757812, 888.8800048828125, 866.989990234375, 842.719970703125, 843.4500122070312, 806.9500122070312, 808.280029296875, 835.9099731445312, 848.1500244140625, 858.3900146484375, 862.5800170898438, 869.6599731445312, 871.6199951171875, 873.5, 871.9199829101562, 861.47998046875, 844.4400024414062, 833.8400268554688, 822.25, 824.6500244140625, 830.6699829101562, 812.7000122070312, 807.97998046875, 778.02001953125, 783.72998046875, 806.2000122070312, 813.9299926757812, 792.6500244140625, 802.9500122070312, 818.4600219726562, 826.969970703125, 844.7999877929688, 836.780029296875, 851.2100219726562, 840.7899780273438, 839.9000244140625, 840.0800170898438, 839.1400146484375, 847.3300170898438, 839.469970703125, 851.739990234375, 859.9400024414062, 870.1799926757812, 873.2899780273438, 872.0999755859375, 865.1199951171875, 874.530029296875, 885.5599975585938, 886.1099853515625, 891.2899780273438, 899.3400268554688, 907.6099853515625, 913.760009765625, 926.8800048828125, 906.8400268554688, 913.8099975585938, 921.7000122070312, 928.4400024414062, 929.5399780273438, 931.27001953125, 939.6500244140625, 944.0399780273438, 947.239990234375, 953.5800170898438, 928.72998046875, 923.1699829101562, 928.6799926757812, 927.0, 957.4099731445312, 968.4199829101562, 977.6199951171875, 985.760009765625, 981.3900146484375, 988.8599853515625, 987.7899780273438, 976.6300048828125, 973.719970703125, 979.1300048828125, 980.2899780273438, 964.4400024414062, 944.6699829101562, 957.75, 977.6599731445312, 981.4000244140625, 979.97998046875, 999.2999877929688, 994.0, 985.9199829101562, 961.22998046875, 928.72998046875, 956.9199829101562, 963.8099975585938, 970.6900024414062, 964.5800170898438, 967.4199829101562, 960.780029296875, 957.8499755859375, 964.3099975585938, 981.969970703125, 977.739990234375, 979.77001953125, 967.4199829101562, 965.1099853515625, 954.2899780273438, 936.5999755859375, 906.3099975585938, 936.2100219726562, 913.9400024414062, 923.1699829101562, 930.7999877929688, 926.2000122070312, 923.47998046875, 904.77001953125, 896.3599853515625, 890.0700073242188, 908.010009765625, 925.489990234375, 926.9000244140625, 940.6500244140625, 943.780029296875, 949.8300170898438, 952.1099853515625, 955.3800048828125, 946.3099975585938, 953.8200073242188, 954.989990234375, 956.7000122070312, 954.0999755859375, 958.0599975585938, 956.1699829101562, 965.780029296875, 970.0900268554688, 969.77001953125, 968.6300048828125, 973.219970703125, 982.02001953125, 989.3900146484375, 1000.6500244140625, 1010.3699951171875, 1014.4199829101562, 1013.9000244140625, 1021.6199951171875, 1029.4599609375, 1031.8800048828125, 1022.219970703125, 1025.7099609375, 1026.8199462890625, 1030.06005859375, 1021.010009765625, 998.27001953125, 990.6900024414062, 983.4500122070312, 961.8099975585938, 967.2000122070312, 969.989990234375, 978.2999877929688, 992.7999877929688, 978.6099853515625, 967.0999755859375, 951.77001953125, 966.719970703125, 962.5, 969.0999755859375, 971.1300048828125, 965.6300048828125, 948.3699951171875, 962.0700073242188, 966.0599975585938, 974.0800170898438, 977.4600219726562, 981.780029296875, 984.5900268554688, 981.0999755859375, 990.1900024414062, 987.5800170898438, 985.8599853515625, 986.1199951171875, 978.7899780273438, 987.77001953125, 991.1300048828125, 997.4099731445312, 997.3699951171875, 998.489990234375, 1003.719970703125, 1015.8800048828125, 1010.989990234375, 1011.5599975585938, 1016.4600219726562, 1012.6199951171875, 1012.1300048828125, 1017.9099731445312, 1022.52001953125, 1029.9599609375, 1035.6400146484375, 1038.1800537109375, 1047.3299560546875, 1044.9599609375, 1047.3599853515625, 1034.47998046875, 1028.9300537109375, 1034.6400146484375, 1043.31005859375, 1044.97998046875, 1054.31005859375, 1051.97998046875, 1049.8299560546875, 1043.6400146484375, 1042.030029296875, 1050.25, 1055.5, 1047.6300048828125, 1046.550048828125, 1035.6800537109375, 1044.1300048828125, 1031.1400146484375, 1037.800048828125, 1036.1099853515625, 1047.9300537109375, 1059.5400390625, 1059.800048828125, 1060.0, 1052.0699462890625, 1051.9200439453125, 1054.0899658203125, 1040.780029296875, 1011.0499877929688, 1021.0800170898438, 991.1500244140625, 967.9000244140625, 993.1799926757812, 1013.1799926757812, 1017.780029296875, 1020.4400024414062, 1023.510009765625, 1031.8399658203125, 1038.3299560546875, 1045.97998046875, 1047.18994140625, 1053.8499755859375, 1052.9599609375, 1054.4300537109375, 1037.219970703125, 1034.6199951171875, 1037.9100341796875, 1026.3399658203125, 1037.739990234375, 1042.7900390625, 1039.4300537109375, 1046.1199951171875, 1036.260009765625, 1037.030029296875, 1034.8199462890625, 1012.510009765625, 1001.4600219726562, 1003.27001953125, 983.2000122070312, 955.3699951171875, 922.3599853515625, 953.4299926757812, 953.1099853515625, 940.1500244140625, 953.469970703125, 983.4299926757812, 990.5399780273438, 993.8599853515625, 1005.3499755859375, 1001.6199951171875, 993.7000122070312, 995.0700073242188, 994.3099975585938, 1011.760009765625, 1008.9500122070312, 1000.1300048828125, 992.3300170898438, 998.5700073242188, 1009.4400024414062, 1005.0, 1001.4299926757812, 1001.3499755859375, 1002.5, 1008.6799926757812, 987.75, 992.6500244140625, 1009.0700073242188, 1029.030029296875, 1035.4599609375, 1031.260009765625, 1032.77001953125, 1041.9200439453125, 1032.31005859375, 1013.719970703125, 1020.1300048828125, 1015.6599731445312, 1005.8900146484375, 992.3400268554688, 965.6300048828125, 977.1500244140625, 977.4299926757812, 998.469970703125, 991.8699951171875, 996.6400146484375, 1006.0399780273438, 1022.8699951171875, 1011.5700073242188, 1005.9600219726562, 1002.8099975585938, 1003.52001953125, 1007.8599853515625, 1001.260009765625, 990.510009765625, 996.5999755859375, 1000.1300048828125, 1003.3099975585938, 1007.4199829101562, 1011.3599853515625, 1027.43994140625, 1028.050048828125, 1033.97998046875, 1031.6600341796875, 1009.6199951171875, 980.2999877929688, 995.1599731445312, 980.3800048828125, 969.9199829101562, 991.3300170898438, 983.25, 971.3900146484375, 957.9000244140625, 943.9400024414062, 933.9000244140625, 958.7000122070312, 942.8499755859375, 915.4000244140625, 889.4400024414062, 882.0900268554688, 849.22998046875, 872.8699951171875, 891.5999755859375, 902.8699951171875, 899.4000244140625, 895.27001953125, 910.530029296875, 895.6799926757812, 877.4199829101562, 852.7899780273438, 839.9199829101562, 878.1500244140625, 874.219970703125, 881.7100219726562, 884.25, 868.1099853515625, 877.3300170898438, 848.2100219726562, 872.97998046875, 881.0700073242188, 895.4500122070312, 912.3200073242188, 900.9600219726562, 881.5399780273438, 870.1400146484375, 889.0800170898438, 891.7100219726562, 872.4400024414062, 871.219970703125, 891.7999877929688, 914.1300048828125, 922.9600219726562, 918.4000244140625, 924.6699829101562, 930.5700073242188, 931.75, 934.6900024414062, 927.1099853515625, 937.8300170898438, 939.0700073242188, 944.530029296875, 940.5700073242188, 947.3200073242188, 952.469970703125, 943.1300048828125, 927.9500122070312, 934.72998046875, 921.8300170898438, 913.8200073242188, 927.3099975585938, 928.010009765625, 924.4400024414062, 918.22998046875, 931.5599975585938, 928.9299926757812, 929.6799926757812, 922.780029296875, 899.8400268554688, 911.1599731445312, 896.1799926757812, 892.219970703125, 904.75, 901.8200073242188, 907.5700073242188, 900.0599975585938, 884.219970703125, 856.1400146484375, 866.3400268554688, 833.6599731445312, 853.0800170898438, 856.25, 865.97998046875, 865.97998046875, 863.7999877929688, 879.8800048828125, 883.5900268554688, 865.0700073242188, 872.6900024414062, 871.4299926757812, 873.969970703125, 886.4400024414062, 893.3599853515625, 891.1400146484375, 891.510009765625, 873.780029296875, 874.9500122070312, 877.1799926757812, 869.8599853515625, 828.77001953125, 823.5800170898438, 799.4099731445312, 802.1500244140625, 798.6900024414062, 769.9199829101562, 778.2999877929688, 746.9600219726562, 714.3800048828125, 750.2999877929688, 770.5999755859375, 769.510009765625, 762.</t>
+          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-10', '2020-04-13', '2020-04-14', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-05-04', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-03', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-15', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-02', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-21', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-15', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-02', '2022-05-03', '2022-05-04', '2022-05-06', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-30', '2022-05-31', '2022-06-02', '2022-06-03', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-24', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-27', '2022-12-28', '2022-12-29', '2023-01-02', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-07', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-26', '2023-12-27', '2023-12-28', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-03-29', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-02', '2024-05-03', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-02', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-26', '2024-12-27', '2024-12-30', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-18', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-02', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-04', '2025-06-05', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-26', '2025-12-29', '2025-12-30', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-19', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-03', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [674.02001953125, 669.9299926757812, 655.3099975585938, 663.4400024414062, 640.9400024414062, 666.0900268554688, 673.030029296875, 679.219970703125, 678.7100219726562, 679.1599731445312, 686.52001953125, 688.4099731445312, 683.469970703125, 676.52001953125, 688.25, 685.5700073242188, 664.7000122070312, 670.1799926757812, 656.3900146484375, 642.47998046875, 646.8499755859375, 661.239990234375, 661.3200073242188, 672.6900024414062, 672.6300048828125, 676.0700073242188, 682.3400268554688, 686.5900268554688, 687.6099853515625, 688.9099731445312, 692.5900268554688, 682.9199829101562, 684.780029296875, 681.6599731445312, 667.989990234375, 639.2899780273438, 656.9500122070312, 654.6300048828125, 638.1699829101562, 610.72998046875, 627.6599731445312, 626.8200073242188, 641.72998046875, 650.1900024414062, 642.719970703125, 614.5999755859375, 619.969970703125, 595.6099853515625, 563.489990234375, 524.0, 504.510009765625, 514.72998046875, 485.1400146484375, 428.3500061035156, 467.75, 443.760009765625, 480.3999938964844, 505.67999267578125, 516.6099853515625, 522.8300170898438, 542.1099853515625, 569.0700073242188, 551.8400268554688, 567.7000122070312, 573.010009765625, 597.2100219726562, 606.9000244140625, 607.3699951171875, 615.9500122070312, 611.260009765625, 596.7100219726562, 610.2899780273438, 623.4299926757812, 634.7899780273438, 637.8200073242188, 628.77001953125, 635.1599731445312, 643.7899780273438, 632.9600219726562, 646.8599853515625, 644.9299926757812, 645.1799926757812, 641.9099731445312, 658.4000244140625, 668.1699829101562, 682.2999877929688, 685.0399780273438, 684.2100219726562, 691.530029296875, 690.5700073242188, 691.9299926757812, 690.8499755859375, 696.3599853515625, 708.760009765625, 716.02001953125, 708.5800170898438, 719.8900146484375, 729.1099853515625, 724.5900268554688, 708.75, 713.6799926757812, 735.719970703125, 743.5800170898438, 737.6599731445312, 742.3699951171875, 749.3099975585938, 753.0399780273438, 753.8200073242188, 758.6199951171875, 757.0599975585938, 746.0599975585938, 693.1500244140625, 735.3800048828125, 735.4000244140625, 737.3300170898438, 742.030029296875, 751.6400146484375, 753.22998046875, 759.5, 750.3599853515625, 750.5800170898438, 734.6900024414062, 737.969970703125, 727.5800170898438, 742.5499877929688, 752.1799926757812, 759.9000244140625, 759.1599731445312, 765.9600219726562, 772.9000244140625, 772.8099975585938, 781.1900024414062, 778.3900146484375, 781.2899780273438, 775.0700073242188, 783.219970703125, 781.9600219726562, 790.5800170898438, 794.989990234375, 801.6900024414062, 794.7999877929688, 801.22998046875, 807.8499755859375, 808.5900268554688, 814.1900024414062, 815.2999877929688, 827.5700073242188, 835.3499755859375, 847.280029296875, 854.1199951171875, 857.6300048828125, 862.760009765625, 860.22998046875, 845.5999755859375, 854.77001953125, 835.030029296875, 800.219970703125, 818.739990234375, 791.1400146484375, 796.010009765625, 815.739990234375, 836.3099975585938, 841.3499755859375, 836.4000244140625, 841.2999877929688, 848.239990234375, 853.3699951171875, 866.739990234375, 874.1300048828125, 866.0399780273438, 878.8800048828125, 878.2899780273438, 869.469970703125, 884.2999877929688, 888.4400024414062, 894.1699829101562, 899.4600219726562, 896.280029296875, 885.1799926757812, 888.8800048828125, 866.989990234375, 842.719970703125, 843.4500122070312, 806.9500122070312, 808.280029296875, 835.9099731445312, 848.1500244140625, 858.3900146484375, 862.5800170898438, 869.6599731445312, 871.6199951171875, 873.5, 871.9199829101562, 861.47998046875, 844.4400024414062, 833.8400268554688, 822.25, 824.6500244140625, 830.6699829101562, 812.7000122070312, 807.97998046875, 778.02001953125, 783.72998046875, 806.2000122070312, 813.9299926757812, 792.6500244140625, 802.9500122070312, 818.4600219726562, 826.969970703125, 844.7999877929688, 836.780029296875, 851.2100219726562, 840.7899780273438, 839.9000244140625, 840.0800170898438, 839.1400146484375, 847.3300170898438, 839.469970703125, 851.739990234375, 859.9400024414062, 870.1799926757812, 873.2899780273438, 872.0999755859375, 865.1199951171875, 874.530029296875, 885.5599975585938, 886.1099853515625, 891.2899780273438, 899.3400268554688, 907.6099853515625, 913.760009765625, 926.8800048828125, 906.8400268554688, 913.8099975585938, 921.7000122070312, 928.4400024414062, 929.5399780273438, 931.27001953125, 939.6500244140625, 944.0399780273438, 947.239990234375, 953.5800170898438, 928.72998046875, 923.1699829101562, 928.6799926757812, 927.0, 957.4099731445312, 968.4199829101562, 977.6199951171875, 985.760009765625, 981.3900146484375, 988.8599853515625, 987.7899780273438, 976.6300048828125, 973.719970703125, 979.1300048828125, 980.2899780273438, 964.4400024414062, 944.6699829101562, 957.75, 977.6599731445312, 981.4000244140625, 979.97998046875, 999.2999877929688, 994.0, 985.9199829101562, 961.22998046875, 928.72998046875, 956.9199829101562, 963.8099975585938, 970.6900024414062, 964.5800170898438, 967.4199829101562, 960.780029296875, 957.8499755859375, 964.3099975585938, 981.969970703125, 977.739990234375, 979.77001953125, 967.4199829101562, 965.1099853515625, 954.2899780273438, 936.5999755859375, 906.3099975585938, 936.2100219726562, 913.9400024414062, 923.1699829101562, 930.7999877929688, 926.2000122070312, 923.47998046875, 904.77001953125, 896.3599853515625, 890.0700073242188, 908.010009765625, 925.489990234375, 926.9000244140625, 940.6500244140625, 943.780029296875, 949.8300170898438, 952.1099853515625, 955.3800048828125, 946.3099975585938, 953.8200073242188, 954.989990234375, 956.7000122070312, 954.0999755859375, 958.0599975585938, 956.1699829101562, 965.780029296875, 970.0900268554688, 969.77001953125, 968.6300048828125, 973.219970703125, 982.02001953125, 989.3900146484375, 1000.6500244140625, 1010.3699951171875, 1014.4199829101562, 1013.9000244140625, 1021.6199951171875, 1029.4599609375, 1031.8800048828125, 1022.219970703125, 1025.7099609375, 1026.8199462890625, 1030.06005859375, 1021.010009765625, 998.27001953125, 990.6900024414062, 983.4500122070312, 961.8099975585938, 967.2000122070312, 969.989990234375, 978.2999877929688, 992.7999877929688, 978.6099853515625, 967.0999755859375, 951.77001953125, 966.719970703125, 962.5, 969.0999755859375, 971.1300048828125, 965.6300048828125, 948.3699951171875, 962.0700073242188, 966.0599975585938, 974.0800170898438, 977.4600219726562, 981.780029296875, 984.5900268554688, 981.0999755859375, 990.1900024414062, 987.5800170898438, 985.8599853515625, 986.1199951171875, 978.7899780273438, 987.77001953125, 991.1300048828125, 997.4099731445312, 997.3699951171875, 998.489990234375, 1003.719970703125, 1015.8800048828125, 1010.989990234375, 1011.5599975585938, 1016.4600219726562, 1012.6199951171875, 1012.1300048828125, 1017.9099731445312, 1022.52001953125, 1029.9599609375, 1035.6400146484375, 1038.1800537109375, 1047.3299560546875, 1044.9599609375, 1047.3599853515625, 1034.47998046875, 1028.9300537109375, 1034.6400146484375, 1043.31005859375, 1044.97998046875, 1054.31005859375, 1051.97998046875, 1049.8299560546875, 1043.6400146484375, 1042.030029296875, 1050.25, 1055.5, 1047.6300048828125, 1046.550048828125, 1035.6800537109375, 1044.1300048828125, 1031.1400146484375, 1037.800048828125, 1036.1099853515625, 1047.9300537109375, 1059.5400390625, 1059.800048828125, 1060.0, 1052.0699462890625, 1051.9200439453125, 1054.0899658203125, 1040.780029296875, 1011.0499877929688, 1021.0800170898438, 991.1500244140625, 967.9000244140625, 993.1799926757812, 1013.1799926757812, 1017.780029296875, 1020.4400024414062, 1023.510009765625, 1031.8399658203125, 1038.3299560546875, 1045.97998046875, 1047.18994140625, 1053.8499755859375, 1052.9599609375, 1054.4300537109375, 1037.219970703125, 1034.6199951171875, 1037.9100341796875, 1026.3399658203125, 1037.739990234375, 1042.7900390625, 1039.4300537109375, 1046.1199951171875, 1036.260009765625, 1037.030029296875, 1034.8199462890625, 1012.510009765625, 1001.4600219726562, 1003.27001953125, 983.2000122070312, 955.3699951171875, 922.3599853515625, 953.4299926757812, 953.1099853515625, 940.1500244140625, 953.469970703125, 983.4299926757812, 990.5399780273438, 993.8599853515625, 1005.3499755859375, 1001.6199951171875, 993.7000122070312, 995.0700073242188, 994.3099975585938, 1011.760009765625, 1008.9500122070312, 1000.1300048828125, 992.3300170898438, 998.5700073242188, 1009.4400024414062, 1005.0, 1001.4299926757812, 1001.3499755859375, 1002.5, 1008.6799926757812, 987.75, 992.6500244140625, 1009.0700073242188, 1029.030029296875, 1035.4599609375, 1031.260009765625, 1032.77001953125, 1041.9200439453125, 1032.31005859375, 1013.719970703125, 1020.1300048828125, 1015.6599731445312, 1005.8900146484375, 992.3400268554688, 965.6300048828125, 977.1500244140625, 977.4299926757812, 998.469970703125, 991.8699951171875, 996.6400146484375, 1006.0399780273438, 1022.8699951171875, 1011.5700073242188, 1005.9600219726562, 1002.8099975585938, 1003.52001953125, 1007.8599853515625, 1001.260009765625, 990.510009765625, 996.5999755859375, 1000.1300048828125, 1003.3099975585938, 1007.4199829101562, 1011.3599853515625, 1027.43994140625, 1028.050048828125, 1033.97998046875, 1031.6600341796875, 1009.6199951171875, 980.2999877929688, 995.1599731445312, 980.3800048828125, 969.9199829101562, 991.3300170898438, 983.25, 971.3900146484375, 957.9000244140625, 943.9400024414062, 933.9000244140625, 958.7000122070312, 942.8499755859375, 915.4000244140625, 889.4400024414062, 882.0900268554688, 849.22998046875, 872.8699951171875, 891.5999755859375, 902.8699951171875, 899.4000244140625, 895.27001953125, 910.530029296875, 895.6799926757812, 877.4199829101562, 852.7899780273438, 839.9199829101562, 878.1500244140625, 874.219970703125, 881.7100219726562, 884.25, 868.1099853515625, 877.3300170898438, 848.2100219726562, 872.97998046875, 881.0700073242188, 895.4500122070312, 912.3200073242188, 900.9600219726562, 881.5399780273438, 870.1400146484375, 889.0800170898438, 891.7100219726562, 872.4400024414062, 871.219970703125, 891.7999877929688, 914.1300048828125, 922.9600219726562, 918.4000244140625, 924.6699829101562, 930.5700073242188, 931.75, 934.6900024414062, 927.1099853515625, 937.8300170898438, 939.0700073242188, 944.530029296875, 940.5700073242188, 947.3200073242188, 952.469970703125, 943.1300048828125, 927.9500122070312, 934.72998046875, 921.8300170898438, 913.8200073242188, 927.3099975585938, 928.010009765625, 924.4400024414062, 918.22998046875, 931.5599975585938, 928.9299926757812, 929.6799926757812, 922.780029296875, 899.8400268554688, 911.1599731445312, 896.1799926757812, 892.219970703125, 904.75, 901.8200073242188, 907.5700073242188, 900.0599975585938, 884.219970703125, 856.1400146484375, 866.3400268554688, 833.6599731445312, 853.0800170898438, 856.25, 865.97998046875, 865.97998046875, 863.7999877929688, 879.8800048828125, 883.5900268554688, 865.0700073242188, 872.6900024414062, 871.4299926757812, 873.969970703125, 886.4400024414062, 893.3599853515625, 891.1400146484375, 891.510009765625, 873.780029296875, 874.9500122070312, 877.1799926757812, 869.8599853515625, 828.77001953125, 823.5800170898438, 799.4099731445312, 802.1500244140625, 798.69000244140</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -1903,11 +1903,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3880.096923828125</v>
+        <v>4051.425048828125</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1942,27 +1942,27 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1971,37 +1971,37 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3986.564807128906</v>
+        <v>3946.813269042969</v>
       </c>
       <c r="Q6" t="n">
-        <v>4069.423901367188</v>
+        <v>4055.951981608073</v>
       </c>
       <c r="R6" t="n">
-        <v>3997.092026774088</v>
+        <v>4005.311446126302</v>
       </c>
       <c r="S6" t="n">
-        <v>3666.620750526329</v>
+        <v>3685.977319494471</v>
       </c>
       <c r="T6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="b">
         <v>1</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-10', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-03', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-25', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-02', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-21', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-15', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-30', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-24', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-26', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-06', '2023-04-07', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-29', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-25', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-03-29', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-25', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-18', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-25', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-03'], 'prices': [3085.197998046875, 3083.785888671875, 3083.407958984375, 3104.802001953125, 3066.89306640625, 3094.882080078125, 3092.291015625, 3115.570068359375, 3106.820068359375, 3090.0400390625, 3074.0810546875, 3075.49609375, 3095.787109375, 3052.139892578125, 3060.7548828125, 2976.528076171875, 2746.60595703125, 2783.2880859375, 2818.087890625, 2866.510009765625, 2875.9599609375, 2890.488037109375, 2901.669921875, 2926.89892578125, 2906.073974609375, 2917.008056640625, 2983.6220703125, 2984.971923828125, 2975.402099609375, 3030.154052734375, 3039.6689453125, 3031.23291015625, 3013.050048828125, 2987.928955078125, 2991.330078125, 2880.303955078125, 2970.930908203125, 2992.89697265625, 3011.666015625, 3071.677001953125, 3034.510986328125, 2943.291015625, 2996.761962890625, 2968.51708984375, 2923.486083984375, 2887.427001953125, 2789.25390625, 2779.64111328125, 2728.756103515625, 2702.1298828125, 2745.617919921875, 2660.169921875, 2722.43798828125, 2781.591064453125, 2764.910888671875, 2772.202880859375, 2747.214111328125, 2750.2958984375, 2734.52197265625, 2780.637939453125, 2763.987060546875, 2820.762939453125, 2815.368896484375, 2825.904052734375, 2796.631103515625, 2783.048095703125, 2827.282958984375, 2811.174072265625, 2819.93505859375, 2838.4951171875, 2852.552978515625, 2827.012939453125, 2843.97998046875, 2838.4990234375, 2808.529052734375, 2815.4951171875, 2810.02392578125, 2822.44189453125, 2860.08203125, 2878.139892578125, 2871.52294921875, 2895.340087890625, 2894.800048828125, 2891.555908203125, 2898.050048828125, 2870.342041015625, 2868.458984375, 2875.41796875, 2898.575927734375, 2883.738037109375, 2867.924072265625, 2813.764892578125, 2817.969970703125, 2846.547119140625, 2836.803955078125, 2846.221923828125, 2852.35107421875, 2915.430908203125, 2921.39794921875, 2923.37109375, 2919.2509765625, 2930.799072265625, 2937.77099609375, 2956.112060546875, 2943.7529296875, 2920.89697265625, 2919.740966796875, 2890.030029296875, 2931.75, 2935.8701171875, 2939.320068359375, 2967.6298828125, 2965.27197265625, 2970.6201171875, 2979.551025390625, 2961.51611328125, 2984.674072265625, 3025.98095703125, 3090.569091796875, 3152.81298828125, 3332.881103515625, 3345.3369140625, 3403.43994140625, 3450.593994140625, 3383.322021484375, 3443.285888671875, 3414.618896484375, 3361.303955078125, 3210.09912109375, 3214.12890625, 3314.14892578125, 3320.89501953125, 3333.1640625, 3325.110107421875, 3196.76806640625, 3205.22705078125, 3227.9599609375, 3294.552001953125, 3286.822021484375, 3310.007080078125, 3367.966064453125, 3371.68994140625, 3377.56005859375, 3386.4599609375, 3354.034912109375, 3379.251953125, 3340.2900390625, 3319.26611328125, 3320.72607421875, 3360.09912109375, 3438.801025390625, 3451.089111328125, 3408.12890625, 3363.89892578125, 3380.68310546875, 3385.637939453125, 3373.577880859375, 3329.739013671875, 3350.110107421875, 3403.806884765625, 3395.677978515625, 3410.60693359375, 3404.802001953125, 3384.98095703125, 3355.366943359375, 3292.591064453125, 3316.4169921875, 3254.6279296875, 3234.822998046875, 3260.345947265625, 3278.81396484375, 3295.679931640625, 3283.924072265625, 3270.43505859375, 3338.090087890625, 3316.93505859375, 3274.302001953125, 3279.7109375, 3223.176025390625, 3219.41796875, 3217.534912109375, 3224.35888671875, 3218.052001953125, 3272.075927734375, 3358.465087890625, 3359.75, 3340.778076171875, 3332.18310546875, 3336.35791015625, 3312.669921875, 3328.10009765625, 3325.02001953125, 3312.5, 3277.9970703125, 3251.118896484375, 3254.31591796875, 3269.239990234375, 3272.72998046875, 3224.532958984375, 3225.1201171875, 3271.073974609375, 3277.43994140625, 3320.133056640625, 3312.158935546875, 3373.72998046875, 3360.14892578125, 3342.202880859375, 3338.679931640625, 3310.10498046875, 3346.968994140625, 3339.89990234375, 3347.302978515625, 3363.087890625, 3377.72998046875, 3414.489990234375, 3402.822998046875, 3362.326904296875, 3369.73291015625, 3408.306884765625, 3391.760009765625, 3451.93994140625, 3449.381103515625, 3442.135986328125, 3444.5810546875, 3416.60400390625, 3410.179931640625, 3371.964111328125, 3373.27587890625, 3347.19091796875, 3369.1201171875, 3367.22998046875, 3366.98291015625, 3404.873046875, 3394.89990234375, 3420.569091796875, 3356.781982421875, 3382.320068359375, 3363.113037109375, 3396.56298828125, 3397.284912109375, 3379.035888671875, 3414.452880859375, 3473.069091796875, 3502.9580078125, 3528.677001953125, 3550.876953125, 3576.205078125, 3570.110107421875, 3531.498046875, 3608.340087890625, 3598.652099609375, 3565.905029296875, 3566.3779296875, 3596.219970703125, 3566.3798828125, 3583.092041015625, 3621.263916015625, 3606.75, 3624.238037109375, 3569.428955078125, 3573.340087890625, 3505.176025390625, 3483.069091796875, 3505.283935546875, 3533.68505859375, 3517.30810546875, 3501.85888671875, 3496.330078125, 3532.447021484375, 3603.489013671875, 3655.087890625, 3675.35693359375, 3696.16796875, 3642.43994140625, 3636.360107421875, 3564.080078125, 3585.050048828125, 3509.080078125, 3551.39990234375, 3508.591064453125, 3576.89990234375, 3503.489990234375, 3501.987060546875, 3421.409912109375, 3359.2900390625, 3357.739990234375, 3436.830078125, 3453.080078125, 3419.949951171875, 3446.73291015625, 3445.551025390625, 3463.068115234375, 3404.659912109375, 3443.43994140625, 3411.510009765625, 3367.06005859375, 3363.590087890625, 3418.326904296875, 3435.300048828125, 3456.679931640625, 3441.909912109375, 3466.330078125, 3484.39208984375, 3482.969970703125, 3479.6298828125, 3482.550048828125, 3450.679931640625, 3412.949951171875, 3396.469970703125, 3416.719970703125, 3398.989990234375, 3426.6201171875, 3477.550048828125, 3472.93994140625, 3472.929931640625, 3465.110107421875, 3474.169921875, 3441.169921875, 3442.610107421875, 3457.070068359375, 3474.89990234375, 3446.860107421875, 3441.280029296875, 3418.8701171875, 3427.989990234375, 3441.85009765625, 3462.75, 3429.5400390625, 3490.3798828125, 3517.6201171875, 3529.010009765625, 3510.9599609375, 3506.93994140625, 3486.56005859375, 3497.280029296875, 3581.340087890625, 3593.360107421875, 3608.85009765625, 3600.780029296875, 3615.47998046875, 3624.7099609375, 3597.139892578125, 3584.2099609375, 3591.840087890625, 3599.5400390625, 3580.110107421875, 3591.39990234375, 3610.860107421875, 3589.75, 3556.56005859375, 3518.330078125, 3525.60009765625, 3525.10009765625, 3529.179931640625, 3557.409912109375, 3566.219970703125, 3566.64990234375, 3607.56005859375, 3606.3701171875, 3573.179931640625, 3591.199951171875, 3588.780029296875, 3518.760009765625, 3534.320068359375, 3530.260009765625, 3553.719970703125, 3525.5, 3524.090087890625, 3547.840087890625, 3566.52001953125, 3528.5, 3564.590087890625, 3539.300048828125, 3539.1201171875, 3536.7900390625, 3562.660888671875, 3574.73388671875, 3550.39990234375, 3467.43994140625, 3381.179931640625, 3361.590087890625, 3411.719970703125, 3397.360107421875, 3464.2900390625, 3447.989990234375, 3477.219970703125, 3466.550048828125, 3458.22998046875, 3494.6298828125, 3529.929931640625, 3532.6201171875, 3524.739990234375, 3516.300048828125, 3517.340087890625, 3446.97607421875, 3485.285888671875, 3465.554931640625, 3427.333984375, 3477.1298828125, 3514.470947265625, 3540.3798828125, 3501.6640625, 3522.156982421875, 3528.15087890625, 3543.93994140625, 3567.10009765625, 3597.0400390625, 3581.72998046875, 3621.860107421875, 3676.590087890625, 3675.18994140625, 3693.1298828125, 3703.110107421875, 3715.3701171875, 3662.60009765625, 3656.219970703125, 3607.090087890625, 3613.969970703125, 3628.489990234375, 3642.219970703125, 3613.070068359375, 3582.830078125, 3602.219970703125, 3536.2900390625, 3568.169921875, 3592.169921875, 3591.7099609375, 3546.93994140625, 3561.760009765625, 3558.280029296875, 3572.3701171875, 3568.139892578125, 3593.14990234375, 3587.0, 3594.780029296875, 3582.60009765625, 3609.860107421875, 3597.639892578125, 3562.31005859375, 3518.419921875, 3547.340087890625, 3544.47998046875, 3505.6298828125, 3498.5400390625, 3526.8701171875, 3491.570068359375, 3498.6298828125, 3507.0, 3492.4599609375, 3532.7900390625, 3539.10009765625, 3533.300048828125, 3521.7900390625, 3537.3701171875, 3520.7099609375, 3560.3701171875, 3582.080078125, 3589.089111328125, 3592.702880859375, 3584.179931640625, 3564.090087890625, 3562.699951171875, 3563.889892578125, 3576.889892578125, 3573.840087890625, 3607.429931640625, 3589.31005859375, 3595.090087890625, 3637.570068359375, 3673.0400390625, 3666.35009765625, 3681.080078125, 3661.530029296875, 3647.6298828125, 3675.02001953125, 3632.360107421875, 3593.60009765625, 3625.1298828125, 3622.6201171875, 3643.340087890625, 3618.053955078125, 3615.969970703125, 3630.112060546875, 3597.0, 3619.18994140625, 3639.780029296875, 3632.330078125, 3595.179931640625, 3586.080078125, 3579.5400390625, 3593.52001953125, 3567.43994140625, 3597.429931640625, 3555.260009765625, 3521.260009765625, 3541.669921875, 3569.909912109375, 3558.179931640625, 3555.06005859375, 3522.570068359375, 3524.110107421875, 3433.06005859375, 3455.669921875, 3394.25, 3361.43994140625, 3429.580078125, 3452.6298828125, 3479.949951171875, 3485.909912109375, 3462.949951171875, 3428.8798828125, 3446.090087890625, 3465.830078125, 3468.0400390625, 3490.760009765625, 3490.610107421875, 3457.14990234375, 3489.14990234375, 3429.9599609375, 3451.409912109375, 3462.31005859375, 3488.830078125, 3484.18994140625, 3481.110107421875, 3447.64990234375, 3372.860107421875, 3293.530029296875, 3256.389892578125, 3296.090087890625, 3309.75, 3223.530029296875, 3063.969970703125, 3170.7099609375, 3215.0400390625, 3251.070068359375, 3253.68994140625, 3259.860107421875, 3271.030029296875, 3250.260009765625, 3212.239990234375, 3214.5, 3203.93994140625, 3266.60009765625, 3252.199951171875, 3282.719970703125, 3283.429931640625, 3236.699951171875, 3251.85009765625, 3167.1298828125, 3213.330078125, 3186.820068359375, 3225.639892578125, 3211.2451171875, 3195.52001953125, 3194.030029296875, 3151.050048828125, 3079.81005859375, 3086.919921875, 2928.510009765625, 2886.429931640625, 2958.280029296875, 2975.47998046875, 3047.06005859375, 3067.760009765625, 3001.56005859375, 3004.139892578125, 3035.840087890625, 3058.699951171875, 3054.989990234375, 3084.280029296875, 3073.75, 3093.699951171875, 3085.97998046875, 3096.9599609375, 3146.570068359375, 3146.860107421875, 3070.929931640625, 3107.4599609375, 3123.110107421875, 3130.239990234375, 3149.06005859375, 3186.429931640625, 3182.159912109375, 3195.4599609375, 3236.3701171875, 3241.760009765625, 3263.7900390625, 3238.949951171875, 3284.830078125, 3255.550048828125, 3288.909912109375, 3305.409912109375, 3285.3798828125, 3316.7900390625, 3315.429931640625, 3306.719970703125, 3267.199951171875, 3320.14990234375, 3349.75, 3379.18994140625, 3409.2099609375, 3361.52001953125, 3398.6201171875, 3387.639892578125, 3405.429931640625, 3404.030029296875, 3355.35009765625, 3364.39990234375, 3356.080078125, 3313.580078125, 3281.469970703125, 3284.2900390625, 3281.739990234375, 3228.06005859375, 3278.10009765625, 3279.429931640625, 3304.719970703125, 3272.0, 3269.969970703125, 3250.389892578125, 3277.43994140625, 3275.760009765625, 3282.580078125, 3253.239990234375, 3259.9599609375, 3186.27001953125, 3163.669921875, 3189.0400390625, 3227.030029296875, 3236.929931640625, 3247.429931640625, 3230.02001953125, 3281.669921875, 3276.889892578125, 3276.090087890625, 3277.8798828125, 3292.530029296875, 3277.5400390625, 3258.080078125, 3277.7900390625, 3276.219970703125, 3215.199951171875, 3246.25, 3236.219970703125, 3240.72998046875, 3227.2</t>
+          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-10', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-04-30', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-03', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-25', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-02', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-22', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-21', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-15', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-05', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-30', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-24', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-26', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-06', '2023-04-07', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-29', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-17', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-25', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-03-29', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-25', '2024-12-26', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-18', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-25', '2025-12-26', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-03', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [3085.197998046875, 3083.785888671875, 3083.407958984375, 3104.802001953125, 3066.89306640625, 3094.882080078125, 3092.291015625, 3115.570068359375, 3106.820068359375, 3090.0400390625, 3074.0810546875, 3075.49609375, 3095.787109375, 3052.139892578125, 3060.7548828125, 2976.528076171875, 2746.60595703125, 2783.2880859375, 2818.087890625, 2866.510009765625, 2875.9599609375, 2890.488037109375, 2901.669921875, 2926.89892578125, 2906.073974609375, 2917.008056640625, 2983.6220703125, 2984.971923828125, 2975.402099609375, 3030.154052734375, 3039.6689453125, 3031.23291015625, 3013.050048828125, 2987.928955078125, 2991.330078125, 2880.303955078125, 2970.930908203125, 2992.89697265625, 3011.666015625, 3071.677001953125, 3034.510986328125, 2943.291015625, 2996.761962890625, 2968.51708984375, 2923.486083984375, 2887.427001953125, 2789.25390625, 2779.64111328125, 2728.756103515625, 2702.1298828125, 2745.617919921875, 2660.169921875, 2722.43798828125, 2781.591064453125, 2764.910888671875, 2772.202880859375, 2747.214111328125, 2750.2958984375, 2734.52197265625, 2780.637939453125, 2763.987060546875, 2820.762939453125, 2815.368896484375, 2825.904052734375, 2796.631103515625, 2783.048095703125, 2827.282958984375, 2811.174072265625, 2819.93505859375, 2838.4951171875, 2852.552978515625, 2827.012939453125, 2843.97998046875, 2838.4990234375, 2808.529052734375, 2815.4951171875, 2810.02392578125, 2822.44189453125, 2860.08203125, 2878.139892578125, 2871.52294921875, 2895.340087890625, 2894.800048828125, 2891.555908203125, 2898.050048828125, 2870.342041015625, 2868.458984375, 2875.41796875, 2898.575927734375, 2883.738037109375, 2867.924072265625, 2813.764892578125, 2817.969970703125, 2846.547119140625, 2836.803955078125, 2846.221923828125, 2852.35107421875, 2915.430908203125, 2921.39794921875, 2923.37109375, 2919.2509765625, 2930.799072265625, 2937.77099609375, 2956.112060546875, 2943.7529296875, 2920.89697265625, 2919.740966796875, 2890.030029296875, 2931.75, 2935.8701171875, 2939.320068359375, 2967.6298828125, 2965.27197265625, 2970.6201171875, 2979.551025390625, 2961.51611328125, 2984.674072265625, 3025.98095703125, 3090.569091796875, 3152.81298828125, 3332.881103515625, 3345.3369140625, 3403.43994140625, 3450.593994140625, 3383.322021484375, 3443.285888671875, 3414.618896484375, 3361.303955078125, 3210.09912109375, 3214.12890625, 3314.14892578125, 3320.89501953125, 3333.1640625, 3325.110107421875, 3196.76806640625, 3205.22705078125, 3227.9599609375, 3294.552001953125, 3286.822021484375, 3310.007080078125, 3367.966064453125, 3371.68994140625, 3377.56005859375, 3386.4599609375, 3354.034912109375, 3379.251953125, 3340.2900390625, 3319.26611328125, 3320.72607421875, 3360.09912109375, 3438.801025390625, 3451.089111328125, 3408.12890625, 3363.89892578125, 3380.68310546875, 3385.637939453125, 3373.577880859375, 3329.739013671875, 3350.110107421875, 3403.806884765625, 3395.677978515625, 3410.60693359375, 3404.802001953125, 3384.98095703125, 3355.366943359375, 3292.591064453125, 3316.4169921875, 3254.6279296875, 3234.822998046875, 3260.345947265625, 3278.81396484375, 3295.679931640625, 3283.924072265625, 3270.43505859375, 3338.090087890625, 3316.93505859375, 3274.302001953125, 3279.7109375, 3223.176025390625, 3219.41796875, 3217.534912109375, 3224.35888671875, 3218.052001953125, 3272.075927734375, 3358.465087890625, 3359.75, 3340.778076171875, 3332.18310546875, 3336.35791015625, 3312.669921875, 3328.10009765625, 3325.02001953125, 3312.5, 3277.9970703125, 3251.118896484375, 3254.31591796875, 3269.239990234375, 3272.72998046875, 3224.532958984375, 3225.1201171875, 3271.073974609375, 3277.43994140625, 3320.133056640625, 3312.158935546875, 3373.72998046875, 3360.14892578125, 3342.202880859375, 3338.679931640625, 3310.10498046875, 3346.968994140625, 3339.89990234375, 3347.302978515625, 3363.087890625, 3377.72998046875, 3414.489990234375, 3402.822998046875, 3362.326904296875, 3369.73291015625, 3408.306884765625, 3391.760009765625, 3451.93994140625, 3449.381103515625, 3442.135986328125, 3444.5810546875, 3416.60400390625, 3410.179931640625, 3371.964111328125, 3373.27587890625, 3347.19091796875, 3369.1201171875, 3367.22998046875, 3366.98291015625, 3404.873046875, 3394.89990234375, 3420.569091796875, 3356.781982421875, 3382.320068359375, 3363.113037109375, 3396.56298828125, 3397.284912109375, 3379.035888671875, 3414.452880859375, 3473.069091796875, 3502.9580078125, 3528.677001953125, 3550.876953125, 3576.205078125, 3570.110107421875, 3531.498046875, 3608.340087890625, 3598.652099609375, 3565.905029296875, 3566.3779296875, 3596.219970703125, 3566.3798828125, 3583.092041015625, 3621.263916015625, 3606.75, 3624.238037109375, 3569.428955078125, 3573.340087890625, 3505.176025390625, 3483.069091796875, 3505.283935546875, 3533.68505859375, 3517.30810546875, 3501.85888671875, 3496.330078125, 3532.447021484375, 3603.489013671875, 3655.087890625, 3675.35693359375, 3696.16796875, 3642.43994140625, 3636.360107421875, 3564.080078125, 3585.050048828125, 3509.080078125, 3551.39990234375, 3508.591064453125, 3576.89990234375, 3503.489990234375, 3501.987060546875, 3421.409912109375, 3359.2900390625, 3357.739990234375, 3436.830078125, 3453.080078125, 3419.949951171875, 3446.73291015625, 3445.551025390625, 3463.068115234375, 3404.659912109375, 3443.43994140625, 3411.510009765625, 3367.06005859375, 3363.590087890625, 3418.326904296875, 3435.300048828125, 3456.679931640625, 3441.909912109375, 3466.330078125, 3484.39208984375, 3482.969970703125, 3479.6298828125, 3482.550048828125, 3450.679931640625, 3412.949951171875, 3396.469970703125, 3416.719970703125, 3398.989990234375, 3426.6201171875, 3477.550048828125, 3472.93994140625, 3472.929931640625, 3465.110107421875, 3474.169921875, 3441.169921875, 3442.610107421875, 3457.070068359375, 3474.89990234375, 3446.860107421875, 3441.280029296875, 3418.8701171875, 3427.989990234375, 3441.85009765625, 3462.75, 3429.5400390625, 3490.3798828125, 3517.6201171875, 3529.010009765625, 3510.9599609375, 3506.93994140625, 3486.56005859375, 3497.280029296875, 3581.340087890625, 3593.360107421875, 3608.85009765625, 3600.780029296875, 3615.47998046875, 3624.7099609375, 3597.139892578125, 3584.2099609375, 3591.840087890625, 3599.5400390625, 3580.110107421875, 3591.39990234375, 3610.860107421875, 3589.75, 3556.56005859375, 3518.330078125, 3525.60009765625, 3525.10009765625, 3529.179931640625, 3557.409912109375, 3566.219970703125, 3566.64990234375, 3607.56005859375, 3606.3701171875, 3573.179931640625, 3591.199951171875, 3588.780029296875, 3518.760009765625, 3534.320068359375, 3530.260009765625, 3553.719970703125, 3525.5, 3524.090087890625, 3547.840087890625, 3566.52001953125, 3528.5, 3564.590087890625, 3539.300048828125, 3539.1201171875, 3536.7900390625, 3562.660888671875, 3574.73388671875, 3550.39990234375, 3467.43994140625, 3381.179931640625, 3361.590087890625, 3411.719970703125, 3397.360107421875, 3464.2900390625, 3447.989990234375, 3477.219970703125, 3466.550048828125, 3458.22998046875, 3494.6298828125, 3529.929931640625, 3532.6201171875, 3524.739990234375, 3516.300048828125, 3517.340087890625, 3446.97607421875, 3485.285888671875, 3465.554931640625, 3427.333984375, 3477.1298828125, 3514.470947265625, 3540.3798828125, 3501.6640625, 3522.156982421875, 3528.15087890625, 3543.93994140625, 3567.10009765625, 3597.0400390625, 3581.72998046875, 3621.860107421875, 3676.590087890625, 3675.18994140625, 3693.1298828125, 3703.110107421875, 3715.3701171875, 3662.60009765625, 3656.219970703125, 3607.090087890625, 3613.969970703125, 3628.489990234375, 3642.219970703125, 3613.070068359375, 3582.830078125, 3602.219970703125, 3536.2900390625, 3568.169921875, 3592.169921875, 3591.7099609375, 3546.93994140625, 3561.760009765625, 3558.280029296875, 3572.3701171875, 3568.139892578125, 3593.14990234375, 3587.0, 3594.780029296875, 3582.60009765625, 3609.860107421875, 3597.639892578125, 3562.31005859375, 3518.419921875, 3547.340087890625, 3544.47998046875, 3505.6298828125, 3498.5400390625, 3526.8701171875, 3491.570068359375, 3498.6298828125, 3507.0, 3492.4599609375, 3532.7900390625, 3539.10009765625, 3533.300048828125, 3521.7900390625, 3537.3701171875, 3520.7099609375, 3560.3701171875, 3582.080078125, 3589.089111328125, 3592.702880859375, 3584.179931640625, 3564.090087890625, 3562.699951171875, 3563.889892578125, 3576.889892578125, 3573.840087890625, 3607.429931640625, 3589.31005859375, 3595.090087890625, 3637.570068359375, 3673.0400390625, 3666.35009765625, 3681.080078125, 3661.530029296875, 3647.6298828125, 3675.02001953125, 3632.360107421875, 3593.60009765625, 3625.1298828125, 3622.6201171875, 3643.340087890625, 3618.053955078125, 3615.969970703125, 3630.112060546875, 3597.0, 3619.18994140625, 3639.780029296875, 3632.330078125, 3595.179931640625, 3586.080078125, 3579.5400390625, 3593.52001953125, 3567.43994140625, 3597.429931640625, 3555.260009765625, 3521.260009765625, 3541.669921875, 3569.909912109375, 3558.179931640625, 3555.06005859375, 3522.570068359375, 3524.110107421875, 3433.06005859375, 3455.669921875, 3394.25, 3361.43994140625, 3429.580078125, 3452.6298828125, 3479.949951171875, 3485.909912109375, 3462.949951171875, 3428.8798828125, 3446.090087890625, 3465.830078125, 3468.0400390625, 3490.760009765625, 3490.610107421875, 3457.14990234375, 3489.14990234375, 3429.9599609375, 3451.409912109375, 3462.31005859375, 3488.830078125, 3484.18994140625, 3481.110107421875, 3447.64990234375, 3372.860107421875, 3293.530029296875, 3256.389892578125, 3296.090087890625, 3309.75, 3223.530029296875, 3063.969970703125, 3170.7099609375, 3215.0400390625, 3251.070068359375, 3253.68994140625, 3259.860107421875, 3271.030029296875, 3250.260009765625, 3212.239990234375, 3214.5, 3203.93994140625, 3266.60009765625, 3252.199951171875, 3282.719970703125, 3283.429931640625, 3236.699951171875, 3251.85009765625, 3167.1298828125, 3213.330078125, 3186.820068359375, 3225.639892578125, 3211.2451171875, 3195.52001953125, 3194.030029296875, 3151.050048828125, 3079.81005859375, 3086.919921875, 2928.510009765625, 2886.429931640625, 2958.280029296875, 2975.47998046875, 3047.06005859375, 3067.760009765625, 3001.56005859375, 3004.139892578125, 3035.840087890625, 3058.699951171875, 3054.989990234375, 3084.280029296875, 3073.75, 3093.699951171875, 3085.97998046875, 3096.9599609375, 3146.570068359375, 3146.860107421875, 3070.929931640625, 3107.4599609375, 3123.110107421875, 3130.239990234375, 3149.06005859375, 3186.429931640625, 3182.159912109375, 3195.4599609375, 3236.3701171875, 3241.760009765625, 3263.7900390625, 3238.949951171875, 3284.830078125, 3255.550048828125, 3288.909912109375, 3305.409912109375, 3285.3798828125, 3316.7900390625, 3315.429931640625, 3306.719970703125, 3267.199951171875, 3320.14990234375, 3349.75, 3379.18994140625, 3409.2099609375, 3361.52001953125, 3398.6201171875, 3387.639892578125, 3405.429931640625, 3404.030029296875, 3355.35009765625, 3364.39990234375, 3356.080078125, 3313.580078125, 3281.469970703125, 3284.2900390625, 3281.739990234375, 3228.06005859375, 3278.10009765625, 3279.429931640625, 3304.719970703125, 3272.0, 3269.969970703125, 3250.389892578125, 3277.43994140625, 3275.760009765625, 3282.580078125, 3253.239990234375, 3259.9599609375, 3186.27001953125, 3163.669921875, 3189.0400390625, 3227.030029296875, 3236.929931640625, 3247.429931640625, 3230.02001953125, 3281.669921875, 3276.889892578125, 3276.090087890625, 3277.8798828125, 3292.530029296875, 3277.540039062</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -2012,11 +2012,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25116.529296875</v>
+        <v>26160.330078125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2051,27 +2051,27 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2080,37 +2080,37 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>25362.62890625</v>
+        <v>25445.864453125</v>
       </c>
       <c r="Q7" t="n">
-        <v>26251.09475911459</v>
+        <v>26161.81409505208</v>
       </c>
       <c r="R7" t="n">
-        <v>26118.27490234375</v>
+        <v>26112.64680989583</v>
       </c>
       <c r="S7" t="n">
-        <v>24528.52632913961</v>
+        <v>24699.29067953531</v>
       </c>
       <c r="T7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="b">
         <v>1</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-02', '2020-07-03', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-02', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-21', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-30', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-24', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-06', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-29', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-02', '2024-04-03', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-02', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-16', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02'], 'prices': [28543.51953125, 28451.5, 28226.189453125, 28322.060546875, 28087.919921875, 28561.0, 28638.19921875, 28954.939453125, 28885.140625, 28773.58984375, 28883.0390625, 29056.419921875, 28795.91015625, 27985.330078125, 28341.0390625, 27909.119140625, 27949.640625, 27160.630859375, 26449.130859375, 26312.630859375, 26356.98046875, 26675.98046875, 26786.740234375, 27493.69921875, 27404.26953125, 27241.33984375, 27583.880859375, 27823.66015625, 27730.0, 27815.599609375, 27959.599609375, 27530.19921875, 27655.810546875, 27609.16015625, 27308.810546875, 26820.880859375, 26893.23046875, 26696.490234375, 26778.619140625, 26129.9296875, 26291.6796875, 26284.8203125, 26222.0703125, 26767.869140625, 26146.669921875, 25040.4609375, 25392.509765625, 25231.609375, 24309.0703125, 24032.91015625, 23063.5703125, 23263.73046875, 22291.8203125, 21709.130859375, 22805.0703125, 21696.130859375, 22663.490234375, 23527.189453125, 23352.33984375, 23484.279296875, 23175.109375, 23603.48046875, 23085.7890625, 23280.060546875, 23236.109375, 23749.119140625, 24253.2890625, 23970.369140625, 24300.330078125, 24435.400390625, 24145.33984375, 24006.44921875, 24380.0, 24330.01953125, 23793.55078125, 23893.359375, 23977.3203125, 23831.330078125, 24280.140625, 24575.9609375, 24643.58984375, 23613.80078125, 23868.66015625, 24137.48046875, 23980.630859375, 24230.169921875, 24602.060546875, 24245.6796875, 24180.30078125, 23829.740234375, 23797.470703125, 23934.76953125, 24388.130859375, 24399.94921875, 24280.029296875, 22930.140625, 22952.240234375, 23384.66015625, 23301.359375, 23132.759765625, 22961.470703125, 23732.51953125, 23995.939453125, 24325.619140625, 24366.30078125, 24770.41015625, 24776.76953125, 25057.220703125, 25049.73046875, 24480.150390625, 24301.380859375, 23776.94921875, 24344.08984375, 24481.41015625, 24464.939453125, 24643.890625, 24511.33984375, 24907.33984375, 24781.580078125, 24549.990234375, 24301.279296875, 24427.189453125, 25124.189453125, 25373.119140625, 26339.16015625, 25975.66015625, 26129.1796875, 26210.16015625, 25727.41015625, 25772.119140625, 25477.890625, 25481.580078125, 24970.689453125, 25089.169921875, 25057.990234375, 25635.66015625, 25057.939453125, 25263.0, 24705.330078125, 24603.259765625, 24772.759765625, 24883.140625, 24710.58984375, 24595.349609375, 24458.130859375, 24946.630859375, 25102.5390625, 24930.580078125, 24531.619140625, 24377.4296875, 24890.6796875, 25244.01953125, 25230.669921875, 25183.009765625, 25347.33984375, 25367.380859375, 25178.91015625, 24791.390625, 25113.83984375, 25551.580078125, 25486.220703125, 25491.7890625, 25281.150390625, 25422.060546875, 25177.05078125, 25184.849609375, 25120.08984375, 25007.599609375, 24695.44921875, 24589.650390625, 24624.33984375, 24468.9296875, 24313.5390625, 24503.310546875, 24640.279296875, 24732.759765625, 24725.630859375, 24340.849609375, 24455.41015625, 23950.689453125, 23716.849609375, 23742.509765625, 23311.0703125, 23235.419921875, 23476.05078125, 23275.529296875, 23459.05078125, 23767.779296875, 23980.650390625, 24242.859375, 24193.349609375, 24119.130859375, 24649.6796875, 24667.08984375, 24158.5390625, 24386.7890625, 24542.259765625, 24569.5390625, 24754.419921875, 24786.130859375, 24918.779296875, 24787.189453125, 24708.80078125, 24586.599609375, 24107.419921875, 24460.009765625, 24939.73046875, 24886.140625, 25695.919921875, 25712.970703125, 26016.169921875, 26301.48046875, 26226.98046875, 26169.380859375, 26156.859375, 26381.669921875, 26415.08984375, 26544.2890625, 26356.970703125, 26451.5390625, 26486.19921875, 26588.19921875, 26669.75, 26819.44921875, 26894.6796875, 26341.490234375, 26567.6796875, 26532.580078125, 26728.5, 26835.919921875, 26506.849609375, 26304.560546875, 26502.83984375, 26410.58984375, 26505.869140625, 26389.51953125, 26207.2890625, 26460.2890625, 26678.380859375, 26498.599609375, 26306.6796875, 26119.25, 26343.099609375, 26386.560546875, 26314.630859375, 26568.490234375, 27147.109375, 27231.130859375, 27472.810546875, 27649.859375, 27692.30078125, 27548.51953125, 27878.220703125, 27908.220703125, 28276.75, 28235.599609375, 28496.859375, 28573.859375, 28862.76953125, 29642.279296875, 29962.470703125, 29927.759765625, 29447.849609375, 30159.009765625, 29391.259765625, 29297.529296875, 28550.76953125, 28283.7109375, 28892.859375, 29248.69921875, 29307.4609375, 29113.5, 29288.6796875, 29319.470703125, 29476.189453125, 30038.720703125, 30173.5703125, 30746.66015625, 31084.939453125, 30595.26953125, 30644.73046875, 30319.830078125, 30632.640625, 29718.240234375, 30074.169921875, 28980.2109375, 29452.5703125, 29095.859375, 29880.419921875, 29236.7890625, 29098.2890625, 28540.830078125, 28773.23046875, 28907.51953125, 29385.609375, 28739.720703125, 28833.759765625, 29027.689453125, 29034.119140625, 29405.720703125, 28990.939453125, 28885.33984375, 28497.380859375, 27918.140625, 27899.609375, 28336.4296875, 28338.30078125, 28577.5, 28378.349609375, 28938.740234375, 28674.80078125, 29008.0703125, 28698.80078125, 28453.279296875, 28497.25, 28900.830078125, 28793.140625, 28969.7109375, 29106.150390625, 29135.73046875, 28621.919921875, 28755.33984375, 29078.75, 28952.830078125, 28941.5390625, 29071.33984375, 29303.259765625, 28724.880859375, 28357.5390625, 28557.140625, 28417.98046875, 28637.4609375, 28610.650390625, 28595.66015625, 28013.810546875, 28231.0390625, 27718.669921875, 28027.5703125, 28194.08984375, 28593.810546875, 28450.2890625, 28458.439453125, 28412.259765625, 28910.859375, 29166.009765625, 29113.19921875, 29124.41015625, 29151.80078125, 29468.0, 29297.619140625, 28966.029296875, 28918.099609375, 28787.279296875, 28781.380859375, 28742.630859375, 28738.880859375, 28842.130859375, 28638.529296875, 28436.83984375, 28558.58984375, 28801.26953125, 28489.0, 28309.759765625, 28817.0703125, 28882.4609375, 29288.220703125, 29268.30078125, 28994.099609375, 28827.94921875, 28310.419921875, 28143.5, 28072.859375, 27960.619140625, 27153.130859375, 27344.5390625, 27515.240234375, 27963.41015625, 27787.4609375, 27996.26953125, 28004.6796875, 27489.779296875, 27259.25, 27224.580078125, 27723.83984375, 27321.98046875, 26192.3203125, 25086.4296875, 25473.880859375, 26315.3203125, 25961.029296875, 26235.80078125, 26194.8203125, 26426.55078125, 26204.689453125, 26179.400390625, 26283.400390625, 26605.619140625, 26660.16015625, 26517.8203125, 26391.619140625, 26181.4609375, 25745.869140625, 25867.009765625, 25316.330078125, 24849.720703125, 25109.58984375, 25727.919921875, 25693.94921875, 25415.689453125, 25407.890625, 25539.5390625, 25878.990234375, 26028.2890625, 26090.4296875, 25901.990234375, 26163.630859375, 26353.630859375, 26320.9296875, 25716.0, 26205.91015625, 25813.810546875, 25502.23046875, 25033.2109375, 24667.849609375, 24920.759765625, 24099.140625, 24221.5390625, 24510.98046875, 24192.16015625, 24208.779296875, 24500.390625, 24663.5, 24575.640625, 24036.369140625, 24104.150390625, 23966.490234375, 24701.73046875, 24837.849609375, 25325.08984375, 24962.58984375, 25330.9609375, 25409.75, 25787.2109375, 26136.01953125, 26017.529296875, 26126.9296875, 26132.029296875, 26038.26953125, 25628.740234375, 25555.73046875, 25377.240234375, 25154.3203125, 25099.669921875, 25024.75, 25225.189453125, 24870.509765625, 24763.76953125, 24813.130859375, 24996.140625, 25247.990234375, 25327.970703125, 25390.91015625, 25713.779296875, 25650.080078125, 25319.720703125, 25049.970703125, 24951.33984375, 24651.580078125, 24685.5, 24740.16015625, 24080.51953125, 23852.240234375, 23475.259765625, 23658.919921875, 23788.9296875, 23766.689453125, 23349.380859375, 23983.66015625, 23996.869140625, 24254.859375, 23995.720703125, 23954.580078125, 23635.94921875, 23420.759765625, 23475.5, 23192.630859375, 22744.859375, 22971.330078125, 23102.330078125, 23193.640625, 23223.759765625, 23280.560546875, 23086.5390625, 23112.009765625, 23397.669921875, 23274.75, 23289.83984375, 22907.25, 23072.859375, 23493.380859375, 23746.5390625, 23739.060546875, 24402.169921875, 24429.76953125, 24383.3203125, 24218.029296875, 24112.779296875, 24127.849609375, 24952.349609375, 24965.55078125, 24656.4609375, 24243.609375, 24289.900390625, 23807.0, 23550.080078125, 23802.259765625, 24573.2890625, 24579.55078125, 24329.490234375, 24829.990234375, 24924.349609375, 24906.66015625, 24556.5703125, 24355.7109375, 24718.900390625, 24792.76953125, 24327.7109375, 24170.0703125, 23520.0, 23660.279296875, 22901.560546875, 22767.1796875, 22713.01953125, 22761.7109375, 22343.919921875, 22467.33984375, 21905.2890625, 21057.630859375, 20765.869140625, 20627.7109375, 20890.259765625, 20553.7890625, 19531.66015625, 18415.080078125, 20087.5, 21501.23046875, 21412.400390625, 21221.33984375, 21889.279296875, 22154.080078125, 21945.94921875, 21404.880859375, 21684.970703125, 21927.630859375, 22232.029296875, 21996.849609375, 22039.55078125, 22502.310546875, 22080.51953125, 21808.98046875, 21872.009765625, 21208.30078125, 21319.130859375, 21374.369140625, 21518.080078125, 21027.759765625, 20944.669921875, 20682.220703125, 20638.51953125, 19869.33984375, 19934.7109375, 19946.359375, 20276.169921875, 21089.390625, 21101.890625, 20869.51953125, 20793.400390625, 20001.9609375, 19633.689453125, 19824.5703125, 19380.33984375, 19898.76953125, 19950.2109375, 20602.51953125, 20644.279296875, 20120.6796875, 20717.240234375, 20470.060546875, 20112.099609375, 20171.26953125, 20116.19921875, 20697.359375, 21123.9296875, 21415.19921875, 21294.939453125, 21082.130859375, 21653.900390625, 21531.669921875, 22014.58984375, 21869.05078125, 21806.1796875, 21067.580078125, 21067.990234375, 21308.2109375, 20845.4296875, 21075.0, 21163.91015625, 21559.58984375, 21008.33984375, 21273.869140625, 21719.060546875, 22229.51953125, 22418.970703125, 21996.890625, 21859.7890625, 21830.349609375, 21853.0703125, 21586.66015625, 21643.580078125, 21725.779296875, 21124.19921875, 20844.740234375, 20797.94921875, 20751.2109375, 20297.720703125, 20846.1796875, 20661.060546875, 20890.220703125, 20574.630859375, 20609.140625, 20562.939453125, 20905.880859375, 20670.0390625, 20622.6796875, 20156.509765625, 20165.83984375, 19689.2109375, 19767.08984375, 20174.0390625, 20201.939453125, 20045.76953125, 20003.439453125, 19610.83984375, 20082.4296875, 20175.619140625, 20040.859375, 19830.51953125, 19922.44921875, 19763.91015625, 19773.029296875, 19656.98046875, 19503.25, 19268.740234375, 19968.380859375, 20170.0390625, 20023.220703125, 19949.029296875, 19954.390625, 19597.310546875, 19452.08984375, 19225.69921875, 19202.73046875, 19044.30078125, 18854.619140625, 19362.25, 19326.859375, 18847.099609375, 18930.380859375, 18761.689453125, 18565.970703125, 18781.419921875, 18444.619140625, 18147.94921875, 17933.26953125, 17855.140625, 17860.310546875, 17250.880859375, 17165.869140625, 17222.830078125, 17079.509765625, 18087.970703125, 18012.150390625, 17740.05078125, 17216.66015625, 16832.359375, 16701.029296875, 16389.109375, 16587.689453125, 16612.900390625, 16914.580078125, 16511.279296875, 16280.2197265625, 16211.1201171875, 15180.6904296875, 15165.58984375, 15317.669921875, 15427.9404296875, 14863.0595703125, 14687.01953125, 15455.26953125, 15827.169921875, 15339.490234375, 16161.1396484375, 16595.91015625, 16557.310546875, 163</t>
+          <t>{'dates': ['2020-01-02', '2020-01-03', '2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-13', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-11', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-24', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-20', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-29', '2020-05-04', '2020-05-05', '2020-05-06', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-02', '2020-07-03', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-23', '2020-07-24', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-10', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-21', '2020-09-22', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-03', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-23', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-28', '2020-12-29', '2020-12-30', '2020-12-31', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-11', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-11', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-23', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-29', '2021-04-30', '2021-05-03', '2021-05-04', '2021-05-05', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-02', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-22', '2021-07-23', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-09', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-20', '2021-09-21', '2021-09-23', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-03', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-23', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-28', '2021-12-29', '2021-12-30', '2021-12-31', '2022-01-03', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-10', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-11', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-21', '2022-02-22', '2022-02-23', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-21', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-04-29', '2022-05-03', '2022-05-04', '2022-05-05', '2022-05-06', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-30', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-18', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-11', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-19', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-23', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-10', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-03', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-23', '2022-11-24', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-03', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-09', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-23', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-21', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-06', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-02', '2023-05-03', '2023-05-04', '2023-05-05', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-29', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-11', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-18', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-09', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-03', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-23', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-02', '2024-01-03', '2024-01-04', '2024-01-05', '2024-01-08', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-23', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-20', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-04-02', '2024-04-03', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-29', '2024-04-30', '2024-05-02', '2024-05-03', '2024-05-06', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-15', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-12', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-16', '2024-09-17', '2024-09-19', '2024-09-20', '2024-09-23', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-14', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-04', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-27', '2024-12-30', '2024-12-31', '2025-01-02', '2025-01-03', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-13', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-11', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-24', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-20', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-29', '2025-04-30', '2025-05-02', '2025-05-06', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-21', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-11', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-15', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-23', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-13', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-30', '2025-10-31', '2025-11-03', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-24', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-29', '2025-12-30', '2025-12-31', '2026-01-02', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-12', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-11', '2026-02-12', '2026-02-13', '2026-02-16', '2026-02-20', '2026-02-23', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [28543.51953125, 28451.5, 28226.189453125, 28322.060546875, 28087.919921875, 28561.0, 28638.19921875, 28954.939453125, 28885.140625, 28773.58984375, 28883.0390625, 29056.419921875, 28795.91015625, 27985.330078125, 28341.0390625, 27909.119140625, 27949.640625, 27160.630859375, 26449.130859375, 26312.630859375, 26356.98046875, 26675.98046875, 26786.740234375, 27493.69921875, 27404.26953125, 27241.33984375, 27583.880859375, 27823.66015625, 27730.0, 27815.599609375, 27959.599609375, 27530.19921875, 27655.810546875, 27609.16015625, 27308.810546875, 26820.880859375, 26893.23046875, 26696.490234375, 26778.619140625, 26129.9296875, 26291.6796875, 26284.8203125, 26222.0703125, 26767.869140625, 26146.669921875, 25040.4609375, 25392.509765625, 25231.609375, 24309.0703125, 24032.91015625, 23063.5703125, 23263.73046875, 22291.8203125, 21709.130859375, 22805.0703125, 21696.130859375, 22663.490234375, 23527.189453125, 23352.33984375, 23484.279296875, 23175.109375, 23603.48046875, 23085.7890625, 23280.060546875, 23236.109375, 23749.119140625, 24253.2890625, 23970.369140625, 24300.330078125, 24435.400390625, 24145.33984375, 24006.44921875, 24380.0, 24330.01953125, 23793.55078125, 23893.359375, 23977.3203125, 23831.330078125, 24280.140625, 24575.9609375, 24643.58984375, 23613.80078125, 23868.66015625, 24137.48046875, 23980.630859375, 24230.169921875, 24602.060546875, 24245.6796875, 24180.30078125, 23829.740234375, 23797.470703125, 23934.76953125, 24388.130859375, 24399.94921875, 24280.029296875, 22930.140625, 22952.240234375, 23384.66015625, 23301.359375, 23132.759765625, 22961.470703125, 23732.51953125, 23995.939453125, 24325.619140625, 24366.30078125, 24770.41015625, 24776.76953125, 25057.220703125, 25049.73046875, 24480.150390625, 24301.380859375, 23776.94921875, 24344.08984375, 24481.41015625, 24464.939453125, 24643.890625, 24511.33984375, 24907.33984375, 24781.580078125, 24549.990234375, 24301.279296875, 24427.189453125, 25124.189453125, 25373.119140625, 26339.16015625, 25975.66015625, 26129.1796875, 26210.16015625, 25727.41015625, 25772.119140625, 25477.890625, 25481.580078125, 24970.689453125, 25089.169921875, 25057.990234375, 25635.66015625, 25057.939453125, 25263.0, 24705.330078125, 24603.259765625, 24772.759765625, 24883.140625, 24710.58984375, 24595.349609375, 24458.130859375, 24946.630859375, 25102.5390625, 24930.580078125, 24531.619140625, 24377.4296875, 24890.6796875, 25244.01953125, 25230.669921875, 25183.009765625, 25347.33984375, 25367.380859375, 25178.91015625, 24791.390625, 25113.83984375, 25551.580078125, 25486.220703125, 25491.7890625, 25281.150390625, 25422.060546875, 25177.05078125, 25184.849609375, 25120.08984375, 25007.599609375, 24695.44921875, 24589.650390625, 24624.33984375, 24468.9296875, 24313.5390625, 24503.310546875, 24640.279296875, 24732.759765625, 24725.630859375, 24340.849609375, 24455.41015625, 23950.689453125, 23716.849609375, 23742.509765625, 23311.0703125, 23235.419921875, 23476.05078125, 23275.529296875, 23459.05078125, 23767.779296875, 23980.650390625, 24242.859375, 24193.349609375, 24119.130859375, 24649.6796875, 24667.08984375, 24158.5390625, 24386.7890625, 24542.259765625, 24569.5390625, 24754.419921875, 24786.130859375, 24918.779296875, 24787.189453125, 24708.80078125, 24586.599609375, 24107.419921875, 24460.009765625, 24939.73046875, 24886.140625, 25695.919921875, 25712.970703125, 26016.169921875, 26301.48046875, 26226.98046875, 26169.380859375, 26156.859375, 26381.669921875, 26415.08984375, 26544.2890625, 26356.970703125, 26451.5390625, 26486.19921875, 26588.19921875, 26669.75, 26819.44921875, 26894.6796875, 26341.490234375, 26567.6796875, 26532.580078125, 26728.5, 26835.919921875, 26506.849609375, 26304.560546875, 26502.83984375, 26410.58984375, 26505.869140625, 26389.51953125, 26207.2890625, 26460.2890625, 26678.380859375, 26498.599609375, 26306.6796875, 26119.25, 26343.099609375, 26386.560546875, 26314.630859375, 26568.490234375, 27147.109375, 27231.130859375, 27472.810546875, 27649.859375, 27692.30078125, 27548.51953125, 27878.220703125, 27908.220703125, 28276.75, 28235.599609375, 28496.859375, 28573.859375, 28862.76953125, 29642.279296875, 29962.470703125, 29927.759765625, 29447.849609375, 30159.009765625, 29391.259765625, 29297.529296875, 28550.76953125, 28283.7109375, 28892.859375, 29248.69921875, 29307.4609375, 29113.5, 29288.6796875, 29319.470703125, 29476.189453125, 30038.720703125, 30173.5703125, 30746.66015625, 31084.939453125, 30595.26953125, 30644.73046875, 30319.830078125, 30632.640625, 29718.240234375, 30074.169921875, 28980.2109375, 29452.5703125, 29095.859375, 29880.419921875, 29236.7890625, 29098.2890625, 28540.830078125, 28773.23046875, 28907.51953125, 29385.609375, 28739.720703125, 28833.759765625, 29027.689453125, 29034.119140625, 29405.720703125, 28990.939453125, 28885.33984375, 28497.380859375, 27918.140625, 27899.609375, 28336.4296875, 28338.30078125, 28577.5, 28378.349609375, 28938.740234375, 28674.80078125, 29008.0703125, 28698.80078125, 28453.279296875, 28497.25, 28900.830078125, 28793.140625, 28969.7109375, 29106.150390625, 29135.73046875, 28621.919921875, 28755.33984375, 29078.75, 28952.830078125, 28941.5390625, 29071.33984375, 29303.259765625, 28724.880859375, 28357.5390625, 28557.140625, 28417.98046875, 28637.4609375, 28610.650390625, 28595.66015625, 28013.810546875, 28231.0390625, 27718.669921875, 28027.5703125, 28194.08984375, 28593.810546875, 28450.2890625, 28458.439453125, 28412.259765625, 28910.859375, 29166.009765625, 29113.19921875, 29124.41015625, 29151.80078125, 29468.0, 29297.619140625, 28966.029296875, 28918.099609375, 28787.279296875, 28781.380859375, 28742.630859375, 28738.880859375, 28842.130859375, 28638.529296875, 28436.83984375, 28558.58984375, 28801.26953125, 28489.0, 28309.759765625, 28817.0703125, 28882.4609375, 29288.220703125, 29268.30078125, 28994.099609375, 28827.94921875, 28310.419921875, 28143.5, 28072.859375, 27960.619140625, 27153.130859375, 27344.5390625, 27515.240234375, 27963.41015625, 27787.4609375, 27996.26953125, 28004.6796875, 27489.779296875, 27259.25, 27224.580078125, 27723.83984375, 27321.98046875, 26192.3203125, 25086.4296875, 25473.880859375, 26315.3203125, 25961.029296875, 26235.80078125, 26194.8203125, 26426.55078125, 26204.689453125, 26179.400390625, 26283.400390625, 26605.619140625, 26660.16015625, 26517.8203125, 26391.619140625, 26181.4609375, 25745.869140625, 25867.009765625, 25316.330078125, 24849.720703125, 25109.58984375, 25727.919921875, 25693.94921875, 25415.689453125, 25407.890625, 25539.5390625, 25878.990234375, 26028.2890625, 26090.4296875, 25901.990234375, 26163.630859375, 26353.630859375, 26320.9296875, 25716.0, 26205.91015625, 25813.810546875, 25502.23046875, 25033.2109375, 24667.849609375, 24920.759765625, 24099.140625, 24221.5390625, 24510.98046875, 24192.16015625, 24208.779296875, 24500.390625, 24663.5, 24575.640625, 24036.369140625, 24104.150390625, 23966.490234375, 24701.73046875, 24837.849609375, 25325.08984375, 24962.58984375, 25330.9609375, 25409.75, 25787.2109375, 26136.01953125, 26017.529296875, 26126.9296875, 26132.029296875, 26038.26953125, 25628.740234375, 25555.73046875, 25377.240234375, 25154.3203125, 25099.669921875, 25024.75, 25225.189453125, 24870.509765625, 24763.76953125, 24813.130859375, 24996.140625, 25247.990234375, 25327.970703125, 25390.91015625, 25713.779296875, 25650.080078125, 25319.720703125, 25049.970703125, 24951.33984375, 24651.580078125, 24685.5, 24740.16015625, 24080.51953125, 23852.240234375, 23475.259765625, 23658.919921875, 23788.9296875, 23766.689453125, 23349.380859375, 23983.66015625, 23996.869140625, 24254.859375, 23995.720703125, 23954.580078125, 23635.94921875, 23420.759765625, 23475.5, 23192.630859375, 22744.859375, 22971.330078125, 23102.330078125, 23193.640625, 23223.759765625, 23280.560546875, 23086.5390625, 23112.009765625, 23397.669921875, 23274.75, 23289.83984375, 22907.25, 23072.859375, 23493.380859375, 23746.5390625, 23739.060546875, 24402.169921875, 24429.76953125, 24383.3203125, 24218.029296875, 24112.779296875, 24127.849609375, 24952.349609375, 24965.55078125, 24656.4609375, 24243.609375, 24289.900390625, 23807.0, 23550.080078125, 23802.259765625, 24573.2890625, 24579.55078125, 24329.490234375, 24829.990234375, 24924.349609375, 24906.66015625, 24556.5703125, 24355.7109375, 24718.900390625, 24792.76953125, 24327.7109375, 24170.0703125, 23520.0, 23660.279296875, 22901.560546875, 22767.1796875, 22713.01953125, 22761.7109375, 22343.919921875, 22467.33984375, 21905.2890625, 21057.630859375, 20765.869140625, 20627.7109375, 20890.259765625, 20553.7890625, 19531.66015625, 18415.080078125, 20087.5, 21501.23046875, 21412.400390625, 21221.33984375, 21889.279296875, 22154.080078125, 21945.94921875, 21404.880859375, 21684.970703125, 21927.630859375, 22232.029296875, 21996.849609375, 22039.55078125, 22502.310546875, 22080.51953125, 21808.98046875, 21872.009765625, 21208.30078125, 21319.130859375, 21374.369140625, 21518.080078125, 21027.759765625, 20944.669921875, 20682.220703125, 20638.51953125, 19869.33984375, 19934.7109375, 19946.359375, 20276.169921875, 21089.390625, 21101.890625, 20869.51953125, 20793.400390625, 20001.9609375, 19633.689453125, 19824.5703125, 19380.33984375, 19898.76953125, 19950.2109375, 20602.51953125, 20644.279296875, 20120.6796875, 20717.240234375, 20470.060546875, 20112.099609375, 20171.26953125, 20116.19921875, 20697.359375, 21123.9296875, 21415.19921875, 21294.939453125, 21082.130859375, 21653.900390625, 21531.669921875, 22014.58984375, 21869.05078125, 21806.1796875, 21067.580078125, 21067.990234375, 21308.2109375, 20845.4296875, 21075.0, 21163.91015625, 21559.58984375, 21008.33984375, 21273.869140625, 21719.060546875, 22229.51953125, 22418.970703125, 21996.890625, 21859.7890625, 21830.349609375, 21853.0703125, 21586.66015625, 21643.580078125, 21725.779296875, 21124.19921875, 20844.740234375, 20797.94921875, 20751.2109375, 20297.720703125, 20846.1796875, 20661.060546875, 20890.220703125, 20574.630859375, 20609.140625, 20562.939453125, 20905.880859375, 20670.0390625, 20622.6796875, 20156.509765625, 20165.83984375, 19689.2109375, 19767.08984375, 20174.0390625, 20201.939453125, 20045.76953125, 20003.439453125, 19610.83984375, 20082.4296875, 20175.619140625, 20040.859375, 19830.51953125, 19922.44921875, 19763.91015625, 19773.029296875, 19656.98046875, 19503.25, 19268.740234375, 19968.380859375, 20170.0390625, 20023.220703125, 19949.029296875, 19954.390625, 19597.310546875, 19452.08984375, 19225.69921875, 19202.73046875, 19044.30078125, 18854.619140625, 19362.25, 19326.859375, 18847.099609375, 18930.380859375, 18761.689453125, 18565.970703125, 18781.419921875, 18444.619140625, 18147.94921875, 17933.26953125, 17855.140625, 17860.310546875, 17250.880859375, 17165.869140625, 17222.830078125, 17079.509765625, 18087.970703125, 18012.150390625, 17740.05078125, 17216.66015625, 16832.359375, 16701.029296875, 16389.109375, 16587.689453125, 16612.900390625, 16914.580078125, 16511.279296875, 16280.2197265625, 16211.1201171875, 15180.6904296875, 15165.58984375, 15317.669921875, 15427.9404296875, 14863.0595703125, 14687.01</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
@@ -2121,11 +2121,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53123.48828125</v>
+        <v>58475.8984375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2160,27 +2160,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2189,22 +2189,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>53436.473828125</v>
+        <v>54662.4921875</v>
       </c>
       <c r="Q8" t="n">
-        <v>54431.33346354167</v>
+        <v>55038.51315104167</v>
       </c>
       <c r="R8" t="n">
-        <v>52129.10338541667</v>
+        <v>52850.89069010417</v>
       </c>
       <c r="S8" t="n">
-        <v>44261.57746550324</v>
+        <v>44816.65649096997</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>{'dates': ['2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-10', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-30', '2020-05-01', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-03', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-25', '2020-12-28', '2020-12-29', '2020-12-30', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-12', '2021-02-15', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-02', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-30', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-21', '2021-09-22', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-21', '2022-02-22', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-15', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-05-02', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-30', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-24', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-26', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-07', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-29', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-25', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-04', '2024-01-05', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-03-29', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-25', '2024-12-26', '2024-12-27', '2024-12-30', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-18', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-25', '2025-12-26', '2025-12-29', '2025-12-30', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-12', '2026-02-13', '2026-02-16', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-03'], 'prices': [23204.859375, 23575.720703125, 23204.759765625, 23739.869140625, 23850.5703125, 24025.169921875, 23916.580078125, 23933.130859375, 24041.259765625, 24083.509765625, 23864.560546875, 24031.349609375, 23795.439453125, 23827.1796875, 23343.509765625, 23215.7109375, 23379.400390625, 22977.75, 23205.1796875, 22971.939453125, 23084.58984375, 23319.560546875, 23873.58984375, 23827.98046875, 23685.98046875, 23861.2109375, 23827.73046875, 23687.58984375, 23523.240234375, 23193.80078125, 23400.69921875, 23479.150390625, 23386.740234375, 22605.41015625, 22426.189453125, 21948.23046875, 21142.9609375, 21344.080078125, 21082.73046875, 21100.060546875, 21329.119140625, 20749.75, 19698.759765625, 19867.119140625, 19416.060546875, 18559.630859375, 17431.05078125, 17002.0390625, 17011.529296875, 16726.55078125, 16552.830078125, 16887.779296875, 18092.349609375, 19546.630859375, 18664.599609375, 19389.4296875, 19084.970703125, 18917.009765625, 18065.41015625, 17818.720703125, 17820.189453125, 18576.30078125, 18950.1796875, 19353.240234375, 19345.76953125, 19498.5, 19043.400390625, 19638.810546875, 19550.08984375, 19290.19921875, 19897.259765625, 19669.119140625, 19280.779296875, 19137.94921875, 19429.439453125, 19262.0, 19783.220703125, 19771.189453125, 20193.689453125, 19619.349609375, 19674.76953125, 20179.08984375, 20390.66015625, 20366.48046875, 20267.05078125, 19914.779296875, 20037.470703125, 20133.73046875, 20433.44921875, 20595.150390625, 20552.310546875, 20388.16015625, 20741.650390625, 21271.169921875, 21419.23046875, 21916.310546875, 21877.890625, 22062.390625, 22325.609375, 22613.759765625, 22695.740234375, 22863.73046875, 23178.099609375, 23091.029296875, 23124.94921875, 22472.91015625, 22305.48046875, 21530.94921875, 22582.2109375, 22455.759765625, 22355.4609375, 22478.7890625, 22437.26953125, 22549.05078125, 22534.3203125, 22259.7890625, 22512.080078125, 21995.0390625, 22288.140625, 22121.73046875, 22145.9609375, 22306.48046875, 22714.439453125, 22614.689453125, 22438.650390625, 22529.2890625, 22290.810546875, 22784.740234375, 22587.009765625, 22945.5, 22770.359375, 22696.419921875, 22717.48046875, 22884.220703125, 22751.609375, 22715.849609375, 22657.380859375, 22397.109375, 22339.23046875, 21710.0, 22195.380859375, 22573.66015625, 22514.849609375, 22418.150390625, 22329.939453125, 22750.240234375, 22843.9609375, 23249.609375, 23289.359375, 23096.75, 23051.080078125, 23110.609375, 22880.619140625, 22920.30078125, 22985.509765625, 23296.76953125, 23290.859375, 23208.859375, 22882.650390625, 23139.759765625, 23138.0703125, 23247.150390625, 23465.529296875, 23205.4296875, 23089.94921875, 23274.130859375, 23032.5390625, 23235.470703125, 23406.490234375, 23559.30078125, 23454.890625, 23475.529296875, 23319.369140625, 23360.30078125, 23346.490234375, 23087.8203125, 23204.619140625, 23511.619140625, 23539.099609375, 23185.119140625, 23029.900390625, 23312.140625, 23433.73046875, 23422.8203125, 23647.0703125, 23619.689453125, 23558.689453125, 23601.779296875, 23626.73046875, 23507.23046875, 23410.630859375, 23671.130859375, 23567.0390625, 23639.4609375, 23474.26953125, 23516.58984375, 23494.33984375, 23485.80078125, 23418.509765625, 23331.939453125, 22977.130859375, 23295.48046875, 23695.23046875, 24105.279296875, 24325.23046875, 24839.83984375, 24905.58984375, 25349.599609375, 25520.880859375, 25385.869140625, 25906.9296875, 26014.619140625, 25728.140625, 25634.33984375, 25527.369140625, 26165.58984375, 26296.859375, 26537.310546875, 26644.7109375, 26433.619140625, 26787.5390625, 26800.98046875, 26809.369140625, 26751.240234375, 26547.439453125, 26467.080078125, 26817.939453125, 26756.240234375, 26652.51953125, 26732.439453125, 26687.83984375, 26757.400390625, 26806.669921875, 26763.390625, 26714.419921875, 26436.390625, 26524.7890625, 26668.349609375, 26656.609375, 26854.029296875, 27568.150390625, 27444.169921875, 27258.380859375, 27158.630859375, 27055.939453125, 27490.130859375, 28139.029296875, 28164.33984375, 28456.58984375, 28698.259765625, 28519.1796875, 28242.2109375, 28633.4609375, 28523.259765625, 28756.859375, 28631.44921875, 28822.2890625, 28546.1796875, 28635.2109375, 28197.419921875, 27663.390625, 28091.05078125, 28362.169921875, 28646.5, 28341.94921875, 28779.189453125, 29388.5, 29505.9296875, 29562.9296875, 29520.0703125, 30084.150390625, 30467.75, 30292.189453125, 30236.08984375, 30017.919921875, 30156.029296875, 29671.69921875, 30168.26953125, 28966.009765625, 29663.5, 29408.169921875, 29559.099609375, 28930.109375, 28864.3203125, 28743.25, 29027.939453125, 29036.560546875, 29211.640625, 29717.830078125, 29766.970703125, 29921.08984375, 29914.330078125, 30216.75, 29792.05078125, 29174.150390625, 28995.919921875, 28405.51953125, 28729.880859375, 29176.69921875, 29384.51953125, 29432.69921875, 29178.80078125, 29388.869140625, 29854.0, 30089.25, 29696.630859375, 29730.7890625, 29708.98046875, 29768.060546875, 29538.73046875, 29751.609375, 29620.990234375, 29642.689453125, 29683.369140625, 29685.369140625, 29100.380859375, 28508.55078125, 29188.169921875, 29020.630859375, 29126.23046875, 28991.890625, 29053.970703125, 28812.630859375, 29331.369140625, 29357.8203125, 29518.33984375, 28608.58984375, 28147.509765625, 27448.009765625, 28084.470703125, 27824.830078125, 28406.83984375, 28044.44921875, 28098.25, 28317.830078125, 28364.609375, 28553.98046875, 28642.189453125, 28549.009765625, 29149.41015625, 28860.080078125, 28814.33984375, 28946.140625, 29058.109375, 28941.51953125, 29019.240234375, 28963.560546875, 28860.80078125, 28958.560546875, 28948.73046875, 29161.80078125, 29441.30078125, 29291.009765625, 29018.330078125, 28964.080078125, 28010.9296875, 28884.130859375, 28874.890625, 28875.23046875, 29066.1796875, 29048.01953125, 28812.609375, 28791.529296875, 28707.0390625, 28783.279296875, 28598.189453125, 28643.2109375, 28366.94921875, 28118.029296875, 27940.419921875, 28569.01953125, 28718.240234375, 28608.490234375, 28279.08984375, 28003.080078125, 27652.740234375, 27388.16015625, 27548.0, 27833.2890625, 27970.220703125, 27581.66015625, 27782.419921875, 27283.58984375, 27781.01953125, 27641.830078125, 27584.080078125, 27728.119140625, 27820.0390625, 27888.150390625, 28070.509765625, 28015.01953125, 27977.150390625, 27523.189453125, 27424.470703125, 27585.91015625, 27281.169921875, 27013.25, 27494.240234375, 27732.099609375, 27724.80078125, 27742.2890625, 27641.140625, 27789.2890625, 28089.5390625, 28451.01953125, 28543.509765625, 29128.109375, 29659.890625, 29916.140625, 30181.2109375, 30008.189453125, 30381.83984375, 30447.369140625, 30670.099609375, 30511.7109375, 30323.33984375, 30500.05078125, 29839.7109375, 29639.400390625, 30248.810546875, 30240.060546875, 30183.9609375, 29544.2890625, 29452.66015625, 28771.0703125, 28444.890625, 27822.119140625, 27528.869140625, 27678.2109375, 28048.939453125, 28498.19921875, 28230.609375, 28140.279296875, 28550.9296875, 29068.630859375, 29025.4609375, 29215.51953125, 29255.55078125, 28708.580078125, 28804.849609375, 28600.41015625, 29106.009765625, 29098.240234375, 28820.08984375, 28892.689453125, 29647.080078125, 29520.900390625, 29794.369140625, 29611.5703125, 29507.05078125, 29285.4609375, 29106.779296875, 29277.859375, 29609.970703125, 29776.80078125, 29808.119140625, 29688.330078125, 29598.66015625, 29745.869140625, 29774.109375, 29302.66015625, 29499.279296875, 28751.619140625, 28283.919921875, 27821.759765625, 27935.619140625, 27753.369140625, 28029.5703125, 27927.369140625, 28455.599609375, 28860.619140625, 28725.470703125, 28437.76953125, 28640.490234375, 28432.640625, 28459.720703125, 29066.3203125, 28545.6796875, 27937.810546875, 28517.58984375, 28562.2109375, 28798.369140625, 28782.58984375, 28676.4609375, 29069.16015625, 28906.880859375, 28791.7109375, 29301.7890625, 29332.16015625, 28487.869140625, 28478.560546875, 28222.48046875, 28765.66015625, 28489.130859375, 28124.279296875, 28333.51953125, 28257.25, 27467.23046875, 27772.9296875, 27522.259765625, 27588.369140625, 27131.33984375, 27011.330078125, 26170.30078125, 26717.33984375, 27001.98046875, 27078.48046875, 27533.599609375, 27241.310546875, 27439.990234375, 27248.869140625, 27284.51953125, 27579.869140625, 27696.080078125, 27079.58984375, 26865.189453125, 27460.400390625, 27232.869140625, 27122.0703125, 26910.869140625, 26449.609375, 25970.8203125, 26476.5, 26526.8203125, 26844.720703125, 26393.029296875, 26577.26953125, 25985.470703125, 25221.41015625, 24790.94921875, 24717.529296875, 25690.400390625, 25162.779296875, 25307.849609375, 25346.48046875, 25762.009765625, 26652.890625, 26827.4296875, 27224.109375, 28040.16015625, 28110.390625, 28149.83984375, 27943.890625, 28252.419921875, 28027.25, 27821.4296875, 27665.98046875, 27736.470703125, 27787.98046875, 27350.30078125, 26888.5703125, 26985.80078125, 26821.51953125, 26334.98046875, 26843.490234375, 27172.0, 27093.189453125, 26799.7109375, 26985.08984375, 27217.849609375, 27553.060546875, 27105.259765625, 26590.779296875, 26700.109375, 26386.630859375, 26847.900390625, 26818.529296875, 27003.560546875, 26319.33984375, 26167.099609375, 26213.640625, 25748.720703125, 26427.650390625, 26547.05078125, 26659.75, 26911.19921875, 26402.83984375, 26739.029296875, 27001.51953125, 26748.140625, 26677.80078125, 26604.83984375, 26781.6796875, 27369.4296875, 27279.80078125, 27457.890625, 27413.880859375, 27761.5703125, 27915.890625, 27943.94921875, 28234.2890625, 28246.529296875, 27824.2890625, 26987.439453125, 26629.859375, 26326.16015625, 26431.19921875, 25963.0, 25771.220703125, 26246.310546875, 26149.55078125, 26171.25, 26491.970703125, 26871.26953125, 27049.470703125, 26804.599609375, 26393.0390625, 25935.619140625, 26153.810546875, 26423.470703125, 26107.650390625, 26490.529296875, 26517.189453125, 26812.30078125, 26336.66015625, 26478.76953125, 26643.390625, 26788.470703125, 26961.6796875, 27680.259765625, 27803.0, 27914.66015625, 27699.25, 27655.2109375, 27715.75, 27815.48046875, 27801.640625, 27993.349609375, 27594.73046875, 27741.900390625, 27932.19921875, 28175.869140625, 28249.240234375, 27999.9609375, 27819.330078125, 28546.98046875, 28871.779296875, 28868.91015625, 29222.76953125, 28942.140625, 28930.330078125, 28794.5, 28452.75, 28313.470703125, 28479.009765625, 28641.380859375, 27878.9609375, 28195.580078125, 28091.529296875, 27661.470703125, 27650.83984375, 27619.609375, 27626.509765625, 27430.30078125, 28065.279296875, 28214.75, 28542.109375, 28614.630859375, 27818.619140625, 27875.91015625, 27567.650390625, 27688.419921875, 27313.130859375, 27153.830078125, 26431.55078125, 26571.869140625, 26173.98046875, 26422.05078125, 25937.2109375, 26215.7890625, 26992.2109375, 27120.529296875, 27311.30078125, 27116.109375, 26401.25, 26396.830078125, 26237.419921875, 27090.759765625, 26775.7890625, 27156.140625, 27257.380859375, 27006.9609375, 26890.580078125, 26974.900390625, 27250.279296875, 27431.83984375, 27345.240234375, 27105.19921875, 27587.4609375, 27678.919921875, 27663.390625, 27199.740234375, 27527.640625, 27872.109375, 27716.4296875, 27446.099609375, 28263.5703125, 27963.470703125, 27990.169921875, 28028.30078125, 27930.5703125, 27899.76953125, 27944.7890625, 28115.740234375, 28383.08984375, 28283.029296875, 28162.830078125, 28027.83984375, 27968.990234375, 28226.080078125, 27777.900390625, 27820.400390625, 27885.869140625, 27686.400390625, 27574.4296875, 27901.009765625, 27842.330</t>
+          <t>{'dates': ['2020-01-06', '2020-01-07', '2020-01-08', '2020-01-09', '2020-01-10', '2020-01-14', '2020-01-15', '2020-01-16', '2020-01-17', '2020-01-20', '2020-01-21', '2020-01-22', '2020-01-23', '2020-01-24', '2020-01-27', '2020-01-28', '2020-01-29', '2020-01-30', '2020-01-31', '2020-02-03', '2020-02-04', '2020-02-05', '2020-02-06', '2020-02-07', '2020-02-10', '2020-02-12', '2020-02-13', '2020-02-14', '2020-02-17', '2020-02-18', '2020-02-19', '2020-02-20', '2020-02-21', '2020-02-25', '2020-02-26', '2020-02-27', '2020-02-28', '2020-03-02', '2020-03-03', '2020-03-04', '2020-03-05', '2020-03-06', '2020-03-09', '2020-03-10', '2020-03-11', '2020-03-12', '2020-03-13', '2020-03-16', '2020-03-17', '2020-03-18', '2020-03-19', '2020-03-23', '2020-03-24', '2020-03-25', '2020-03-26', '2020-03-27', '2020-03-30', '2020-03-31', '2020-04-01', '2020-04-02', '2020-04-03', '2020-04-06', '2020-04-07', '2020-04-08', '2020-04-09', '2020-04-10', '2020-04-13', '2020-04-14', '2020-04-15', '2020-04-16', '2020-04-17', '2020-04-20', '2020-04-21', '2020-04-22', '2020-04-23', '2020-04-24', '2020-04-27', '2020-04-28', '2020-04-30', '2020-05-01', '2020-05-07', '2020-05-08', '2020-05-11', '2020-05-12', '2020-05-13', '2020-05-14', '2020-05-15', '2020-05-18', '2020-05-19', '2020-05-20', '2020-05-21', '2020-05-22', '2020-05-25', '2020-05-26', '2020-05-27', '2020-05-28', '2020-05-29', '2020-06-01', '2020-06-02', '2020-06-03', '2020-06-04', '2020-06-05', '2020-06-08', '2020-06-09', '2020-06-10', '2020-06-11', '2020-06-12', '2020-06-15', '2020-06-16', '2020-06-17', '2020-06-18', '2020-06-19', '2020-06-22', '2020-06-23', '2020-06-24', '2020-06-25', '2020-06-26', '2020-06-29', '2020-06-30', '2020-07-01', '2020-07-02', '2020-07-03', '2020-07-06', '2020-07-07', '2020-07-08', '2020-07-09', '2020-07-10', '2020-07-13', '2020-07-14', '2020-07-15', '2020-07-16', '2020-07-17', '2020-07-20', '2020-07-21', '2020-07-22', '2020-07-27', '2020-07-28', '2020-07-29', '2020-07-30', '2020-07-31', '2020-08-03', '2020-08-04', '2020-08-05', '2020-08-06', '2020-08-07', '2020-08-11', '2020-08-12', '2020-08-13', '2020-08-14', '2020-08-17', '2020-08-18', '2020-08-19', '2020-08-20', '2020-08-21', '2020-08-24', '2020-08-25', '2020-08-26', '2020-08-27', '2020-08-28', '2020-08-31', '2020-09-01', '2020-09-02', '2020-09-03', '2020-09-04', '2020-09-07', '2020-09-08', '2020-09-09', '2020-09-10', '2020-09-11', '2020-09-14', '2020-09-15', '2020-09-16', '2020-09-17', '2020-09-18', '2020-09-23', '2020-09-24', '2020-09-25', '2020-09-28', '2020-09-29', '2020-09-30', '2020-10-02', '2020-10-05', '2020-10-06', '2020-10-07', '2020-10-08', '2020-10-09', '2020-10-12', '2020-10-13', '2020-10-14', '2020-10-15', '2020-10-16', '2020-10-19', '2020-10-20', '2020-10-21', '2020-10-22', '2020-10-23', '2020-10-26', '2020-10-27', '2020-10-28', '2020-10-29', '2020-10-30', '2020-11-02', '2020-11-04', '2020-11-05', '2020-11-06', '2020-11-09', '2020-11-10', '2020-11-11', '2020-11-12', '2020-11-13', '2020-11-16', '2020-11-17', '2020-11-18', '2020-11-19', '2020-11-20', '2020-11-24', '2020-11-25', '2020-11-26', '2020-11-27', '2020-11-30', '2020-12-01', '2020-12-02', '2020-12-03', '2020-12-04', '2020-12-07', '2020-12-08', '2020-12-09', '2020-12-10', '2020-12-11', '2020-12-14', '2020-12-15', '2020-12-16', '2020-12-17', '2020-12-18', '2020-12-21', '2020-12-22', '2020-12-23', '2020-12-24', '2020-12-25', '2020-12-28', '2020-12-29', '2020-12-30', '2021-01-04', '2021-01-05', '2021-01-06', '2021-01-07', '2021-01-08', '2021-01-12', '2021-01-13', '2021-01-14', '2021-01-15', '2021-01-18', '2021-01-19', '2021-01-20', '2021-01-21', '2021-01-22', '2021-01-25', '2021-01-26', '2021-01-27', '2021-01-28', '2021-01-29', '2021-02-01', '2021-02-02', '2021-02-03', '2021-02-04', '2021-02-05', '2021-02-08', '2021-02-09', '2021-02-10', '2021-02-12', '2021-02-15', '2021-02-16', '2021-02-17', '2021-02-18', '2021-02-19', '2021-02-22', '2021-02-24', '2021-02-25', '2021-02-26', '2021-03-01', '2021-03-02', '2021-03-03', '2021-03-04', '2021-03-05', '2021-03-08', '2021-03-09', '2021-03-10', '2021-03-11', '2021-03-12', '2021-03-15', '2021-03-16', '2021-03-17', '2021-03-18', '2021-03-19', '2021-03-22', '2021-03-23', '2021-03-24', '2021-03-25', '2021-03-26', '2021-03-29', '2021-03-30', '2021-03-31', '2021-04-01', '2021-04-02', '2021-04-05', '2021-04-06', '2021-04-07', '2021-04-08', '2021-04-09', '2021-04-12', '2021-04-13', '2021-04-14', '2021-04-15', '2021-04-16', '2021-04-19', '2021-04-20', '2021-04-21', '2021-04-22', '2021-04-23', '2021-04-26', '2021-04-27', '2021-04-28', '2021-04-30', '2021-05-06', '2021-05-07', '2021-05-10', '2021-05-11', '2021-05-12', '2021-05-13', '2021-05-14', '2021-05-17', '2021-05-18', '2021-05-19', '2021-05-20', '2021-05-21', '2021-05-24', '2021-05-25', '2021-05-26', '2021-05-27', '2021-05-28', '2021-05-31', '2021-06-01', '2021-06-02', '2021-06-03', '2021-06-04', '2021-06-07', '2021-06-08', '2021-06-09', '2021-06-10', '2021-06-11', '2021-06-14', '2021-06-15', '2021-06-16', '2021-06-17', '2021-06-18', '2021-06-21', '2021-06-22', '2021-06-23', '2021-06-24', '2021-06-25', '2021-06-28', '2021-06-29', '2021-06-30', '2021-07-01', '2021-07-02', '2021-07-05', '2021-07-06', '2021-07-07', '2021-07-08', '2021-07-09', '2021-07-12', '2021-07-13', '2021-07-14', '2021-07-15', '2021-07-16', '2021-07-19', '2021-07-20', '2021-07-21', '2021-07-26', '2021-07-27', '2021-07-28', '2021-07-29', '2021-07-30', '2021-08-02', '2021-08-03', '2021-08-04', '2021-08-05', '2021-08-06', '2021-08-10', '2021-08-11', '2021-08-12', '2021-08-13', '2021-08-16', '2021-08-17', '2021-08-18', '2021-08-19', '2021-08-20', '2021-08-23', '2021-08-24', '2021-08-25', '2021-08-26', '2021-08-27', '2021-08-30', '2021-08-31', '2021-09-01', '2021-09-02', '2021-09-03', '2021-09-06', '2021-09-07', '2021-09-08', '2021-09-09', '2021-09-10', '2021-09-13', '2021-09-14', '2021-09-15', '2021-09-16', '2021-09-17', '2021-09-21', '2021-09-22', '2021-09-24', '2021-09-27', '2021-09-28', '2021-09-29', '2021-09-30', '2021-10-01', '2021-10-04', '2021-10-05', '2021-10-06', '2021-10-07', '2021-10-08', '2021-10-11', '2021-10-12', '2021-10-13', '2021-10-14', '2021-10-15', '2021-10-18', '2021-10-19', '2021-10-20', '2021-10-21', '2021-10-22', '2021-10-25', '2021-10-26', '2021-10-27', '2021-10-28', '2021-10-29', '2021-11-01', '2021-11-02', '2021-11-04', '2021-11-05', '2021-11-08', '2021-11-09', '2021-11-10', '2021-11-11', '2021-11-12', '2021-11-15', '2021-11-16', '2021-11-17', '2021-11-18', '2021-11-19', '2021-11-22', '2021-11-24', '2021-11-25', '2021-11-26', '2021-11-29', '2021-11-30', '2021-12-01', '2021-12-02', '2021-12-03', '2021-12-06', '2021-12-07', '2021-12-08', '2021-12-09', '2021-12-10', '2021-12-13', '2021-12-14', '2021-12-15', '2021-12-16', '2021-12-17', '2021-12-20', '2021-12-21', '2021-12-22', '2021-12-23', '2021-12-24', '2021-12-27', '2021-12-28', '2021-12-29', '2021-12-30', '2022-01-04', '2022-01-05', '2022-01-06', '2022-01-07', '2022-01-11', '2022-01-12', '2022-01-13', '2022-01-14', '2022-01-17', '2022-01-18', '2022-01-19', '2022-01-20', '2022-01-21', '2022-01-24', '2022-01-25', '2022-01-26', '2022-01-27', '2022-01-28', '2022-01-31', '2022-02-01', '2022-02-02', '2022-02-03', '2022-02-04', '2022-02-07', '2022-02-08', '2022-02-09', '2022-02-10', '2022-02-14', '2022-02-15', '2022-02-16', '2022-02-17', '2022-02-18', '2022-02-21', '2022-02-22', '2022-02-24', '2022-02-25', '2022-02-28', '2022-03-01', '2022-03-02', '2022-03-03', '2022-03-04', '2022-03-07', '2022-03-08', '2022-03-09', '2022-03-10', '2022-03-11', '2022-03-14', '2022-03-15', '2022-03-16', '2022-03-17', '2022-03-18', '2022-03-22', '2022-03-23', '2022-03-24', '2022-03-25', '2022-03-28', '2022-03-29', '2022-03-30', '2022-03-31', '2022-04-01', '2022-04-04', '2022-04-05', '2022-04-06', '2022-04-07', '2022-04-08', '2022-04-11', '2022-04-12', '2022-04-13', '2022-04-14', '2022-04-15', '2022-04-18', '2022-04-19', '2022-04-20', '2022-04-21', '2022-04-22', '2022-04-25', '2022-04-26', '2022-04-27', '2022-04-28', '2022-05-02', '2022-05-06', '2022-05-09', '2022-05-10', '2022-05-11', '2022-05-12', '2022-05-13', '2022-05-16', '2022-05-17', '2022-05-18', '2022-05-19', '2022-05-20', '2022-05-23', '2022-05-24', '2022-05-25', '2022-05-26', '2022-05-27', '2022-05-30', '2022-05-31', '2022-06-01', '2022-06-02', '2022-06-03', '2022-06-06', '2022-06-07', '2022-06-08', '2022-06-09', '2022-06-10', '2022-06-13', '2022-06-14', '2022-06-15', '2022-06-16', '2022-06-17', '2022-06-20', '2022-06-21', '2022-06-22', '2022-06-23', '2022-06-24', '2022-06-27', '2022-06-28', '2022-06-29', '2022-06-30', '2022-07-01', '2022-07-04', '2022-07-05', '2022-07-06', '2022-07-07', '2022-07-08', '2022-07-11', '2022-07-12', '2022-07-13', '2022-07-14', '2022-07-15', '2022-07-19', '2022-07-20', '2022-07-21', '2022-07-22', '2022-07-25', '2022-07-26', '2022-07-27', '2022-07-28', '2022-07-29', '2022-08-01', '2022-08-02', '2022-08-03', '2022-08-04', '2022-08-05', '2022-08-08', '2022-08-09', '2022-08-10', '2022-08-12', '2022-08-15', '2022-08-16', '2022-08-17', '2022-08-18', '2022-08-19', '2022-08-22', '2022-08-23', '2022-08-24', '2022-08-25', '2022-08-26', '2022-08-29', '2022-08-30', '2022-08-31', '2022-09-01', '2022-09-02', '2022-09-05', '2022-09-06', '2022-09-07', '2022-09-08', '2022-09-09', '2022-09-12', '2022-09-13', '2022-09-14', '2022-09-15', '2022-09-16', '2022-09-20', '2022-09-21', '2022-09-22', '2022-09-26', '2022-09-27', '2022-09-28', '2022-09-29', '2022-09-30', '2022-10-03', '2022-10-04', '2022-10-05', '2022-10-06', '2022-10-07', '2022-10-11', '2022-10-12', '2022-10-13', '2022-10-14', '2022-10-17', '2022-10-18', '2022-10-19', '2022-10-20', '2022-10-21', '2022-10-24', '2022-10-25', '2022-10-26', '2022-10-27', '2022-10-28', '2022-10-31', '2022-11-01', '2022-11-02', '2022-11-04', '2022-11-07', '2022-11-08', '2022-11-09', '2022-11-10', '2022-11-11', '2022-11-14', '2022-11-15', '2022-11-16', '2022-11-17', '2022-11-18', '2022-11-21', '2022-11-22', '2022-11-24', '2022-11-25', '2022-11-28', '2022-11-29', '2022-11-30', '2022-12-01', '2022-12-02', '2022-12-05', '2022-12-06', '2022-12-07', '2022-12-08', '2022-12-09', '2022-12-12', '2022-12-13', '2022-12-14', '2022-12-15', '2022-12-16', '2022-12-19', '2022-12-20', '2022-12-21', '2022-12-22', '2022-12-23', '2022-12-26', '2022-12-27', '2022-12-28', '2022-12-29', '2022-12-30', '2023-01-04', '2023-01-05', '2023-01-06', '2023-01-10', '2023-01-11', '2023-01-12', '2023-01-13', '2023-01-16', '2023-01-17', '2023-01-18', '2023-01-19', '2023-01-20', '2023-01-23', '2023-01-24', '2023-01-25', '2023-01-26', '2023-01-27', '2023-01-30', '2023-01-31', '2023-02-01', '2023-02-02', '2023-02-03', '2023-02-06', '2023-02-07', '2023-02-08', '2023-02-09', '2023-02-10', '2023-02-13', '2023-02-14', '2023-02-15', '2023-02-16', '2023-02-17', '2023-02-20', '2023-02-21', '2023-02-22', '2023-02-24', '2023-02-27', '2023-02-28', '2023-03-01', '2023-03-02', '2023-03-03', '2023-03-06', '2023-03-07', '2023-03-08', '2023-03-09', '2023-03-10', '2023-03-13', '2023-03-14', '2023-03-15', '2023-03-16', '2023-03-17', '2023-03-20', '2023-03-22', '2023-03-23', '2023-03-24', '2023-03-27', '2023-03-28', '2023-03-29', '2023-03-30', '2023-03-31', '2023-04-03', '2023-04-04', '2023-04-05', '2023-04-06', '2023-04-07', '2023-04-10', '2023-04-11', '2023-04-12', '2023-04-13', '2023-04-14', '2023-04-17', '2023-04-18', '2023-04-19', '2023-04-20', '2023-04-21', '2023-04-24', '2023-04-25', '2023-04-26', '2023-04-27', '2023-04-28', '2023-05-01', '2023-05-02', '2023-05-08', '2023-05-09', '2023-05-10', '2023-05-11', '2023-05-12', '2023-05-15', '2023-05-16', '2023-05-17', '2023-05-18', '2023-05-19', '2023-05-22', '2023-05-23', '2023-05-24', '2023-05-25', '2023-05-26', '2023-05-29', '2023-05-30', '2023-05-31', '2023-06-01', '2023-06-02', '2023-06-05', '2023-06-06', '2023-06-07', '2023-06-08', '2023-06-09', '2023-06-12', '2023-06-13', '2023-06-14', '2023-06-15', '2023-06-16', '2023-06-19', '2023-06-20', '2023-06-21', '2023-06-22', '2023-06-23', '2023-06-26', '2023-06-27', '2023-06-28', '2023-06-29', '2023-06-30', '2023-07-03', '2023-07-04', '2023-07-05', '2023-07-06', '2023-07-07', '2023-07-10', '2023-07-11', '2023-07-12', '2023-07-13', '2023-07-14', '2023-07-18', '2023-07-19', '2023-07-20', '2023-07-21', '2023-07-24', '2023-07-25', '2023-07-26', '2023-07-27', '2023-07-28', '2023-07-31', '2023-08-01', '2023-08-02', '2023-08-03', '2023-08-04', '2023-08-07', '2023-08-08', '2023-08-09', '2023-08-10', '2023-08-14', '2023-08-15', '2023-08-16', '2023-08-17', '2023-08-18', '2023-08-21', '2023-08-22', '2023-08-23', '2023-08-24', '2023-08-25', '2023-08-28', '2023-08-29', '2023-08-30', '2023-08-31', '2023-09-01', '2023-09-04', '2023-09-05', '2023-09-06', '2023-09-07', '2023-09-08', '2023-09-11', '2023-09-12', '2023-09-13', '2023-09-14', '2023-09-15', '2023-09-19', '2023-09-20', '2023-09-21', '2023-09-22', '2023-09-25', '2023-09-26', '2023-09-27', '2023-09-28', '2023-09-29', '2023-10-02', '2023-10-03', '2023-10-04', '2023-10-05', '2023-10-06', '2023-10-10', '2023-10-11', '2023-10-12', '2023-10-13', '2023-10-16', '2023-10-17', '2023-10-18', '2023-10-19', '2023-10-20', '2023-10-23', '2023-10-24', '2023-10-25', '2023-10-26', '2023-10-27', '2023-10-30', '2023-10-31', '2023-11-01', '2023-11-02', '2023-11-06', '2023-11-07', '2023-11-08', '2023-11-09', '2023-11-10', '2023-11-13', '2023-11-14', '2023-11-15', '2023-11-16', '2023-11-17', '2023-11-20', '2023-11-21', '2023-11-22', '2023-11-24', '2023-11-27', '2023-11-28', '2023-11-29', '2023-11-30', '2023-12-01', '2023-12-04', '2023-12-05', '2023-12-06', '2023-12-07', '2023-12-08', '2023-12-11', '2023-12-12', '2023-12-13', '2023-12-14', '2023-12-15', '2023-12-18', '2023-12-19', '2023-12-20', '2023-12-21', '2023-12-22', '2023-12-25', '2023-12-26', '2023-12-27', '2023-12-28', '2023-12-29', '2024-01-04', '2024-01-05', '2024-01-09', '2024-01-10', '2024-01-11', '2024-01-12', '2024-01-15', '2024-01-16', '2024-01-17', '2024-01-18', '2024-01-19', '2024-01-22', '2024-01-23', '2024-01-24', '2024-01-25', '2024-01-26', '2024-01-29', '2024-01-30', '2024-01-31', '2024-02-01', '2024-02-02', '2024-02-05', '2024-02-06', '2024-02-07', '2024-02-08', '2024-02-09', '2024-02-13', '2024-02-14', '2024-02-15', '2024-02-16', '2024-02-19', '2024-02-20', '2024-02-21', '2024-02-22', '2024-02-26', '2024-02-27', '2024-02-28', '2024-02-29', '2024-03-01', '2024-03-04', '2024-03-05', '2024-03-06', '2024-03-07', '2024-03-08', '2024-03-11', '2024-03-12', '2024-03-13', '2024-03-14', '2024-03-15', '2024-03-18', '2024-03-19', '2024-03-21', '2024-03-22', '2024-03-25', '2024-03-26', '2024-03-27', '2024-03-28', '2024-03-29', '2024-04-01', '2024-04-02', '2024-04-03', '2024-04-04', '2024-04-05', '2024-04-08', '2024-04-09', '2024-04-10', '2024-04-11', '2024-04-12', '2024-04-15', '2024-04-16', '2024-04-17', '2024-04-18', '2024-04-19', '2024-04-22', '2024-04-23', '2024-04-24', '2024-04-25', '2024-04-26', '2024-04-30', '2024-05-01', '2024-05-02', '2024-05-07', '2024-05-08', '2024-05-09', '2024-05-10', '2024-05-13', '2024-05-14', '2024-05-15', '2024-05-16', '2024-05-17', '2024-05-20', '2024-05-21', '2024-05-22', '2024-05-23', '2024-05-24', '2024-05-27', '2024-05-28', '2024-05-29', '2024-05-30', '2024-05-31', '2024-06-03', '2024-06-04', '2024-06-05', '2024-06-06', '2024-06-07', '2024-06-10', '2024-06-11', '2024-06-12', '2024-06-13', '2024-06-14', '2024-06-17', '2024-06-18', '2024-06-19', '2024-06-20', '2024-06-21', '2024-06-24', '2024-06-25', '2024-06-26', '2024-06-27', '2024-06-28', '2024-07-01', '2024-07-02', '2024-07-03', '2024-07-04', '2024-07-05', '2024-07-08', '2024-07-09', '2024-07-10', '2024-07-11', '2024-07-12', '2024-07-16', '2024-07-17', '2024-07-18', '2024-07-19', '2024-07-22', '2024-07-23', '2024-07-24', '2024-07-25', '2024-07-26', '2024-07-29', '2024-07-30', '2024-07-31', '2024-08-01', '2024-08-02', '2024-08-05', '2024-08-06', '2024-08-07', '2024-08-08', '2024-08-09', '2024-08-13', '2024-08-14', '2024-08-15', '2024-08-16', '2024-08-19', '2024-08-20', '2024-08-21', '2024-08-22', '2024-08-23', '2024-08-26', '2024-08-27', '2024-08-28', '2024-08-29', '2024-08-30', '2024-09-02', '2024-09-03', '2024-09-04', '2024-09-05', '2024-09-06', '2024-09-09', '2024-09-10', '2024-09-11', '2024-09-12', '2024-09-13', '2024-09-17', '2024-09-18', '2024-09-19', '2024-09-20', '2024-09-24', '2024-09-25', '2024-09-26', '2024-09-27', '2024-09-30', '2024-10-01', '2024-10-02', '2024-10-03', '2024-10-04', '2024-10-07', '2024-10-08', '2024-10-09', '2024-10-10', '2024-10-11', '2024-10-15', '2024-10-16', '2024-10-17', '2024-10-18', '2024-10-21', '2024-10-22', '2024-10-23', '2024-10-24', '2024-10-25', '2024-10-28', '2024-10-29', '2024-10-30', '2024-10-31', '2024-11-01', '2024-11-05', '2024-11-06', '2024-11-07', '2024-11-08', '2024-11-11', '2024-11-12', '2024-11-13', '2024-11-14', '2024-11-15', '2024-11-18', '2024-11-19', '2024-11-20', '2024-11-21', '2024-11-22', '2024-11-25', '2024-11-26', '2024-11-27', '2024-11-28', '2024-11-29', '2024-12-02', '2024-12-03', '2024-12-04', '2024-12-05', '2024-12-06', '2024-12-09', '2024-12-10', '2024-12-11', '2024-12-12', '2024-12-13', '2024-12-16', '2024-12-17', '2024-12-18', '2024-12-19', '2024-12-20', '2024-12-23', '2024-12-24', '2024-12-25', '2024-12-26', '2024-12-27', '2024-12-30', '2025-01-06', '2025-01-07', '2025-01-08', '2025-01-09', '2025-01-10', '2025-01-14', '2025-01-15', '2025-01-16', '2025-01-17', '2025-01-20', '2025-01-21', '2025-01-22', '2025-01-23', '2025-01-24', '2025-01-27', '2025-01-28', '2025-01-29', '2025-01-30', '2025-01-31', '2025-02-03', '2025-02-04', '2025-02-05', '2025-02-06', '2025-02-07', '2025-02-10', '2025-02-12', '2025-02-13', '2025-02-14', '2025-02-17', '2025-02-18', '2025-02-19', '2025-02-20', '2025-02-21', '2025-02-25', '2025-02-26', '2025-02-27', '2025-02-28', '2025-03-03', '2025-03-04', '2025-03-05', '2025-03-06', '2025-03-07', '2025-03-10', '2025-03-11', '2025-03-12', '2025-03-13', '2025-03-14', '2025-03-17', '2025-03-18', '2025-03-19', '2025-03-21', '2025-03-24', '2025-03-25', '2025-03-26', '2025-03-27', '2025-03-28', '2025-03-31', '2025-04-01', '2025-04-02', '2025-04-03', '2025-04-04', '2025-04-07', '2025-04-08', '2025-04-09', '2025-04-10', '2025-04-11', '2025-04-14', '2025-04-15', '2025-04-16', '2025-04-17', '2025-04-18', '2025-04-21', '2025-04-22', '2025-04-23', '2025-04-24', '2025-04-25', '2025-04-28', '2025-04-30', '2025-05-01', '2025-05-02', '2025-05-07', '2025-05-08', '2025-05-09', '2025-05-12', '2025-05-13', '2025-05-14', '2025-05-15', '2025-05-16', '2025-05-19', '2025-05-20', '2025-05-21', '2025-05-22', '2025-05-23', '2025-05-26', '2025-05-27', '2025-05-28', '2025-05-29', '2025-05-30', '2025-06-02', '2025-06-03', '2025-06-04', '2025-06-05', '2025-06-06', '2025-06-09', '2025-06-10', '2025-06-11', '2025-06-12', '2025-06-13', '2025-06-16', '2025-06-17', '2025-06-18', '2025-06-19', '2025-06-20', '2025-06-23', '2025-06-24', '2025-06-25', '2025-06-26', '2025-06-27', '2025-06-30', '2025-07-01', '2025-07-02', '2025-07-03', '2025-07-04', '2025-07-07', '2025-07-08', '2025-07-09', '2025-07-10', '2025-07-11', '2025-07-14', '2025-07-15', '2025-07-16', '2025-07-17', '2025-07-18', '2025-07-22', '2025-07-23', '2025-07-24', '2025-07-25', '2025-07-28', '2025-07-29', '2025-07-30', '2025-07-31', '2025-08-01', '2025-08-04', '2025-08-05', '2025-08-06', '2025-08-07', '2025-08-08', '2025-08-12', '2025-08-13', '2025-08-14', '2025-08-15', '2025-08-18', '2025-08-19', '2025-08-20', '2025-08-21', '2025-08-22', '2025-08-25', '2025-08-26', '2025-08-27', '2025-08-28', '2025-08-29', '2025-09-01', '2025-09-02', '2025-09-03', '2025-09-04', '2025-09-05', '2025-09-08', '2025-09-09', '2025-09-10', '2025-09-11', '2025-09-12', '2025-09-16', '2025-09-17', '2025-09-18', '2025-09-19', '2025-09-22', '2025-09-24', '2025-09-25', '2025-09-26', '2025-09-29', '2025-09-30', '2025-10-01', '2025-10-02', '2025-10-03', '2025-10-06', '2025-10-07', '2025-10-08', '2025-10-09', '2025-10-10', '2025-10-14', '2025-10-15', '2025-10-16', '2025-10-17', '2025-10-20', '2025-10-21', '2025-10-22', '2025-10-23', '2025-10-24', '2025-10-27', '2025-10-28', '2025-10-29', '2025-10-30', '2025-10-31', '2025-11-04', '2025-11-05', '2025-11-06', '2025-11-07', '2025-11-10', '2025-11-11', '2025-11-12', '2025-11-13', '2025-11-14', '2025-11-17', '2025-11-18', '2025-11-19', '2025-11-20', '2025-11-21', '2025-11-25', '2025-11-26', '2025-11-27', '2025-11-28', '2025-12-01', '2025-12-02', '2025-12-03', '2025-12-04', '2025-12-05', '2025-12-08', '2025-12-09', '2025-12-10', '2025-12-11', '2025-12-12', '2025-12-15', '2025-12-16', '2025-12-17', '2025-12-18', '2025-12-19', '2025-12-22', '2025-12-23', '2025-12-24', '2025-12-25', '2025-12-26', '2025-12-29', '2025-12-30', '2026-01-05', '2026-01-06', '2026-01-07', '2026-01-08', '2026-01-09', '2026-01-13', '2026-01-14', '2026-01-15', '2026-01-16', '2026-01-19', '2026-01-20', '2026-01-21', '2026-01-22', '2026-01-23', '2026-01-26', '2026-01-27', '2026-01-28', '2026-01-29', '2026-01-30', '2026-02-02', '2026-02-03', '2026-02-04', '2026-02-05', '2026-02-06', '2026-02-09', '2026-02-10', '2026-02-12', '2026-02-13', '2026-02-16', '2026-02-17', '2026-02-18', '2026-02-19', '2026-02-20', '2026-02-24', '2026-02-25', '2026-02-26', '2026-02-27', '2026-03-02', '2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-03', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17'], 'prices': [23204.859375, 23575.720703125, 23204.759765625, 23739.869140625, 23850.5703125, 24025.169921875, 23916.580078125, 23933.130859375, 24041.259765625, 24083.509765625, 23864.560546875, 24031.349609375, 23795.439453125, 23827.1796875, 23343.509765625, 23215.7109375, 23379.400390625, 22977.75, 23205.1796875, 22971.939453125, 23084.58984375, 23319.560546875, 23873.58984375, 23827.98046875, 23685.98046875, 23861.2109375, 23827.73046875, 23687.58984375, 23523.240234375, 23193.80078125, 23400.69921875, 23479.150390625, 23386.740234375, 22605.41015625, 22426.189453125, 21948.23046875, 21142.9609375, 21344.080078125, 21082.73046875, 21100.060546875, 21329.119140625, 20749.75, 19698.759765625, 19867.119140625, 19416.060546875, 18559.630859375, 17431.05078125, 17002.0390625, 17011.529296875, 16726.55078125, 16552.830078125, 16887.779296875, 18092.349609375, 19546.630859375, 18664.599609375, 19389.4296875, 19084.970703125, 18917.009765625, 18065.41015625, 17818.720703125, 17820.189453125, 18576.30078125, 18950.1796875, 19353.240234375, 19345.76953125, 19498.5, 19043.400390625, 19638.810546875, 19550.08984375, 19290.19921875, 19897.259765625, 19669.119140625, 19280.779296875, 19137.94921875, 19429.439453125, 19262.0, 19783.220703125, 19771.189453125, 20193.689453125, 19619.349609375, 19674.76953125, 20179.08984375, 20390.66015625, 20366.48046875, 20267.05078125, 19914.779296875, 20037.470703125, 20133.73046875, 20433.44921875, 20595.150390625, 20552.310546875, 20388.16015625, 20741.650390625, 21271.169921875, 21419.23046875, 21916.310546875, 21877.890625, 22062.390625, 22325.609375, 22613.759765625, 22695.740234375, 22863.73046875, 23178.099609375, 23091.029296875, 23124.94921875, 22472.91015625, 22305.48046875, 21530.94921875, 22582.2109375, 22455.759765625, 22355.4609375, 22478.7890625, 22437.26953125, 22549.05078125, 22534.3203125, 22259.7890625, 22512.080078125, 21995.0390625, 22288.140625, 22121.73046875, 22145.9609375, 22306.48046875, 22714.439453125, 22614.689453125, 22438.650390625, 22529.2890625, 22290.810546875, 22784.740234375, 22587.009765625, 22945.5, 22770.359375, 22696.419921875, 22717.48046875, 22884.220703125, 22751.609375, 22715.849609375, 22657.380859375, 22397.109375, 22339.23046875, 21710.0, 22195.380859375, 22573.66015625, 22514.849609375, 22418.150390625, 22329.939453125, 22750.240234375, 22843.9609375, 23249.609375, 23289.359375, 23096.75, 23051.080078125, 23110.609375, 22880.619140625, 22920.30078125, 22985.509765625, 23296.76953125, 23290.859375, 23208.859375, 22882.650390625, 23139.759765625, 23138.0703125, 23247.150390625, 23465.529296875, 23205.4296875, 23089.94921875, 23274.130859375, 23032.5390625, 23235.470703125, 23406.490234375, 23559.30078125, 23454.890625, 23475.529296875, 23319.369140625, 23360.30078125, 23346.490234375, 23087.8203125, 23204.619140625, 23511.619140625, 23539.099609375, 23185.119140625, 23029.900390625, 23312.140625, 23433.73046875, 23422.8203125, 23647.0703125, 23619.689453125, 23558.689453125, 23601.779296875, 23626.73046875, 23507.23046875, 23410.630859375, 23671.130859375, 23567.0390625, 23639.4609375, 23474.26953125, 23516.58984375, 23494.33984375, 23485.80078125, 23418.509765625, 23331.939453125, 22977.130859375, 23295.48046875, 23695.23046875, 24105.279296875, 24325.23046875, 24839.83984375, 24905.58984375, 25349.599609375, 25520.880859375, 25385.869140625, 25906.9296875, 26014.619140625, 25728.140625, 25634.33984375, 25527.369140625, 26165.58984375, 26296.859375, 26537.310546875, 26644.7109375, 26433.619140625, 26787.5390625, 26800.98046875, 26809.369140625, 26751.240234375, 26547.439453125, 26467.080078125, 26817.939453125, 26756.240234375, 26652.51953125, 26732.439453125, 26687.83984375, 26757.400390625, 26806.669921875, 26763.390625, 26714.419921875, 26436.390625, 26524.7890625, 26668.349609375, 26656.609375, 26854.029296875, 27568.150390625, 27444.169921875, 27258.380859375, 27158.630859375, 27055.939453125, 27490.130859375, 28139.029296875, 28164.33984375, 28456.58984375, 28698.259765625, 28519.1796875, 28242.2109375, 28633.4609375, 28523.259765625, 28756.859375, 28631.44921875, 28822.2890625, 28546.1796875, 28635.2109375, 28197.419921875, 27663.390625, 28091.05078125, 28362.169921875, 28646.5, 28341.94921875, 28779.189453125, 29388.5, 29505.9296875, 29562.9296875, 29520.0703125, 30084.150390625, 30467.75, 30292.189453125, 30236.08984375, 30017.919921875, 30156.029296875, 29671.69921875, 30168.26953125, 28966.009765625, 29663.5, 29408.169921875, 29559.099609375, 28930.109375, 28864.3203125, 28743.25, 29027.939453125, 29036.560546875, 29211.640625, 29717.830078125, 29766.970703125, 29921.08984375, 29914.330078125, 30216.75, 29792.05078125, 29174.150390625, 28995.919921875, 28405.51953125, 28729.880859375, 29176.69921875, 29384.51953125, 29432.69921875, 29178.80078125, 29388.869140625, 29854.0, 30089.25, 29696.630859375, 29730.7890625, 29708.98046875, 29768.060546875, 29538.73046875, 29751.609375, 29620.990234375, 29642.689453125, 29683.369140625, 29685.369140625, 29100.380859375, 28508.55078125, 29188.169921875, 29020.630859375, 29126.23046875, 28991.890625, 29053.970703125, 28812.630859375, 29331.369140625, 29357.8203125, 29518.33984375, 28608.58984375, 28147.509765625, 27448.009765625, 28084.470703125, 27824.830078125, 28406.83984375, 28044.44921875, 28098.25, 28317.830078125, 28364.609375, 28553.98046875, 28642.189453125, 28549.009765625, 29149.41015625, 28860.080078125, 28814.33984375, 28946.140625, 29058.109375, 28941.51953125, 29019.240234375, 28963.560546875, 28860.80078125, 28958.560546875, 28948.73046875, 29161.80078125, 29441.30078125, 29291.009765625, 29018.330078125, 28964.080078125, 28010.9296875, 28884.130859375, 28874.890625, 28875.23046875, 29066.1796875, 29048.01953125, 28812.609375, 28791.529296875, 28707.0390625, 28783.279296875, 28598.189453125, 28643.2109375, 28366.94921875, 28118.029296875, 27940.419921875, 28569.01953125, 28718.240234375, 28608.490234375, 28279.08984375, 28003.080078125, 27652.740234375, 27388.16015625, 27548.0, 27833.2890625, 27970.220703125, 27581.66015625, 27782.419921875, 27283.58984375, 27781.01953125, 27641.830078125, 27584.080078125, 27728.119140625, 27820.0390625, 27888.150390625, 28070.509765625, 28015.01953125, 27977.150390625, 27523.189453125, 27424.470703125, 27585.91015625, 27281.169921875, 27013.25, 27494.240234375, 27732.099609375, 27724.80078125, 27742.2890625, 27641.140625, 27789.2890625, 28089.5390625, 28451.01953125, 28543.509765625, 29128.109375, 29659.890625, 29916.140625, 30181.2109375, 30008.189453125, 30381.83984375, 30447.369140625, 30670.099609375, 30511.7109375, 30323.33984375, 30500.05078125, 29839.7109375, 29639.400390625, 30248.810546875, 30240.060546875, 30183.9609375, 29544.2890625, 29452.66015625, 28771.0703125, 28444.890625, 27822.119140625, 27528.869140625, 27678.2109375, 28048.939453125, 28498.19921875, 28230.609375, 28140.279296875, 28550.9296875, 29068.630859375, 29025.4609375, 29215.51953125, 29255.55078125, 28708.580078125, 28804.849609375, 28600.41015625, 29106.009765625, 29098.240234375, 28820.08984375, 28892.689453125, 29647.080078125, 29520.900390625, 29794.369140625, 29611.5703125, 29507.05078125, 29285.4609375, 29106.779296875, 29277.859375, 29609.970703125, 29776.80078125, 29808.119140625, 29688.330078125, 29598.66015625, 29745.869140625, 29774.109375, 29302.66015625, 29499.279296875, 28751.619140625, 28283.919921875, 27821.759765625, 27935.619140625, 27753.369140625, 28029.5703125, 27927.369140625, 28455.599609375, 28860.619140625, 28725.470703125, 28437.76953125, 28640.490234375, 28432.640625, 28459.720703125, 29066.3203125, 28545.6796875, 27937.810546875, 28517.58984375, 28562.2109375, 28798.369140625, 28782.58984375, 28676.4609375, 29069.16015625, 28906.880859375, 28791.7109375, 29301.7890625, 29332.16015625, 28487.869140625, 28478.560546875, 28222.48046875, 28765.66015625, 28489.130859375, 28124.279296875, 28333.51953125, 28257.25, 27467.23046875, 27772.9296875, 27522.259765625, 27588.369140625, 27131.33984375, 27011.330078125, 26170.30078125, 26717.33984375, 27001.98046875, 27078.48046875, 27533.599609375, 27241.310546875, 27439.990234375, 27248.869140625, 27284.51953125, 27579.869140625, 27696.080078125, 27079.58984375, 26865.189453125, 27460.400390625, 27232.869140625, 27122.0703125, 26910.869140625, 26449.609375, 25970.8203125, 26476.5, 26526.8203125, 26844.720703125, 26393.029296875, 26577.26953125, 25985.470703125, 25221.41015625, 24790.94921875, 24717.529296875, 25690.400390625, 25162.779296875, 25307.849609375, 25346.48046875, 25762.009765625, 26652.890625, 26827.4296875, 27224.109375, 28040.16015625, 28110.390625, 28149.83984375, 27943.890625, 28252.419921875, 28027.25, 27821.4296875, 27665.98046875, 27736.470703125, 27787.98046875, 27350.30078125, 26888.5703125, 26985.80078125, 26821.51953125, 26334.98046875, 26843.490234375, 27172.0, 27093.189453125, 26799.7109375, 26985.08984375, 27217.849609375, 27553.060546875, 27105.259765625, 26590.779296875, 26700.109375, 26386.630859375, 26847.900390625, 26818.529296875, 27003.560546875, 26319.33984375, 26167.099609375, 26213.640625, 25748.720703125, 26427.650390625, 26547.05078125, 26659.75, 26911.19921875, 26402.83984375, 26739.029296875, 27001.51953125, 26748.140625, 26677.80078125, 26604.83984375, 26781.6796875, 27369.4296875, 27279.80078125, 27457.890625, 27413.880859375, 27761.5703125, 27915.890625, 27943.94921875, 28234.2890625, 28246.529296875, 27824.2890625, 26987.439453125, 26629.859375, 26326.16015625, 26431.19921875, 25963.0, 25771.220703125, 26246.310546875, 26149.55078125, 26171.25, 26491.970703125, 26871.26953125, 27049.470703125, 26804.599609375, 26393.0390625, 25935.619140625, 26153.810546875, 26423.470703125, 26107.650390625, 26490.529296875, 26517.189453125, 26812.30078125, 26336.66015625, 26478.76953125, 26643.390625, 26788.470703125, 26961.6796875, 27680.259765625, 27803.0, 27914.66015625, 27699.25, 27655.2109375, 27715.75, 27815.48046875, 27801.640625, 27993.349609375, 27594.73046875, 27741.900390625, 27932.19921875, 28175.869140625, 28249.240234375, 27999.9609375, 27819.330078125, 28546.98046875, 28871.779296875, 28868.91015625, 29222.76953125, 28942.140625, 28930.330078125, 28794.5, 28452.75, 28313.470703125, 28479.009765625, 28641.380859375, 27878.9609375, 28195.580078125, 28091.529296875, 27661.470703125, 27650.83984375, 27619.609375, 27626.509765625, 27430.30078125, 28065.279296875, 28214.75, 28542.109375, 28614.630859375, 27818.619140625, 27875.91015625, 27567.650390625, 27688.419921875, 27313.130859375, 27153.830078125, 26431.55078125, 26571.869140625, 26173.98046875, 26422.05078125, 25937.2109375, 26215.7890625, 26992.2109375, 27120.529296875, 27311.30078125, 27116.109375, 26401.25, 26396.830078125, 26237.419921875, 27090.759765625, 26775.7890625, 27156.140625, 27257.380859375, 27006.9609375, 26890.580078125, 26974.900390625, 27250.279296875, 27431.83984375, 27345.240234375, 27105.19921875, 27587.4609375, 27678.919921875, 27663.390625, 27199.740234375, 27527.640625, 27872.109375, 27716.4296875, 27446.099609375, 28263.5703125, 27963.470703125, 27990.169921875, 28028.30078125, 27930.5703125, 27899.76953125, 27944.7890625, 28115.740234375, 28383.08984375, 28283.029296875, 28162.830078125, 28027.83984375, 279</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-05 14:48:46</t>
+          <t>2026-04-19 16:11:00</t>
         </is>
       </c>
     </row>
